--- a/data/upcoming_events.xlsx
+++ b/data/upcoming_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D172"/>
+  <dimension ref="A1:D192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,27 +441,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AONESTEELS</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WAAREERTL</t>
+          <t>AYE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -471,37 +471,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VARMORA</t>
+          <t>DBSTOCKBRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SMLMAH</t>
+          <t>DIGJAMLMTD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -511,17 +511,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NELCO</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -531,17 +531,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MGEL</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -551,17 +551,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>SHEKHAWATI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -571,17 +571,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JPPOWER</t>
+          <t>SWASTIKAIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -591,57 +591,57 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MOTOGENFIN</t>
+          <t>VMM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GTECJAINX</t>
+          <t>ZEELEARN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GOCLCORP</t>
+          <t>VGL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -651,37 +651,37 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GALLANTT</t>
+          <t>TINNARUBR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ELEVATE</t>
+          <t>SWIGGY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -691,57 +691,57 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DELTACORP</t>
+          <t>SURYODAY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BEPL</t>
+          <t>SAPPHIRE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>PAISALO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,87 +751,87 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KAPSTON</t>
+          <t>RALLIS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Financial Results/Stock split/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SRTL</t>
+          <t>INDOTHAI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VINCOFE</t>
+          <t>FAIRCHEMOR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>CYIENT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -841,17 +841,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>VMM</t>
+          <t>CREDITACC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -861,17 +861,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SHEKHAWATI</t>
+          <t>BONLON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -881,17 +881,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>BLUESTONE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -901,7 +901,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SWASTIKAIN</t>
+          <t>BANSALWIRE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -921,17 +921,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DBSTOCKBRO</t>
+          <t>NUVOCO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -941,7 +941,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AYE</t>
+          <t>PONNIERODE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -951,37 +951,37 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>RAMCOSYS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DIGJAMLMTD</t>
+          <t>REPRO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -991,17 +991,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ZEELEARN</t>
+          <t>RUNWALENTR</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1021,17 +1021,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>VGL</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1041,17 +1041,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TINNARUBR</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1061,17 +1061,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SWIGGY</t>
+          <t>SSWL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1081,17 +1081,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SURYODAY</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1101,7 +1101,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RALLIS</t>
+          <t>UNIECOM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1121,7 +1121,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PAISALO</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1141,7 +1141,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SAPPHIRE</t>
+          <t>PANACHE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1161,7 +1161,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>INDOTHAI</t>
+          <t>SKMEGGPROD</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1181,7 +1181,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FAIRCHEMOR</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1201,17 +1201,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CYIENT</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1221,17 +1221,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CREDITACC</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1241,17 +1241,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BONLON</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1261,17 +1261,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BLUESTONE</t>
+          <t>ASMS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1281,7 +1281,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BANSALWIRE</t>
+          <t>CUBEXTUB</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1301,7 +1301,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NUVOCO</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1321,12 +1321,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>RAMCOSYS</t>
+          <t>GRADIENTE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>REPRO</t>
+          <t>GNA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1355,13 +1355,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>NEWGEN</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1375,18 +1375,18 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SKMEGGPROD</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1395,18 +1395,18 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>KSOLVES</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1415,13 +1415,13 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>KSOLVES</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1435,18 +1435,18 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>MAHLOG</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1455,13 +1455,13 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PONNIERODE</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1475,23 +1475,23 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SSWL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1501,17 +1501,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>TIJARIA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -1521,7 +1521,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>SESHAPAPER</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -1541,7 +1541,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>RAJOOENG</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1561,17 +1561,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MAHLOG</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -1581,7 +1581,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>KSOLVES</t>
+          <t>BHARATCOAL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -1601,17 +1601,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>CHEMCON</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -1621,7 +1621,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -1641,7 +1641,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>GNA</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -1661,7 +1661,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>GERMAN</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -1681,7 +1681,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CUBEXTUB</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1691,37 +1691,37 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NEWGEN</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SESHAPAPER</t>
+          <t>UGARSUGAR</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1731,17 +1731,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>RAJOOENG</t>
+          <t>SHANTIGEAR</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1751,77 +1751,77 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>NDTV</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TIJARIA</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BHARATCOAL</t>
+          <t>LEAPIND</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1831,17 +1831,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>JBMA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>ASTEC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1871,42 +1871,42 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CHEMCON</t>
+          <t>ISHANCH</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>GENUSPOWER</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Buyback</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SHANTIGEAR</t>
+          <t>DHANBANK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1935,13 +1935,13 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>DEEPA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1955,18 +1955,18 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1975,13 +1975,13 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>JBMA</t>
+          <t>CYBERMEDIA</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1995,13 +1995,13 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2015,18 +2015,18 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CYBERMEDIA</t>
+          <t>AAVAS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2035,13 +2035,13 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>ITCHOTELS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2055,23 +2055,23 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ASTEC</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -2081,7 +2081,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AAVAS</t>
+          <t>NIITLTD</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -2101,17 +2101,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DHANBANK</t>
+          <t>ODIGMA</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2135,18 +2135,18 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>STERTOOLS</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STARHEALTH</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2175,18 +2175,18 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>STARHEALTH</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2195,18 +2195,18 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ODIGMA</t>
+          <t>LTFOODS</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2215,18 +2215,18 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2235,13 +2235,13 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>JSWCEMENT</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2255,13 +2255,13 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>JSWCEMENT</t>
+          <t>CENTENKA</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2275,18 +2275,18 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>IRISDOREME</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2295,18 +2295,18 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>INDOCO</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2315,18 +2315,18 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>HUHTAMAKI</t>
+          <t>KNACK</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2335,13 +2335,13 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>LTFOODS</t>
+          <t>HUHTAMAKI</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2355,13 +2355,13 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CENTENKA</t>
+          <t>INDOCO</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2375,53 +2375,53 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ZENSARTECH</t>
+          <t>IRISDOREME</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>TCIFINANCE</t>
+          <t>GULFPETRO</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>VSTIND</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2435,13 +2435,13 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MEESHO</t>
+          <t>ZENSARTECH</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2455,18 +2455,18 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>TCIFINANCE</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>SMARTLINK</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2495,13 +2495,13 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>KAMDHENU</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2515,18 +2515,18 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>MEESHO</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2535,18 +2535,18 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2555,13 +2555,13 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2575,13 +2575,13 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>KAMDHENU</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2595,18 +2595,18 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2615,13 +2615,13 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>INFOBEAN</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>JETFREIGHT</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2655,13 +2655,13 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>INFOBEAN</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2675,13 +2675,13 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SURYODAY</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2691,17 +2691,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>NOCIL</t>
+          <t>ANANTRAJ</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2711,57 +2711,57 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>KREBSBIO</t>
+          <t>ATLASCYCLE</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>INDSWFTLAB</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2771,62 +2771,62 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>INDGN</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>FSL</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>GREENPLY</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -2835,18 +2835,18 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CARERATING</t>
+          <t>STEAMHOUSE</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -2855,18 +2855,18 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CAPITALSFB</t>
+          <t>SANOFI</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -2875,18 +2875,18 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>PINELABS</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -2895,13 +2895,13 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2915,13 +2915,13 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>NOCIL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2935,13 +2935,13 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>SURYODAY</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2951,37 +2951,37 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>KREBSBIO</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>GREENPLY</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2991,37 +2991,37 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>GMDCLTD</t>
+          <t>INDGN</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>ICRA</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3031,17 +3031,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BHARATGEAR</t>
+          <t>FSL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3051,37 +3051,37 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>CARERATING</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR</t>
+          <t>CAPITALSFB</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3091,57 +3091,57 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ATULAUTO</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>3IINFOLTD</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>INDSWFTLAB</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3151,37 +3151,37 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DLINKINDIA</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>IITL</t>
+          <t>GMDCLTD</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3191,17 +3191,17 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>LATENTVIEW</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3211,17 +3211,17 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>TVTODAY</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3231,37 +3231,37 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>BHARATGEAR</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SHK</t>
+          <t>ANDHRAPAP</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3271,37 +3271,37 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>NELCAST</t>
+          <t>BESTAGRO</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>NEPHROPLUS</t>
+          <t>UTTAMSUGAR</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SUBEXLTD</t>
+          <t>MERCURYEV</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>RML</t>
+          <t>LATENTVIEW</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3391,17 +3391,17 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>IITL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3411,17 +3411,17 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>NITINSPIN</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3431,17 +3431,17 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3451,37 +3451,37 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>ATULAUTO</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3491,77 +3491,77 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>GSPLTRANS</t>
+          <t>DLINKINDIA</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>ARE&amp;M</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>MINDTECK</t>
+          <t>NELCAST</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3571,97 +3571,97 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>SHK</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>TVTODAY</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>RBZJEWEL</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>LCL</t>
+          <t>SUBEXLTD</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -3671,37 +3671,37 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ORIENTPPR</t>
+          <t>RML</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>PRAXIS</t>
+          <t>ZYDUSWELL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -3711,17 +3711,17 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>TEAMLEASE</t>
+          <t>NEPHROPLUS</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3731,37 +3731,37 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>UGROCAP</t>
+          <t>GSPLTRANS</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>TTKPRESTIG</t>
+          <t>EMCURE</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3771,37 +3771,37 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>COFFEEDAY</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>FOSECOIND</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -3811,17 +3811,17 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>LUXIND</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -3831,31 +3831,431 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
+          <t>STOVEKRAFT</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>SAREGAMA</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>MINDTECK</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>MARKSANS</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>RITES</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>LCL</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>EMUDHRA</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>ELLEN</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>LENSKART</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>AMAGI</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>IRIS</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>ORIENTPPR</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>PRAXIS</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>TEAMLEASE</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>UGROCAP</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>TTKPRESTIG</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>COFFEEDAY</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>FOSECOIND</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>RAIN</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
           <t>RANEHOLDIN</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
         <is>
           <t>2026-11-12</t>
         </is>
       </c>
-      <c r="D172" t="n">
-        <v>25</v>
+      <c r="D192" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/data/upcoming_events.xlsx
+++ b/data/upcoming_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D192"/>
+  <dimension ref="A1:D199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -935,18 +935,18 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PONNIERODE</t>
+          <t>RAMCOSYS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -955,18 +955,18 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RAMCOSYS</t>
+          <t>REPRO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>REPRO</t>
+          <t>RUNWALENTR</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -995,18 +995,18 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RUNWALENTR</t>
+          <t>SAKAR</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PANACHE</t>
+          <t>PONNIERODE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -1175,13 +1175,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>PANACHE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1215,13 +1215,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>NEWGEN</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GNA</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1355,13 +1355,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NEWGEN</t>
+          <t>GNA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -1455,13 +1455,13 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1475,38 +1475,38 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TIJARIA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1515,18 +1515,18 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SESHAPAPER</t>
+          <t>TIJARIA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1535,13 +1535,13 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>RAJOOENG</t>
+          <t>SESHAPAPER</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1555,18 +1555,18 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>RAJOOENG</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1575,18 +1575,18 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BHARATCOAL</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1595,18 +1595,18 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CHEMCON</t>
+          <t>BHARATCOAL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1615,18 +1615,18 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>CHEMCON</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1635,13 +1635,13 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1655,13 +1655,13 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GERMAN</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1675,13 +1675,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>GERMAN</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1691,22 +1691,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1715,18 +1715,18 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>UGARSUGAR</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1735,18 +1735,18 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SHANTIGEAR</t>
+          <t>SRIT</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1755,13 +1755,13 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>UGARSUGAR</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1775,13 +1775,13 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>SHANTIGEAR</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1795,13 +1795,13 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1815,13 +1815,13 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>LEAPIND</t>
+          <t>NDTV</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1835,13 +1835,13 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>JBMA</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1855,13 +1855,13 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ASTEC</t>
+          <t>LEAPIND</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1875,13 +1875,13 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ISHANCH</t>
+          <t>JBMA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1895,18 +1895,18 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>GENUSPOWER</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Buyback</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DHANBANK</t>
+          <t>ISHANCH</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1935,18 +1935,18 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DEEPA</t>
+          <t>GENUSPOWER</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Buyback</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1955,18 +1955,18 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>DHANBANK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1975,13 +1975,13 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CYBERMEDIA</t>
+          <t>DEEPA</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1995,18 +1995,18 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2015,18 +2015,18 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AAVAS</t>
+          <t>CYBERMEDIA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2035,13 +2035,13 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ITCHOTELS</t>
+          <t>ASTEC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2055,58 +2055,58 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>AAVAS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>NIITLTD</t>
+          <t>ITCHOTELS</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ODIGMA</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2115,18 +2115,18 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>NIITLTD</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STERTOOLS</t>
+          <t>ODIGMA</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2155,18 +2155,18 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2175,13 +2175,13 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STARHEALTH</t>
+          <t>TBZ</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2195,18 +2195,18 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>LTFOODS</t>
+          <t>STERTOOLS</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2215,18 +2215,18 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2235,18 +2235,18 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>JSWCEMENT</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2255,13 +2255,13 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CENTENKA</t>
+          <t>STARHEALTH</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2275,13 +2275,13 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>LTFOODS</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2295,13 +2295,13 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GANDHAR</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2315,18 +2315,18 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>KNACK</t>
+          <t>JSWCEMENT</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2335,13 +2335,13 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>HUHTAMAKI</t>
+          <t>CENTENKA</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2355,13 +2355,13 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>INDOCO</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>IRISDOREME</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100">
@@ -2415,33 +2415,33 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>VSTIND</t>
+          <t>KNACK</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ZENSARTECH</t>
+          <t>HUHTAMAKI</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2451,17 +2451,17 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>TCIFINANCE</t>
+          <t>INDOCO</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2471,57 +2471,57 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SMARTLINK</t>
+          <t>IRISDOREME</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>HOMEFIRST</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MEESHO</t>
+          <t>TCIFINANCE</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2535,18 +2535,18 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>ZENSARTECH</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2555,13 +2555,13 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>VSTIND</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2575,13 +2575,13 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>KAMDHENU</t>
+          <t>SMARTLINK</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110">
@@ -2615,13 +2615,13 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>INFOBEAN</t>
+          <t>NITYAS</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>JETFREIGHT</t>
+          <t>MEESHO</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2655,18 +2655,18 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2675,13 +2675,13 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2695,13 +2695,13 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>KAMDHENU</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2715,13 +2715,13 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2735,13 +2735,13 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ATLASCYCLE</t>
+          <t>INFOBEAN</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2755,13 +2755,13 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>JETFREIGHT</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2795,18 +2795,18 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -2815,33 +2815,33 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>ANANTRAJ</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STEAMHOUSE</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2851,57 +2851,57 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SANOFI</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PINELABS</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2911,17 +2911,17 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>NOCIL</t>
+          <t>ATLASCYCLE</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2931,11 +2931,11 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="127">
@@ -2955,18 +2955,18 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>KREBSBIO</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -2975,13 +2975,13 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GREENPLY</t>
+          <t>STEAMHOUSE</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2995,18 +2995,18 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>INDGN</t>
+          <t>SANOFI</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3015,18 +3015,18 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>PINELABS</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3035,18 +3035,18 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FSL</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3055,18 +3055,18 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>CARERATING</t>
+          <t>NOCIL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3075,18 +3075,18 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CAPITALSFB</t>
+          <t>KREBSBIO</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3095,18 +3095,18 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>GREENPLY</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3115,13 +3115,13 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>INDGN</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>INDSWFTLAB</t>
+          <t>ICRA</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3155,13 +3155,13 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>FSL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3171,37 +3171,37 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>GMDCLTD</t>
+          <t>CARERATING</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>CAPITALSFB</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3211,57 +3211,57 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BHARATGEAR</t>
+          <t>3IINFOLTD</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ANDHRAPAP</t>
+          <t>INDSWFTLAB</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3271,17 +3271,17 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3295,13 +3295,13 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BESTAGRO</t>
+          <t>GMDCLTD</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3315,13 +3315,13 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3335,13 +3335,13 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>MERCURYEV</t>
+          <t>BESTAGRO</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>LATENTVIEW</t>
+          <t>ANDHRAPAP</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3391,17 +3391,17 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>IITL</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3411,17 +3411,17 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>NITINSPIN</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3431,17 +3431,17 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>BHARATGEAR</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3451,17 +3451,17 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>UTTAMSUGAR</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3475,13 +3475,13 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ATULAUTO</t>
+          <t>MERCURYEV</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3495,18 +3495,18 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>DLINKINDIA</t>
+          <t>LATENTVIEW</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3515,33 +3515,33 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>IITL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>NELCAST</t>
+          <t>NITINSPIN</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -3551,17 +3551,17 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3571,17 +3571,17 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SHK</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -3591,77 +3591,77 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>ATULAUTO</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>TVTODAY</t>
+          <t>DLINKINDIA</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>RBZJEWEL</t>
+          <t>ARE&amp;M</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SUBEXLTD</t>
+          <t>NELCAST</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -3671,17 +3671,17 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>RML</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -3691,17 +3691,17 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>SHK</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -3711,37 +3711,37 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>NEPHROPLUS</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>GSPLTRANS</t>
+          <t>TVTODAY</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3751,17 +3751,17 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>ZYDUSWELL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3775,18 +3775,18 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>SUBEXLTD</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3795,13 +3795,13 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>RML</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -3815,13 +3815,13 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>NEPHROPLUS</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -3835,33 +3835,33 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>STOVEKRAFT</t>
+          <t>RBZJEWEL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>GSPLTRANS</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3871,77 +3871,77 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>MINDTECK</t>
+          <t>EMCURE</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>LCL</t>
+          <t>LUXIND</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -3951,17 +3951,17 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>STOVEKRAFT</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -3975,18 +3975,18 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -3995,18 +3995,18 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>MINDTECK</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4015,13 +4015,13 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4035,13 +4035,13 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>AMAGI</t>
+          <t>LENSKART</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4051,57 +4051,57 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>RITES</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ORIENTPPR</t>
+          <t>JASH</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>PRAXIS</t>
+          <t>EMUDHRA</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4111,57 +4111,57 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>TEAMLEASE</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>UGROCAP</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>TTKPRESTIG</t>
+          <t>LCL</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4171,17 +4171,17 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>COFFEEDAY</t>
+          <t>AMAGI</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4191,17 +4191,17 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>FOSECOIND</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4211,51 +4211,191 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>ORIENTPPR</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
+          <t>PRAXIS</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>TEAMLEASE</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>UGROCAP</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>TTKPRESTIG</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>COFFEEDAY</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>FOSECOIND</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>RAIN</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
           <t>RANEHOLDIN</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
         <is>
           <t>2026-11-12</t>
         </is>
       </c>
-      <c r="D192" t="n">
-        <v>24</v>
+      <c r="D199" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/data/upcoming_events.xlsx
+++ b/data/upcoming_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D199"/>
+  <dimension ref="A1:D190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>BANSALWIRE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,17 +451,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AYE</t>
+          <t>ZEELEARN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -471,17 +471,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DBSTOCKBRO</t>
+          <t>TINNARUBR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -491,17 +491,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DIGJAMLMTD</t>
+          <t>SWIGGY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -511,37 +511,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>SURYODAY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>SAPPHIRE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -551,17 +551,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SHEKHAWATI</t>
+          <t>RALLIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -571,17 +571,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SWASTIKAIN</t>
+          <t>PAISALO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -591,42 +591,42 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VMM</t>
+          <t>VGL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ZEELEARN</t>
+          <t>INDOTHAI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -641,12 +641,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VGL</t>
+          <t>FAIRCHEMOR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -661,12 +661,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TINNARUBR</t>
+          <t>CYIENT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -681,12 +681,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SWIGGY</t>
+          <t>CREDITACC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -701,12 +701,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SURYODAY</t>
+          <t>BONLON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -721,12 +721,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SAPPHIRE</t>
+          <t>BLUESTONE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -741,7 +741,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PAISALO</t>
+          <t>NUVOCO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -761,47 +761,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RALLIS</t>
+          <t>RAMCOSYS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>INDOTHAI</t>
+          <t>REPRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FAIRCHEMOR</t>
+          <t>RUNWALENTR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -811,117 +811,117 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CYIENT</t>
+          <t>SAKAR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CREDITACC</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BONLON</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BLUESTONE</t>
+          <t>SKMEGGPROD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BANSALWIRE</t>
+          <t>SSWL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NUVOCO</t>
+          <t>UNIECOM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -931,22 +931,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>RAMCOSYS</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>REPRO</t>
+          <t>PONNIERODE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -981,7 +981,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RUNWALENTR</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1001,12 +1001,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SAKAR</t>
+          <t>PANACHE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1021,7 +1021,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>NEWGEN</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1061,12 +1061,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SSWL</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1081,12 +1081,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>ASMS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1101,7 +1101,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>UNIECOM</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1121,7 +1121,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>CUBEXTUB</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1141,7 +1141,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PONNIERODE</t>
+          <t>GNA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1161,12 +1161,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SKMEGGPROD</t>
+          <t>GRADIENTE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1181,7 +1181,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PANACHE</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1221,7 +1221,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NEWGEN</t>
+          <t>KSOLVES</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1241,12 +1241,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>KSOLVES</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1261,12 +1261,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ASMS</t>
+          <t>MAHLOG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CUBEXTUB</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1301,7 +1301,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1321,47 +1321,47 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GRADIENTE</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>TIJARIA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GNA</t>
+          <t>SESHAPAPER</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1371,17 +1371,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>RAJOOENG</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1391,37 +1391,37 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>KSOLVES</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dividend</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KSOLVES</t>
+          <t>BHARATCOAL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1431,37 +1431,37 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MAHLOG</t>
+          <t>CHEMCON</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1471,17 +1471,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1491,22 +1491,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>GERMAN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1521,87 +1521,87 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TIJARIA</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SESHAPAPER</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>RAJOOENG</t>
+          <t>SRIT</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>UGARSUGAR</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BHARATCOAL</t>
+          <t>SHANTIGEAR</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1611,37 +1611,37 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CHEMCON</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>NDTV</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1651,17 +1651,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1671,17 +1671,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>GERMAN</t>
+          <t>LEAPIND</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1691,17 +1691,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>JBMA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1721,12 +1721,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1741,12 +1741,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SRIT</t>
+          <t>ISHANCH</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1761,12 +1761,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>UGARSUGAR</t>
+          <t>GENUSPOWER</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Buyback</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1781,7 +1781,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SHANTIGEAR</t>
+          <t>DHANBANK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>DEEPA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1821,12 +1821,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1841,7 +1841,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>CYBERMEDIA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1861,7 +1861,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>LEAPIND</t>
+          <t>ASTEC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>JBMA</t>
+          <t>AAVAS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1901,7 +1901,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>ITCHOTELS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1921,107 +1921,107 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ISHANCH</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GENUSPOWER</t>
+          <t>NIITLTD</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Buyback</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DHANBANK</t>
+          <t>ODIGMA</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DEEPA</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CYBERMEDIA</t>
+          <t>STARHEALTH</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2031,82 +2031,82 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ASTEC</t>
+          <t>STERTOOLS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AAVAS</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ITCHOTELS</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>LTFOODS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2121,12 +2121,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>NIITLTD</t>
+          <t>TBZ</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2141,12 +2141,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ODIGMA</t>
+          <t>JSWCEMENT</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2161,12 +2161,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>CENTENKA</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TBZ</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STERTOOLS</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2221,12 +2221,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>GULFPETRO</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2241,12 +2241,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>KNACK</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STARHEALTH</t>
+          <t>HUHTAMAKI</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2281,7 +2281,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>LTFOODS</t>
+          <t>INDOCO</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2301,7 +2301,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>IRISDOREME</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2321,12 +2321,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>JSWCEMENT</t>
+          <t>HOMEFIRST</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CENTENKA</t>
+          <t>ZENSARTECH</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>VSTIND</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2371,37 +2371,37 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>GANDHAR</t>
+          <t>SMARTLINK</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>GULFPETRO</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2411,37 +2411,37 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>KNACK</t>
+          <t>NITYAS</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>HUHTAMAKI</t>
+          <t>MEESHO</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2451,71 +2451,71 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>INDOCO</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>IRISDOREME</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>HOMEFIRST</t>
+          <t>KAMDHENU</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106">
@@ -2541,7 +2541,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ZENSARTECH</t>
+          <t>INFOBEAN</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2561,7 +2561,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>VSTIND</t>
+          <t>JETFREIGHT</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2581,7 +2581,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SMARTLINK</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2601,12 +2601,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2621,7 +2621,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>NITYAS</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2641,7 +2641,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MEESHO</t>
+          <t>ANANTRAJ</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2661,12 +2661,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2681,7 +2681,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>ATLASCYCLE</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2701,7 +2701,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>KAMDHENU</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2721,7 +2721,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2741,12 +2741,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>INFOBEAN</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2761,7 +2761,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>JETFREIGHT</t>
+          <t>SURYODAY</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2771,17 +2771,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>STEAMHOUSE</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2791,77 +2791,77 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>SANOFI</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>PINELABS</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>NOCIL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2871,37 +2871,37 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>KREBSBIO</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2911,17 +2911,17 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ATLASCYCLE</t>
+          <t>INDSWFTLAB</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2931,22 +2931,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SURYODAY</t>
+          <t>INDGN</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -2961,12 +2961,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>ICRA</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -2981,7 +2981,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STEAMHOUSE</t>
+          <t>GREENPLY</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3001,7 +3001,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SANOFI</t>
+          <t>CARERATING</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3021,12 +3021,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>PINELABS</t>
+          <t>CAPITALSFB</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>NOCIL</t>
+          <t>3IINFOLTD</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3081,12 +3081,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>KREBSBIO</t>
+          <t>FSL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3101,7 +3101,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>GREENPLY</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3111,37 +3111,37 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>INDGN</t>
+          <t>GMDCLTD</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3151,17 +3151,17 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FSL</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3171,37 +3171,37 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CARERATING</t>
+          <t>BESTAGRO</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>CAPITALSFB</t>
+          <t>ANDHRAPAP</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3211,57 +3211,57 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>INDSWFTLAB</t>
+          <t>BHARATGEAR</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3271,17 +3271,17 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>UTTAMSUGAR</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3291,17 +3291,17 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>GMDCLTD</t>
+          <t>MERCURYEV</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>LATENTVIEW</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>IITL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BESTAGRO</t>
+          <t>NITINSPIN</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ANDHRAPAP</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3391,17 +3391,17 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3411,17 +3411,17 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>ATULAUTO</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3431,57 +3431,57 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>BHARATGEAR</t>
+          <t>DLINKINDIA</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR</t>
+          <t>ARE&amp;M</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MERCURYEV</t>
+          <t>NELCAST</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3491,17 +3491,17 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>LATENTVIEW</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3511,17 +3511,17 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>IITL</t>
+          <t>SHK</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3531,37 +3531,37 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>NITINSPIN</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>TVTODAY</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3571,17 +3571,17 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>ZYDUSWELL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -3591,17 +3591,17 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ATULAUTO</t>
+          <t>SUBEXLTD</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3611,77 +3611,77 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>DLINKINDIA</t>
+          <t>RML</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>NEPHROPLUS</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>NELCAST</t>
+          <t>RBZJEWEL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>GSPLTRANS</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -3691,17 +3691,17 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SHK</t>
+          <t>EMCURE</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -3711,17 +3711,17 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3731,17 +3731,17 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>TVTODAY</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3751,17 +3751,17 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>LUXIND</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3781,7 +3781,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SUBEXLTD</t>
+          <t>STOVEKRAFT</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -3791,17 +3791,17 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>RML</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -3811,57 +3811,57 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>NEPHROPLUS</t>
+          <t>MINDTECK</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>RBZJEWEL</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>GSPLTRANS</t>
+          <t>LENSKART</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3871,57 +3871,57 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>RITES</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>JASH</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>EMUDHRA</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -3931,37 +3931,37 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>STOVEKRAFT</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>LCL</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4001,27 +4001,27 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>MINDTECK</t>
+          <t>AMAGI</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4031,57 +4031,57 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>ORIENTPPR</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>PRAXIS</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>JASH</t>
+          <t>TEAMLEASE</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4091,57 +4091,57 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>UGROCAP</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>TTKPRESTIG</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>COFFEEDAY</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4151,17 +4151,17 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>LCL</t>
+          <t>FOSECOIND</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4171,17 +4171,17 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>AMAGI</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4191,17 +4191,17 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>RANEHOLDIN</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4211,190 +4211,10 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>ORIENTPPR</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Financial Results/Other business matters</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>PRAXIS</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>TEAMLEASE</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>UGROCAP</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Financial Results/Other business matters</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>TTKPRESTIG</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="D195" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>COFFEEDAY</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="D196" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>FOSECOIND</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="D197" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>RAIN</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="D198" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>RANEHOLDIN</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="D199" t="n">
         <v>23</v>
       </c>
     </row>

--- a/data/upcoming_events.xlsx
+++ b/data/upcoming_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D190"/>
+  <dimension ref="A1:D247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -475,13 +475,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TINNARUBR</t>
+          <t>VGL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VGL</t>
+          <t>TINNARUBR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -615,18 +615,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INDOTHAI</t>
+          <t>NEUEON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -635,18 +635,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FAIRCHEMOR</t>
+          <t>INDOTHAI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -655,18 +655,18 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CYIENT</t>
+          <t>FAIRCHEMOR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -675,18 +675,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CREDITACC</t>
+          <t>CYIENT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -695,18 +695,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BONLON</t>
+          <t>CREDITACC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -715,18 +715,18 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BLUESTONE</t>
+          <t>BONLON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -735,18 +735,18 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NUVOCO</t>
+          <t>BLUESTONE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -755,38 +755,38 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RAMCOSYS</t>
+          <t>NUVOCO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>REPRO</t>
+          <t>RAMCOSYS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -795,13 +795,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RUNWALENTR</t>
+          <t>REPRO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -855,13 +855,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -875,18 +875,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SKMEGGPROD</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>UNIECOM</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>UNIECOM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -955,13 +955,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PONNIERODE</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>PONNIERODE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -995,18 +995,18 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PANACHE</t>
+          <t>SKMEGGPROD</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>PANACHE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1035,13 +1035,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NEWGEN</t>
+          <t>RUNWALENTR</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1055,13 +1055,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>NEWGEN</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1075,18 +1075,18 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ASMS</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1095,18 +1095,18 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>ASMS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GNA</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -1175,13 +1175,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>GNA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1315,38 +1315,38 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TIJARIA</t>
+          <t>MODIS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1355,18 +1355,18 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SESHAPAPER</t>
+          <t>TIJARIA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RAJOOENG</t>
+          <t>SESHAPAPER</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1395,18 +1395,18 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>RAJOOENG</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1415,18 +1415,18 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BHARATCOAL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1435,18 +1435,18 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CHEMCON</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1455,18 +1455,18 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>CHEMCON</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>BHARATCOAL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1495,13 +1495,13 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GERMAN</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1515,13 +1515,13 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1531,57 +1531,57 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>GERMAN</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SRIT</t>
+          <t>RAILTEL</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>UGARSUGAR</t>
+          <t>NDTV</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1595,18 +1595,18 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SHANTIGEAR</t>
+          <t>NDTV</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
@@ -1635,13 +1635,13 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>PNGSREVA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1655,13 +1655,13 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>RIR</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1675,13 +1675,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LEAPIND</t>
+          <t>SHANTIGEAR</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1695,18 +1695,18 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>JBMA</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1715,18 +1715,18 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>SRIT</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ISHANCH</t>
+          <t>UGARSUGAR</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1755,18 +1755,18 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>GENUSPOWER</t>
+          <t>VIDHIING</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Buyback</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1775,18 +1775,18 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DHANBANK</t>
+          <t>VINEETLAB</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1795,13 +1795,13 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DEEPA</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1815,18 +1815,18 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>SMCGLOBAL</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1835,13 +1835,13 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CYBERMEDIA</t>
+          <t>LEAPIND</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1855,18 +1855,18 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ASTEC</t>
+          <t>GENUSPOWER</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Buyback</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1875,18 +1875,18 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AAVAS</t>
+          <t>JBMA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1895,18 +1895,18 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ITCHOTELS</t>
+          <t>AAVAS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1915,93 +1915,93 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>ACEVECTOR</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>NIITLTD</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ODIGMA</t>
+          <t>ASTEC</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>CYBERMEDIA</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STARHEALTH</t>
+          <t>DEEPA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2031,77 +2031,77 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STERTOOLS</t>
+          <t>DHANBANK</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>ISHANCH</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>LTFOODS</t>
+          <t>ITCHOTELS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2111,37 +2111,37 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TBZ</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>JSWCEMENT</t>
+          <t>RAYMOND</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CENTENKA</t>
+          <t>ONESOURCE</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2175,18 +2175,18 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2195,18 +2195,18 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>GANDHAR</t>
+          <t>QUICKHEAL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2215,18 +2215,18 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>GULFPETRO</t>
+          <t>RAYMONDREL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2235,18 +2235,18 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>KNACK</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2255,18 +2255,18 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>HUHTAMAKI</t>
+          <t>SIYSIL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2275,13 +2275,13 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>INDOCO</t>
+          <t>STARHEALTH</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2295,13 +2295,13 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>IRISDOREME</t>
+          <t>STERTOOLS</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2315,18 +2315,18 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>HOMEFIRST</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2335,33 +2335,33 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ZENSARTECH</t>
+          <t>NIITLTD</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>VSTIND</t>
+          <t>TBZ</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2371,77 +2371,77 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SMARTLINK</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>NITYAS</t>
+          <t>ODIGMA</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MEESHO</t>
+          <t>LTFOODS</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2451,37 +2451,37 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>BHARATSE</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>KAMDHENU</t>
+          <t>CENTENKA</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2511,77 +2511,77 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>TCIFINANCE</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>INFOBEAN</t>
+          <t>GULFPETRO</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>JETFREIGHT</t>
+          <t>HOMEFIRST</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2591,17 +2591,17 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>INDOCO</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2611,17 +2611,17 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>INFOMEDIA</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2631,37 +2631,37 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>IRISDOREME</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>JSWCEMENT</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2671,57 +2671,57 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ATLASCYCLE</t>
+          <t>KHANDSE</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>KNACK</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>HUHTAMAKI</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2731,22 +2731,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>SASKEN</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2755,13 +2755,13 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SURYODAY</t>
+          <t>NKIND</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2771,57 +2771,57 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STEAMHOUSE</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SANOFI</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>PINELABS</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2831,37 +2831,37 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>NOCIL</t>
+          <t>SADHNANIQ</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2871,57 +2871,57 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>SEITINVIT</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>KREBSBIO</t>
+          <t>VSTIND</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>INDSWFTLAB</t>
+          <t>STYLAMIND</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2931,97 +2931,97 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>INDGN</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GREENPLY</t>
+          <t>SUNDRMFAST</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CARERATING</t>
+          <t>TCIFINANCE</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CAPITALSFB</t>
+          <t>ZENSARTECH</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3031,57 +3031,57 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>NITYAS</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>SMARTLINK</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>FSL</t>
+          <t>MEESHO</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3091,17 +3091,17 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3111,17 +3111,17 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>GMDCLTD</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3131,17 +3131,17 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3151,37 +3151,37 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>ADROITIND</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>BESTAGRO</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3191,37 +3191,37 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ANDHRAPAP</t>
+          <t>AGI</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>ANANTRAJ</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3231,17 +3231,17 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>ATLASCYCLE</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3251,37 +3251,37 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BHARATGEAR</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3291,17 +3291,17 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MERCURYEV</t>
+          <t>CONTROLPR</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3311,37 +3311,37 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>LATENTVIEW</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>IITL</t>
+          <t>GATEWAY</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>NITINSPIN</t>
+          <t>INFOBEAN</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>JAGSNPHARM</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3391,17 +3391,17 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>JETFREIGHT</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3411,17 +3411,17 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ATULAUTO</t>
+          <t>KAMDHENU</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3431,57 +3431,57 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>DLINKINDIA</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>NOCIL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>NELCAST</t>
+          <t>OMAXAUTO</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3491,77 +3491,77 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SHK</t>
+          <t>PINELABS</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>PRAJIND</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>TVTODAY</t>
+          <t>RAMRAT</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3571,17 +3571,17 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>STEAMHOUSE</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -3591,57 +3591,57 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SUBEXLTD</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>RML</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>NEPHROPLUS</t>
+          <t>SURYODAY</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -3651,97 +3651,97 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>RBZJEWEL</t>
+          <t>TIPSFILMS</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>GSPLTRANS</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>SANOFI</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>FINOPB</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3751,17 +3751,17 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>INDSWFTLAB</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3771,37 +3771,37 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>STOVEKRAFT</t>
+          <t>3IINFOLTD</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -3811,37 +3811,37 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>MINDTECK</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>CAPITALSFB</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3851,77 +3851,77 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>KREBSBIO</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>DWARKESH</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>JASH</t>
+          <t>CARERATING</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>FSL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -3931,37 +3931,37 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>GREENPLY</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>ICRA</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -3971,37 +3971,37 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>LCL</t>
+          <t>INDGN</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>AMAGI</t>
+          <t>EMMBI</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4011,17 +4011,17 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4031,37 +4031,37 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ORIENTPPR</t>
+          <t>KAMOPAINTS</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>PRAXIS</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4071,17 +4071,17 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>TEAMLEASE</t>
+          <t>GMDCLTD</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4091,37 +4091,37 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>UGROCAP</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>TTKPRESTIG</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4131,17 +4131,17 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>COFFEEDAY</t>
+          <t>BESTAGRO</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4151,17 +4151,17 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>FOSECOIND</t>
+          <t>ANDHRAPAP</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4171,17 +4171,17 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4191,30 +4191,1170 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>BHARATGEAR</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>UTTAMSUGAR</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>MERCURYEV</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>LATENTVIEW</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>IITL</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>NITINSPIN</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>CLEAN</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>ATULAUTO</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>DLINKINDIA</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>ARE&amp;M</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>NELCAST</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>PTC</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>SHK</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>THOMASCOOK</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>TVTODAY</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>ZUARI</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>RBZJEWEL</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>SUBEXLTD</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>RML</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>NEPHROPLUS</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>ZYDUSWELL</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>GSPLTRANS</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>EMCURE</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>ASKAUTOLTD</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>ALLCARGO</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>LUXIND</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>UNICHEMLAB</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>STOVEKRAFT</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>RITES</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>PRICOLLTD</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>PANAMAPET</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>MINDTECK</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>MARKSANS</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>SAREGAMA</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>LCL</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>JASH</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>EXCELINDUS</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>EMUDHRA</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>ELLEN</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>LENSKART</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>UGROCAP</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>TEAMLEASE</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>PRAXIS</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>ORIENTPPR</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>BIRLACABLE</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>AMAGI</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>IRIS</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>COFFEEDAY</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>FOSECOIND</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>RAIN</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>TTKPRESTIG</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>GOLDIAM</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
           <t>RANEHOLDIN</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
         <is>
           <t>2026-11-12</t>
         </is>
       </c>
-      <c r="D190" t="n">
+      <c r="D245" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>JAICORPLTD</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>MTNL</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
         <v>23</v>
       </c>
     </row>

--- a/data/upcoming_events.xlsx
+++ b/data/upcoming_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D247"/>
+  <dimension ref="A1:D230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BANSALWIRE</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,17 +451,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ZEELEARN</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -471,37 +471,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VGL</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SWIGGY</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -511,57 +511,57 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SURYODAY</t>
+          <t>SSWL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SAPPHIRE</t>
+          <t>SKMEGGPROD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RALLIS</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -571,17 +571,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PAISALO</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -591,17 +591,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TINNARUBR</t>
+          <t>SAKAR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -611,182 +611,182 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NEUEON</t>
+          <t>RUNWALENTR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>INDOTHAI</t>
+          <t>REPRO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FAIRCHEMOR</t>
+          <t>RAMCOSYS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CYIENT</t>
+          <t>PONNIERODE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CREDITACC</t>
+          <t>PANACHE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BONLON</t>
+          <t>UNIECOM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BLUESTONE</t>
+          <t>NEWGEN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NUVOCO</t>
+          <t>ASMS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RAMCOSYS</t>
+          <t>CUBEXTUB</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>REPRO</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -821,12 +821,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SAKAR</t>
+          <t>GRADIENTE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -841,7 +841,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -861,7 +861,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>GNA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -881,12 +881,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>KSOLVES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -901,12 +901,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SSWL</t>
+          <t>KSOLVES</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -921,12 +921,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>MAHLOG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -941,7 +941,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>UNIECOM</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -981,7 +981,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PONNIERODE</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1001,47 +1001,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SKMEGGPROD</t>
+          <t>MODIS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PANACHE</t>
+          <t>TIJARIA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RUNWALENTR</t>
+          <t>SESHAPAPER</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NEWGEN</t>
+          <t>RAJOOENG</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1071,77 +1071,77 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ASMS</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CUBEXTUB</t>
+          <t>CHEMCON</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>BHARATCOAL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GRADIENTE</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1171,17 +1171,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1191,17 +1191,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GNA</t>
+          <t>GERMAN</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1211,37 +1211,37 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KSOLVES</t>
+          <t>RAILTEL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Dividend</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KSOLVES</t>
+          <t>NDTV</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1251,37 +1251,37 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MAHLOG</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>PNGSREVA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>RIR</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1311,17 +1311,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>SHANTIGEAR</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1331,57 +1331,57 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MODIS</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TIJARIA</t>
+          <t>SRIT</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SESHAPAPER</t>
+          <t>UGARSUGAR</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RAJOOENG</t>
+          <t>VIDHIING</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1411,17 +1411,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>VINEETLAB</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1431,57 +1431,57 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CHEMCON</t>
+          <t>SMCGLOBAL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BHARATCOAL</t>
+          <t>LEAPIND</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1491,37 +1491,37 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>NDTV</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>JBMA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1531,17 +1531,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GERMAN</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1551,37 +1551,37 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>RAILTEL</t>
+          <t>ACEVECTOR</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1601,12 +1601,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>ASTEC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1641,7 +1641,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PNGSREVA</t>
+          <t>CYBERMEDIA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1661,12 +1661,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>RIR</t>
+          <t>AAVAS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SHANTIGEAR</t>
+          <t>DEEPA</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1701,12 +1701,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>DHANBANK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1721,12 +1721,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SRIT</t>
+          <t>GENUSPOWER</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Buyback</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1741,7 +1741,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>UGARSUGAR</t>
+          <t>ISHANCH</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>VIDHIING</t>
+          <t>ITCHOTELS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1781,12 +1781,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>VINEETLAB</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1801,27 +1801,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>ODIGMA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SMCGLOBAL</t>
+          <t>ONESOURCE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1831,57 +1831,57 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>LEAPIND</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GENUSPOWER</t>
+          <t>QUICKHEAL</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Buyback</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>JBMA</t>
+          <t>RAYMOND</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1891,37 +1891,37 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AAVAS</t>
+          <t>RAYMONDREL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ACEVECTOR</t>
+          <t>STARHEALTH</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1931,57 +1931,57 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>SIYSIL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ASTEC</t>
+          <t>STERTOOLS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CYBERMEDIA</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1991,37 +1991,37 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DEEPA</t>
+          <t>TBZ</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2031,77 +2031,77 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DHANBANK</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ISHANCH</t>
+          <t>NIITLTD</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ITCHOTELS</t>
+          <t>LTFOODS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2111,37 +2111,37 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>RAYMOND</t>
+          <t>BHARATSE</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ONESOURCE</t>
+          <t>CENTENKA</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2201,12 +2201,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>QUICKHEAL</t>
+          <t>GULFPETRO</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2221,12 +2221,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>RAYMONDREL</t>
+          <t>HOMEFIRST</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2241,12 +2241,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SIYSIL</t>
+          <t>INDOCO</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2281,7 +2281,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STARHEALTH</t>
+          <t>INFOMEDIA</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2301,7 +2301,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STERTOOLS</t>
+          <t>IRISDOREME</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2321,7 +2321,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>JSWCEMENT</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>NIITLTD</t>
+          <t>KHANDSE</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2361,12 +2361,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>TBZ</t>
+          <t>KNACK</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2381,12 +2381,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>HUHTAMAKI</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2401,107 +2401,107 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>SASKEN</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ODIGMA</t>
+          <t>NKIND</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>LTFOODS</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BHARATSE</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CENTENKA</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2511,37 +2511,37 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>GANDHAR</t>
+          <t>SADHNANIQ</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>GULFPETRO</t>
+          <t>SEITINVIT</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2551,37 +2551,37 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>HOMEFIRST</t>
+          <t>VSTIND</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>STYLAMIND</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2591,17 +2591,17 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>INDOCO</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2611,57 +2611,57 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>INFOMEDIA</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>IRISDOREME</t>
+          <t>SUNDRMFAST</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>JSWCEMENT</t>
+          <t>TCIFINANCE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2671,57 +2671,57 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>KHANDSE</t>
+          <t>ZENSARTECH</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>KNACK</t>
+          <t>NITYAS</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>HUHTAMAKI</t>
+          <t>SMARTLINK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2731,22 +2731,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SASKEN</t>
+          <t>MEESHO</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2761,7 +2761,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>NKIND</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2781,12 +2781,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -2801,7 +2801,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2821,12 +2821,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -2841,7 +2841,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2861,12 +2861,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SADHNANIQ</t>
+          <t>AGI</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -2881,12 +2881,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SEITINVIT</t>
+          <t>ANANTRAJ</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -2901,7 +2901,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>VSTIND</t>
+          <t>ATLASCYCLE</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2921,7 +2921,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STYLAMIND</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2941,12 +2941,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>ADROITIND</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -2961,12 +2961,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>CONTROLPR</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -2981,12 +2981,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SUNDRMFAST</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3001,7 +3001,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>TCIFINANCE</t>
+          <t>GATEWAY</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3021,7 +3021,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ZENSARTECH</t>
+          <t>INFOBEAN</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3041,7 +3041,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>NITYAS</t>
+          <t>JAGSNPHARM</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3061,7 +3061,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SMARTLINK</t>
+          <t>JETFREIGHT</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3081,7 +3081,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MEESHO</t>
+          <t>KAMDHENU</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3101,7 +3101,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>NOCIL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3131,17 +3131,17 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>OMAXAUTO</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3151,17 +3151,17 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ADROITIND</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3171,117 +3171,117 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>PINELABS</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>AGI</t>
+          <t>PRAJIND</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ATLASCYCLE</t>
+          <t>SANOFI</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>STEAMHOUSE</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3291,17 +3291,17 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CONTROLPR</t>
+          <t>SURYODAY</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3311,37 +3311,37 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>GATEWAY</t>
+          <t>RAMRAT</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>INFOBEAN</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>JAGSNPHARM</t>
+          <t>FINOPB</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3391,17 +3391,17 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>JETFREIGHT</t>
+          <t>INDSWFTLAB</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3411,37 +3411,37 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>KAMDHENU</t>
+          <t>INDGN</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>ICRA</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3451,17 +3451,17 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>NOCIL</t>
+          <t>GREENPLY</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3481,7 +3481,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>OMAXAUTO</t>
+          <t>FSL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3501,12 +3501,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>EMMBI</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3521,12 +3521,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>PINELABS</t>
+          <t>TIPSFILMS</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3541,12 +3541,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>PRAJIND</t>
+          <t>CARERATING</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3561,7 +3561,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>RAMRAT</t>
+          <t>CAPITALSFB</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3581,12 +3581,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>STEAMHOUSE</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3601,12 +3601,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3621,12 +3621,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>3IINFOLTD</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3641,12 +3641,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SURYODAY</t>
+          <t>KREBSBIO</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3661,7 +3661,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>TIPSFILMS</t>
+          <t>DWARKESH</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -3681,47 +3681,47 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>GMDCLTD</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SANOFI</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3731,17 +3731,17 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>FINOPB</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3751,17 +3751,17 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>INDSWFTLAB</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3771,37 +3771,37 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>KAMOPAINTS</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>BESTAGRO</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -3811,37 +3811,37 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>ANDHRAPAP</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>CAPITALSFB</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3851,37 +3851,37 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>KREBSBIO</t>
+          <t>BHARATGEAR</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>DWARKESH</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -3891,37 +3891,37 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>CARERATING</t>
+          <t>UTTAMSUGAR</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>FSL</t>
+          <t>MERCURYEV</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -3931,17 +3931,17 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>GREENPLY</t>
+          <t>LATENTVIEW</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -3951,17 +3951,17 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>IITL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -3971,37 +3971,37 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>INDGN</t>
+          <t>NITINSPIN</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>EMMBI</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4011,17 +4011,17 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4031,17 +4031,17 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>KAMOPAINTS</t>
+          <t>ATULAUTO</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4051,57 +4051,57 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>DLINKINDIA</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>GMDCLTD</t>
+          <t>ARE&amp;M</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>NELCAST</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4111,17 +4111,17 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4131,17 +4131,17 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>BESTAGRO</t>
+          <t>SHK</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4151,37 +4151,37 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ANDHRAPAP</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>TVTODAY</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4191,17 +4191,17 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>ZUARI</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4211,37 +4211,37 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>BHARATGEAR</t>
+          <t>RBZJEWEL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR</t>
+          <t>ZYDUSWELL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4251,17 +4251,17 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>MERCURYEV</t>
+          <t>RML</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>LATENTVIEW</t>
+          <t>NEPHROPLUS</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>IITL</t>
+          <t>SUBEXLTD</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4311,17 +4311,17 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>NITINSPIN</t>
+          <t>GSPLTRANS</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4331,17 +4331,17 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>EMCURE</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4351,37 +4351,37 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ATULAUTO</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4391,57 +4391,57 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>DLINKINDIA</t>
+          <t>LUXIND</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>UNICHEMLAB</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>NELCAST</t>
+          <t>STOVEKRAFT</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4451,17 +4451,17 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4471,17 +4471,17 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SHK</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4491,57 +4491,57 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>PANAMAPET</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>TVTODAY</t>
+          <t>MINDTECK</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ZUARI</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4551,37 +4551,37 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>RBZJEWEL</t>
+          <t>RITES</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SUBEXLTD</t>
+          <t>LCL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4591,17 +4591,17 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>RML</t>
+          <t>JASH</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -4611,17 +4611,17 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>NEPHROPLUS</t>
+          <t>EXCELINDUS</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -4631,17 +4631,17 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>EMUDHRA</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -4651,37 +4651,37 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>GSPLTRANS</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -4691,57 +4691,57 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>LENSKART</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>UGROCAP</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>TEAMLEASE</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -4751,17 +4751,17 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>UNICHEMLAB</t>
+          <t>PRAXIS</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -4771,17 +4771,17 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>STOVEKRAFT</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -4791,37 +4791,37 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>BIRLACABLE</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>AMAGI</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -4831,57 +4831,57 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>PANAMAPET</t>
+          <t>ORIENTPPR</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>MINDTECK</t>
+          <t>COFFEEDAY</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>FOSECOIND</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -4891,17 +4891,17 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -4911,17 +4911,17 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>LCL</t>
+          <t>TTKPRESTIG</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -4931,37 +4931,37 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>JASH</t>
+          <t>GOLDIAM</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>EXCELINDUS</t>
+          <t>RANEHOLDIN</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -4971,390 +4971,50 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>JAICORPLTD</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>MTNL</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>BSE</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="D231" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>LENSKART</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="D232" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>UGROCAP</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Financial Results/Other business matters</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="D233" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>TEAMLEASE</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="D234" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>PRAXIS</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="D235" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>ORIENTPPR</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Financial Results/Other business matters</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="D236" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>BIRLACABLE</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="D237" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>AMAGI</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="D238" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>IRIS</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="D239" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>COFFEEDAY</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="D240" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>FOSECOIND</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="D241" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>RAIN</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="D242" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>TTKPRESTIG</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="D243" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>GOLDIAM</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Financial Results/Dividend</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>2026-11-07</t>
-        </is>
-      </c>
-      <c r="D244" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>RANEHOLDIN</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="D245" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>JAICORPLTD</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Financial Results/Other business matters</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="D246" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>MTNL</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="D247" t="n">
         <v>23</v>
       </c>
     </row>

--- a/data/upcoming_events.xlsx
+++ b/data/upcoming_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D230"/>
+  <dimension ref="A1:D284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GRADIENTE</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>GRADIENTE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -875,18 +875,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KSOLVES</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -906,7 +906,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -915,18 +915,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MAHLOG</t>
+          <t>KSOLVES</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -935,18 +935,18 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>MAHLOG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -955,13 +955,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -995,18 +995,18 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MODIS</t>
+          <t>TIJARIA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1015,18 +1015,18 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TIJARIA</t>
+          <t>SESHAPAPER</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1035,13 +1035,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SESHAPAPER</t>
+          <t>RAJOOENG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1055,18 +1055,18 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>RAJOOENG</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1075,18 +1075,18 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1095,18 +1095,18 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>MODIS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -1215,18 +1215,18 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>RAILTEL</t>
+          <t>BHARATCOAL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1235,33 +1235,33 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>RAILTEL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>NDTV</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1275,18 +1275,18 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PNGSREVA</t>
+          <t>NDTV</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>RIR</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1315,13 +1315,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SHANTIGEAR</t>
+          <t>PNGSREVA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1335,18 +1335,18 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>RIR</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1355,18 +1355,18 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SRIT</t>
+          <t>UGARSUGAR</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>UGARSUGAR</t>
+          <t>SMCGLOBAL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1395,18 +1395,18 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>VIDHIING</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1415,18 +1415,18 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>VINEETLAB</t>
+          <t>VIDHIING</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1435,18 +1435,18 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>VINEETLAB</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1455,13 +1455,13 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SMCGLOBAL</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LEAPIND</t>
+          <t>SHANTIGEAR</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1495,18 +1495,18 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>LEAPIND</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1515,18 +1515,18 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>JBMA</t>
+          <t>SRIT</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1535,13 +1535,13 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>JBMA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1555,13 +1555,13 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ACEVECTOR</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1575,18 +1575,18 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>AAVAS</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1595,13 +1595,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ASTEC</t>
+          <t>ACEVECTOR</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1635,13 +1635,13 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CYBERMEDIA</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1655,18 +1655,18 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AAVAS</t>
+          <t>CYBERMEDIA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1675,13 +1675,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DEEPA</t>
+          <t>ASTEC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1695,13 +1695,13 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DHANBANK</t>
+          <t>DEEPA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1715,18 +1715,18 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>GENUSPOWER</t>
+          <t>DHANBANK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Buyback</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1735,18 +1735,18 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ISHANCH</t>
+          <t>GENUSPOWER</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Buyback</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1755,13 +1755,13 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ITCHOTELS</t>
+          <t>ISHANCH</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1775,18 +1775,18 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>ITCHOTELS</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1795,38 +1795,38 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ODIGMA</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ONESOURCE</t>
+          <t>ODIGMA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1835,18 +1835,18 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>RAYMONDREL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1855,13 +1855,13 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>QUICKHEAL</t>
+          <t>ONESOURCE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1875,18 +1875,18 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>RAYMOND</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1895,13 +1895,13 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>RAYMONDREL</t>
+          <t>QUICKHEAL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STARHEALTH</t>
+          <t>RAYMOND</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1935,18 +1935,18 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SIYSIL</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1955,18 +1955,18 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STERTOOLS</t>
+          <t>TBZ</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1975,18 +1975,18 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1995,18 +1995,18 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>STARHEALTH</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2015,18 +2015,18 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TBZ</t>
+          <t>STERTOOLS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2035,18 +2035,18 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2055,13 +2055,13 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>LTFOODS</t>
+          <t>VISL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2115,18 +2115,18 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>WAAREEENER</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2135,18 +2135,18 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BHARATSE</t>
+          <t>SIYSIL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CENTENKA</t>
+          <t>MOREPENLAB</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2175,13 +2175,13 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>GANDHAR</t>
+          <t>OMAXE</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2195,18 +2195,18 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>GULFPETRO</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2215,18 +2215,18 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>HOMEFIRST</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2235,18 +2235,18 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2255,13 +2255,13 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>INDOCO</t>
+          <t>BHARATSE</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2275,13 +2275,13 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>INFOMEDIA</t>
+          <t>CENTENKA</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2295,18 +2295,18 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>IRISDOREME</t>
+          <t>CONCORDBIO</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>JSWCEMENT</t>
+          <t>DYCL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2335,13 +2335,13 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>KHANDSE</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2355,13 +2355,13 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>KNACK</t>
+          <t>GULFPETRO</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>HUHTAMAKI</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2395,33 +2395,33 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SASKEN</t>
+          <t>HUHTAMAKI</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>NKIND</t>
+          <t>INDOCO</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2431,117 +2431,117 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>INFOMEDIA</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>IRISDOREME</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>JSWCEMENT</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>KHANDSE</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SADHNANIQ</t>
+          <t>KNACK</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SEITINVIT</t>
+          <t>HOMEFIRST</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>VSTIND</t>
+          <t>LTFOODS</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2571,22 +2571,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STYLAMIND</t>
+          <t>SASKEN</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2595,13 +2595,13 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>SADHNANIQ</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2615,18 +2615,18 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2635,18 +2635,18 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SUNDRMFAST</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2655,18 +2655,18 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>TCIFINANCE</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2675,13 +2675,13 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ZENSARTECH</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2695,13 +2695,13 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>NITYAS</t>
+          <t>NKIND</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2715,13 +2715,13 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SMARTLINK</t>
+          <t>SATIN</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2735,18 +2735,18 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MEESHO</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2755,18 +2755,18 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>SEITINVIT</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -2775,18 +2775,18 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>ZENSARTECH</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -2795,13 +2795,13 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>STYLAMIND</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2815,13 +2815,13 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2835,18 +2835,18 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -2855,18 +2855,18 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AGI</t>
+          <t>SUNDRMFAST</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -2875,13 +2875,13 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>TCIFINANCE</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2895,13 +2895,13 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ATLASCYCLE</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2915,13 +2915,13 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>VSTIND</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2935,13 +2935,13 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ADROITIND</t>
+          <t>ZOTA</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2955,13 +2955,13 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CONTROLPR</t>
+          <t>NITYAS</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2975,18 +2975,18 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>SMARTLINK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -2995,13 +2995,13 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>GATEWAY</t>
+          <t>MEESHO</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3015,13 +3015,13 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>INFOBEAN</t>
+          <t>SHALPAINTS</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3035,13 +3035,13 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>JAGSNPHARM</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3055,18 +3055,18 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>JETFREIGHT</t>
+          <t>20MICRONS</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3075,13 +3075,13 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>KAMDHENU</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3095,18 +3095,18 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>ADROITIND</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3115,13 +3115,13 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>NOCIL</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3131,77 +3131,77 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>OMAXAUTO</t>
+          <t>AGI</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>ANANTRAJ</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PINELABS</t>
+          <t>ATLASCYCLE</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PRAJIND</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3211,37 +3211,37 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SANOFI</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3251,37 +3251,37 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STEAMHOUSE</t>
+          <t>CONTROLPR</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3291,17 +3291,17 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SURYODAY</t>
+          <t>CARTRADE</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3311,37 +3311,37 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>KAMDHENU</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>RAMRAT</t>
+          <t>JAGSNPHARM</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>INFOBEAN</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>FINOPB</t>
+          <t>JETFREIGHT</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3391,97 +3391,97 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>INDSWFTLAB</t>
+          <t>GOKULAGRO</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>INDGN</t>
+          <t>GATEWAY</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>GREENPLY</t>
+          <t>GOODLUCK</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>FSL</t>
+          <t>NILKAMAL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3495,13 +3495,13 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>EMMBI</t>
+          <t>RAMRAT</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>TIPSFILMS</t>
+          <t>NOCIL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3535,18 +3535,18 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CARERATING</t>
+          <t>OMAXAUTO</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3555,18 +3555,18 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CAPITALSFB</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3575,18 +3575,18 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>PINELABS</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3595,13 +3595,13 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>PRAJIND</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3615,18 +3615,18 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>RPGLIFE</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3635,18 +3635,18 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>KREBSBIO</t>
+          <t>SURYODAY</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3655,18 +3655,18 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>DWARKESH</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3675,33 +3675,33 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>GMDCLTD</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>STEAMHOUSE</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -3711,17 +3711,17 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3731,17 +3731,17 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>TIPSFILMS</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3751,17 +3751,17 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>WHEELS</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3771,17 +3771,17 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>KAMOPAINTS</t>
+          <t>MILKYMIST</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -3791,37 +3791,37 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>BESTAGRO</t>
+          <t>SANOFI</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ANDHRAPAP</t>
+          <t>LINCOLN</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -3831,17 +3831,17 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3851,17 +3851,17 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>BHARATGEAR</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3871,77 +3871,77 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR</t>
+          <t>3IINFOLTD</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>MERCURYEV</t>
+          <t>BLISSGVS</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>LATENTVIEW</t>
+          <t>BOROLTD</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -3951,57 +3951,57 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>IITL</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>NITINSPIN</t>
+          <t>CARERATING</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>DWARKESH</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4011,17 +4011,17 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>EMMBI</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4031,17 +4031,17 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ATULAUTO</t>
+          <t>CAPITALSFB</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4051,57 +4051,57 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>DLINKINDIA</t>
+          <t>FSL</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>GREENPLY</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>NELCAST</t>
+          <t>ICRA</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4111,17 +4111,17 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4131,77 +4131,77 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SHK</t>
+          <t>INDGN</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>INDSWFTLAB</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>TVTODAY</t>
+          <t>KREBSBIO</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ZUARI</t>
+          <t>FINOPB</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4211,37 +4211,37 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>RBZJEWEL</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>LCCPROJECT</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4251,17 +4251,17 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>RML</t>
+          <t>KAMOPAINTS</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>NEPHROPLUS</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SUBEXLTD</t>
+          <t>GMDCLTD</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4311,17 +4311,17 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>GSPLTRANS</t>
+          <t>GLOBALE</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4331,57 +4331,57 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4391,17 +4391,17 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>BHARATGEAR</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4411,17 +4411,17 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>UNICHEMLAB</t>
+          <t>BESTAGRO</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4431,17 +4431,17 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>STOVEKRAFT</t>
+          <t>ANDHRAPAP</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4451,17 +4451,17 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4471,17 +4471,17 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4491,17 +4491,17 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>PANAMAPET</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4511,37 +4511,37 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>MINDTECK</t>
+          <t>UTTAMSUGAR</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>MERCURYEV</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4551,37 +4551,37 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>NITINSPIN</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>LCL</t>
+          <t>MHLXMIRU</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4591,17 +4591,17 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>JASH</t>
+          <t>LATENTVIEW</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -4611,17 +4611,17 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>EXCELINDUS</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -4631,57 +4631,57 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>DLINKINDIA</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>ATULAUTO</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -4691,17 +4691,17 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>IITL</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -4711,37 +4711,37 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>UGROCAP</t>
+          <t>ZUARI</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>TEAMLEASE</t>
+          <t>TVTODAY</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -4751,37 +4751,37 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>PRAXIS</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>BIRLACABLE</t>
+          <t>SHK</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -4811,17 +4811,17 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>AMAGI</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -4831,57 +4831,57 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ORIENTPPR</t>
+          <t>NELCAST</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>COFFEEDAY</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>FOSECOIND</t>
+          <t>IDEAFORGE</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -4891,17 +4891,17 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>HECPROJECT</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -4911,17 +4911,17 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>TTKPRESTIG</t>
+          <t>DIGITIDE</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -4931,91 +4931,1171 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>GOLDIAM</t>
+          <t>BCLIND</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>RANEHOLDIN</t>
+          <t>ARE&amp;M</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>JAICORPLTD</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
+          <t>RBZJEWEL</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>ZYDUSWELL</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>SUBEXLTD</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>SHUKRAPHAR</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>RML</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>NEULANDLAB</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>ASKAUTOLTD</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>LUXIND</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>GSPLTRANS</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>EMCURE</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>ALLCARGO</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>NEPHROPLUS</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>MITTAL</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>UNICHEMLAB</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>STOVEKRAFT</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>SAREGAMA</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>RITES</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>PRICOLLTD</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>PANAMAPET</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>WEBELSOLAR</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>NAVKARURB</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>MINDTECK</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>JASH</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>LENSKART</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>LCL</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>EXCELINDUS</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>ENTERO</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>EMUDHRA</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>ELLEN</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>CERA</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>MARKSANS</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>UGROCAP</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>TEAMLEASE</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>PRAXIS</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>ORIENTPPR</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>IRIS</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>MFML</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>GHCLTEXTIL</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>EXCELSOFT</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>BIRLACABLE</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>AMAGI</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>GOACARBON</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>TTKPRESTIG</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>RAIN</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>KAKATCEM</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>HONASA</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>CORDSCABLE</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>COFFEEDAY</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>FOSECOIND</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D279" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>GOLDIAM</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>RANEHOLDIN</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D282" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>JAICORPLTD</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
           <t>MTNL</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="D230" t="n">
-        <v>23</v>
+      <c r="D284" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/data/upcoming_events.xlsx
+++ b/data/upcoming_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D284"/>
+  <dimension ref="A1:D256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,17 +451,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -471,17 +471,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>BHARATCOAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -491,77 +491,77 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>CHEMCON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SSWL</t>
+          <t>GERMAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SKMEGGPROD</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>MODIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -571,57 +571,57 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SAKAR</t>
+          <t>RAJOOENG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RUNWALENTR</t>
+          <t>SESHAPAPER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -631,57 +631,57 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>REPRO</t>
+          <t>TIJARIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RAMCOSYS</t>
+          <t>RAILTEL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PONNIERODE</t>
+          <t>BHARATCOAL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -691,17 +691,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PANACHE</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -711,37 +711,37 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UNIECOM</t>
+          <t>VINEETLAB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NEWGEN</t>
+          <t>VIDHIING</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,77 +751,77 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ASMS</t>
+          <t>UGARSUGAR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CUBEXTUB</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>SRIT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>SMCGLOBAL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -831,17 +831,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GRADIENTE</t>
+          <t>SHANTIGEAR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -851,17 +851,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GNA</t>
+          <t>RIR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -871,17 +871,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>PNGSREVA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -891,77 +891,77 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>KSOLVES</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>KSOLVES</t>
+          <t>NDTV</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MAHLOG</t>
+          <t>LEAPIND</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>NDTV</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -971,17 +971,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>JBMA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -991,57 +991,57 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TIJARIA</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SESHAPAPER</t>
+          <t>AAVAS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RAJOOENG</t>
+          <t>ACEVECTOR</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1051,57 +1051,57 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MODIS</t>
+          <t>CYBERMEDIA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1111,37 +1111,37 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CHEMCON</t>
+          <t>ASTEC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BHARATCOAL</t>
+          <t>DEEPA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>DHANBANK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1171,37 +1171,37 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>GENUSPOWER</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Buyback</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GERMAN</t>
+          <t>ISHANCH</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1211,17 +1211,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BHARATCOAL</t>
+          <t>ITCHOTELS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1231,37 +1231,37 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>RAILTEL</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>RAYMONDREL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1271,57 +1271,57 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>ODIGMA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>OMAXE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PNGSREVA</t>
+          <t>ONESOURCE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1331,37 +1331,37 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>RIR</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>UGARSUGAR</t>
+          <t>QUICKHEAL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1371,17 +1371,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SMCGLOBAL</t>
+          <t>RAYMOND</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1391,37 +1391,37 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>VIDHIING</t>
+          <t>VISL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1431,57 +1431,57 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>VINEETLAB</t>
+          <t>STARHEALTH</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>STERTOOLS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SHANTIGEAR</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1491,57 +1491,57 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>LEAPIND</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SRIT</t>
+          <t>TBZ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>JBMA</t>
+          <t>WAAREEENER</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1551,57 +1551,57 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>NIITLTD</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AAVAS</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ACEVECTOR</t>
+          <t>MOREPENLAB</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1611,77 +1611,77 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>SIYSIL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CYBERMEDIA</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ASTEC</t>
+          <t>BHARATSE</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1691,17 +1691,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DEEPA</t>
+          <t>CENTENKA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DHANBANK</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1731,37 +1731,37 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>GENUSPOWER</t>
+          <t>CONCORDBIO</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Buyback</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ISHANCH</t>
+          <t>DYCL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1771,62 +1771,62 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ITCHOTELS</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>GULFPETRO</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ODIGMA</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1841,7 +1841,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>RAYMONDREL</t>
+          <t>HUHTAMAKI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1861,7 +1861,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ONESOURCE</t>
+          <t>INDOCO</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>INFOMEDIA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1901,12 +1901,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>QUICKHEAL</t>
+          <t>IRISDOREME</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1921,7 +1921,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>RAYMOND</t>
+          <t>JSWCEMENT</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1941,12 +1941,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>KHANDSE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1961,12 +1961,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TBZ</t>
+          <t>KNACK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1981,12 +1981,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>LTFOODS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2001,12 +2001,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STARHEALTH</t>
+          <t>HOMEFIRST</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2021,7 +2021,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STERTOOLS</t>
+          <t>ZOTA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2031,17 +2031,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>SADHNANIQ</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2051,57 +2051,57 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>NIITLTD</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>VISL</t>
+          <t>NKIND</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2111,17 +2111,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>WAAREEENER</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2131,57 +2131,57 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SIYSIL</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MOREPENLAB</t>
+          <t>SASKEN</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>OMAXE</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2191,77 +2191,77 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>SATIN</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>SHALPAINTS</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BHARATSE</t>
+          <t>SMARTLINK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CENTENKA</t>
+          <t>STYLAMIND</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2291,97 +2291,97 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CONCORDBIO</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DYCL</t>
+          <t>SUNDRMFAST</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GANDHAR</t>
+          <t>TCIFINANCE</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>GULFPETRO</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>NITYAS</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2391,17 +2391,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>HUHTAMAKI</t>
+          <t>ZENSARTECH</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2411,37 +2411,37 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>INDOCO</t>
+          <t>SEITINVIT</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>INFOMEDIA</t>
+          <t>VSTIND</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2451,37 +2451,37 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>IRISDOREME</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>JSWCEMENT</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>KHANDSE</t>
+          <t>20MICRONS</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2511,82 +2511,82 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>KNACK</t>
+          <t>MEESHO</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>HOMEFIRST</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>LTFOODS</t>
+          <t>ADROITIND</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SASKEN</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2601,12 +2601,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SADHNANIQ</t>
+          <t>AGI</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2621,7 +2621,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>REFEX</t>
+          <t>ANANTRAJ</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2641,7 +2641,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>ATLASCYCLE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2661,12 +2661,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2681,7 +2681,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2701,7 +2701,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>NKIND</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2721,7 +2721,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SATIN</t>
+          <t>CONTROLPR</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2741,12 +2741,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>CARTRADE</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2761,12 +2761,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SEITINVIT</t>
+          <t>JETFREIGHT</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -2781,7 +2781,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ZENSARTECH</t>
+          <t>JAGSNPHARM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2801,7 +2801,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STYLAMIND</t>
+          <t>INFOBEAN</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2821,7 +2821,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>KAMDHENU</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2841,7 +2841,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>GOKULAGRO</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2861,12 +2861,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SUNDRMFAST</t>
+          <t>GATEWAY</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -2881,12 +2881,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>TCIFINANCE</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -2901,12 +2901,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>GOODLUCK</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -2921,7 +2921,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>VSTIND</t>
+          <t>RAMRAT</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2931,37 +2931,37 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ZOTA</t>
+          <t>NILKAMAL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>NITYAS</t>
+          <t>NOCIL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SMARTLINK</t>
+          <t>OMAXAUTO</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2991,57 +2991,57 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MEESHO</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SHALPAINTS</t>
+          <t>PINELABS</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>PRAJIND</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3051,37 +3051,37 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>20MICRONS</t>
+          <t>RPGLIFE</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>SURYODAY</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3091,17 +3091,17 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ADROITIND</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3111,57 +3111,57 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AGI</t>
+          <t>STEAMHOUSE</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3171,17 +3171,17 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ATLASCYCLE</t>
+          <t>TIPSFILMS</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3191,17 +3191,17 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>WHEELS</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3211,17 +3211,17 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>MILKYMIST</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3231,17 +3231,17 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>SANOFI</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>LINCOLN</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3271,17 +3271,17 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CONTROLPR</t>
+          <t>BOROLTD</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3291,17 +3291,17 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CARTRADE</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3311,37 +3311,37 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>KAMDHENU</t>
+          <t>3IINFOLTD</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>JAGSNPHARM</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3351,137 +3351,137 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>INFOBEAN</t>
+          <t>BLISSGVS</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>JETFREIGHT</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>GOKULAGRO</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>GATEWAY</t>
+          <t>CARERATING</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>DWARKESH</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>GOODLUCK</t>
+          <t>EMMBI</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>NILKAMAL</t>
+          <t>CAPITALSFB</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3501,7 +3501,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>RAMRAT</t>
+          <t>FSL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3521,7 +3521,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>NOCIL</t>
+          <t>GREENPLY</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3541,7 +3541,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>OMAXAUTO</t>
+          <t>ICRA</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -3561,12 +3561,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3581,7 +3581,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>PINELABS</t>
+          <t>INDGN</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -3601,7 +3601,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>PRAJIND</t>
+          <t>INDSWFTLAB</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3621,12 +3621,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>RPGLIFE</t>
+          <t>KREBSBIO</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3641,7 +3641,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SURYODAY</t>
+          <t>FINOPB</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -3661,47 +3661,47 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>GLOBALE</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>STEAMHOUSE</t>
+          <t>LCCPROJECT</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -3711,17 +3711,17 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>KAMOPAINTS</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3731,17 +3731,17 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>TIPSFILMS</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3751,17 +3751,17 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>WHEELS</t>
+          <t>GMDCLTD</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3771,17 +3771,17 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>MILKYMIST</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -3791,37 +3791,37 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SANOFI</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>LINCOLN</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -3831,17 +3831,17 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>BHARATGEAR</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3851,17 +3851,17 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>BESTAGRO</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3871,137 +3871,137 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>ANDHRAPAP</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>BLISSGVS</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>BOROLTD</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>IITL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CARERATING</t>
+          <t>UTTAMSUGAR</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>DWARKESH</t>
+          <t>NITINSPIN</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4011,17 +4011,17 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>EMMBI</t>
+          <t>MHLXMIRU</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4031,17 +4031,17 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CAPITALSFB</t>
+          <t>MERCURYEV</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4051,17 +4051,17 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>FSL</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4071,37 +4071,37 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>GREENPLY</t>
+          <t>DLINKINDIA</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4111,17 +4111,17 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>ATULAUTO</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4131,37 +4131,37 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>INDGN</t>
+          <t>LATENTVIEW</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>INDSWFTLAB</t>
+          <t>SHK</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4171,37 +4171,37 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>KREBSBIO</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>FINOPB</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>ZUARI</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4231,37 +4231,37 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>LCCPROJECT</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>KAMOPAINTS</t>
+          <t>NELCAST</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>TVTODAY</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4291,37 +4291,37 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>GMDCLTD</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>GLOBALE</t>
+          <t>IDEAFORGE</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4331,37 +4331,37 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>HECPROJECT</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>DIGITIDE</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4371,17 +4371,17 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>BCLIND</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4391,57 +4391,57 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>BHARATGEAR</t>
+          <t>ARE&amp;M</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>BESTAGRO</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ANDHRAPAP</t>
+          <t>ZYDUSWELL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4451,17 +4451,17 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>SUBEXLTD</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4471,17 +4471,17 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>SHUKRAPHAR</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4491,17 +4491,17 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>RML</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4511,37 +4511,37 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR</t>
+          <t>RBZJEWEL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>MERCURYEV</t>
+          <t>NEULANDLAB</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4551,17 +4551,17 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>NITINSPIN</t>
+          <t>LUXIND</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4571,17 +4571,17 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>MHLXMIRU</t>
+          <t>GSPLTRANS</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4591,17 +4591,17 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>LATENTVIEW</t>
+          <t>EMCURE</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -4611,57 +4611,57 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>DLINKINDIA</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>NEPHROPLUS</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -4671,17 +4671,17 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ATULAUTO</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -4691,17 +4691,17 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>IITL</t>
+          <t>UNICHEMLAB</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -4711,17 +4711,17 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ZUARI</t>
+          <t>STOVEKRAFT</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -4731,17 +4731,17 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>TVTODAY</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -4751,37 +4751,37 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>RITES</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>SHK</t>
+          <t>PANAMAPET</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -4811,17 +4811,17 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>NAVKARURB</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -4831,57 +4831,57 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>NELCAST</t>
+          <t>MINDTECK</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>MITTAL</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>IDEAFORGE</t>
+          <t>LENSKART</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -4891,17 +4891,17 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>HECPROJECT</t>
+          <t>LCL</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -4911,17 +4911,17 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>DIGITIDE</t>
+          <t>JASH</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -4931,17 +4931,17 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>BCLIND</t>
+          <t>EXCELINDUS</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -4951,57 +4951,57 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>EMUDHRA</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>RBZJEWEL</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5011,37 +5011,37 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>CERA</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>SUBEXLTD</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5071,37 +5071,37 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>RML</t>
+          <t>UGROCAP</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>NEULANDLAB</t>
+          <t>TEAMLEASE</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5111,57 +5111,57 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>PRAXIS</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>ORIENTPPR</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>GSPLTRANS</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5171,17 +5171,17 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>MFML</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5191,17 +5191,17 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>GHCLTEXTIL</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5211,17 +5211,17 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>NEPHROPLUS</t>
+          <t>EXCELSOFT</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>MITTAL</t>
+          <t>BIRLACABLE</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5251,17 +5251,17 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>UNICHEMLAB</t>
+          <t>AMAGI</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5271,17 +5271,17 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>STOVEKRAFT</t>
+          <t>GOACARBON</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5291,17 +5291,17 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>TTKPRESTIG</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5311,57 +5311,57 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>KAKATCEM</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>PANAMAPET</t>
+          <t>HONASA</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5371,17 +5371,17 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>CORDSCABLE</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5391,17 +5391,17 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>NAVKARURB</t>
+          <t>COFFEEDAY</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5411,57 +5411,57 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>MINDTECK</t>
+          <t>FOSECOIND</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>JASH</t>
+          <t>GOLDIAM</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>KALYANKJIL</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5471,17 +5471,17 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>LCL</t>
+          <t>RANEHOLDIN</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5491,610 +5491,50 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>EXCELINDUS</t>
+          <t>JAICORPLTD</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>MTNL</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>EMUDHRA</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="D257" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>ELLEN</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>Financial Results/Other business matters</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="D258" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>CERA</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Financial Results/Other business matters</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="D259" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>BSE</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="D260" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>MARKSANS</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="D261" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>UGROCAP</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>Financial Results/Other business matters</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="D262" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>TEAMLEASE</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="D263" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>PRAXIS</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="D264" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>ORIENTPPR</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>Financial Results/Other business matters</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="D265" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>IRIS</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="D266" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>MFML</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="D267" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>GHCLTEXTIL</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="D268" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>EXCELSOFT</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="D269" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>BIRLACABLE</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="D270" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>AMAGI</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="D271" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>GOACARBON</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="D272" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>TTKPRESTIG</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="D273" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>RAIN</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="D274" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>KAKATCEM</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>Financial Results/Other business matters</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="D275" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>HONASA</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="D276" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>CORDSCABLE</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="D277" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>COFFEEDAY</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="D278" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>FOSECOIND</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="D279" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>GOLDIAM</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>Financial Results/Dividend</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>2026-11-07</t>
-        </is>
-      </c>
-      <c r="D280" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>KALYANKJIL</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="D281" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>RANEHOLDIN</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="D282" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>JAICORPLTD</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>Financial Results/Other business matters</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="D283" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>MTNL</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="D284" t="n">
         <v>22</v>
       </c>
     </row>

--- a/data/upcoming_events.xlsx
+++ b/data/upcoming_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D256"/>
+  <dimension ref="A1:D305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -1335,7 +1335,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -1415,13 +1415,13 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>VISL</t>
+          <t>TBZ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1435,18 +1435,18 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STARHEALTH</t>
+          <t>SIYSIL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1455,18 +1455,18 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STERTOOLS</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>STARHEALTH</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1495,18 +1495,18 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>STERTOOLS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1515,13 +1515,13 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TBZ</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1535,13 +1535,13 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>WAAREEENER</t>
+          <t>VISL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1555,18 +1555,18 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NIITLTD</t>
+          <t>WAAREEENER</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1575,18 +1575,18 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>NIITLTD</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising/Other business matters</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1595,18 +1595,18 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MOREPENLAB</t>
+          <t>SHAHINVEST</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1615,18 +1615,18 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SIYSIL</t>
+          <t>MOREPENLAB</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1635,18 +1635,18 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1655,18 +1655,18 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1675,18 +1675,18 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BHARATSE</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1695,13 +1695,13 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CENTENKA</t>
+          <t>BHARATSE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>CENTENKA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1735,18 +1735,18 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CONCORDBIO</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1755,13 +1755,13 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DYCL</t>
+          <t>CONCORDBIO</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1775,18 +1775,18 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GANDHAR</t>
+          <t>DYCL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1795,13 +1795,13 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GULFPETRO</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1815,18 +1815,18 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>GULFPETRO</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1835,13 +1835,13 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>HUHTAMAKI</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1855,13 +1855,13 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>INDOCO</t>
+          <t>HUHTAMAKI</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1875,13 +1875,13 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>INFOMEDIA</t>
+          <t>INDOCO</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1895,18 +1895,18 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>IRISDOREME</t>
+          <t>INFOMEDIA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1915,18 +1915,18 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>JSWCEMENT</t>
+          <t>IRISDOREME</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1935,18 +1935,18 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>KHANDSE</t>
+          <t>JSWCEMENT</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1955,13 +1955,13 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>KNACK</t>
+          <t>KHANDSE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1975,18 +1975,18 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>LTFOODS</t>
+          <t>KNACK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1995,18 +1995,18 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HOMEFIRST</t>
+          <t>LTFOODS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2015,13 +2015,13 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ZOTA</t>
+          <t>HOMEFIRST</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2031,22 +2031,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SADHNANIQ</t>
+          <t>SASKEN</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2055,13 +2055,13 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>REFEX</t>
+          <t>SADHNANIQ</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2075,13 +2075,13 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>NKIND</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>ORBTEXP</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2155,18 +2155,18 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SASKEN</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2175,18 +2175,18 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>SATIN</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2195,13 +2195,13 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SATIN</t>
+          <t>PRUDENT</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2215,18 +2215,18 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>SEITINVIT</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2235,13 +2235,13 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SHALPAINTS</t>
+          <t>VSTIND</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
@@ -2295,18 +2295,18 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2315,18 +2315,18 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SUNDRMFAST</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2335,18 +2335,18 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TCIFINANCE</t>
+          <t>SUNDRMFAST</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2355,13 +2355,13 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>TCIFINANCE</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>NITYAS</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2395,13 +2395,13 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ZENSARTECH</t>
+          <t>NKIND</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2415,18 +2415,18 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SEITINVIT</t>
+          <t>WELINV</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2435,13 +2435,13 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>VSTIND</t>
+          <t>ZENSARTECH</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2455,18 +2455,18 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>ZOTA</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>SHALPAINTS</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2495,18 +2495,18 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>20MICRONS</t>
+          <t>NITYAS</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2515,18 +2515,18 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MEESHO</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2535,18 +2535,18 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2555,18 +2555,18 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ADROITIND</t>
+          <t>MEESHO</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2575,18 +2575,18 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>20MICRONS</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2595,18 +2595,18 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AGI</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2615,13 +2615,13 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2635,18 +2635,18 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ATLASCYCLE</t>
+          <t>ADROITIND</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2655,13 +2655,13 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2675,13 +2675,13 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>ANANTRAJ</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2695,13 +2695,13 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>ATLASCYCLE</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2715,13 +2715,13 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CONTROLPR</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2735,13 +2735,13 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CARTRADE</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2755,13 +2755,13 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>JETFREIGHT</t>
+          <t>CARTRADE</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2775,18 +2775,18 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>JAGSNPHARM</t>
+          <t>AGI</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -2795,18 +2795,18 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>INFOBEAN</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -2815,13 +2815,13 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>KAMDHENU</t>
+          <t>CONTROLPR</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2835,18 +2835,18 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>GOKULAGRO</t>
+          <t>KAMDHENU</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -2855,13 +2855,13 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>GATEWAY</t>
+          <t>JETFREIGHT</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2875,18 +2875,18 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>JAGSNPHARM</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -2895,18 +2895,18 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GOODLUCK</t>
+          <t>INFOBEAN</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -2915,13 +2915,13 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RAMRAT</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2931,37 +2931,37 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>NILKAMAL</t>
+          <t>GOKULAGRO</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>NOCIL</t>
+          <t>GATEWAY</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>OMAXAUTO</t>
+          <t>FABTECH</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2991,17 +2991,17 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>GOODLUCK</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3011,22 +3011,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>PINELABS</t>
+          <t>SANOFI</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3035,13 +3035,13 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>PRAJIND</t>
+          <t>NILKAMAL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3055,13 +3055,13 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>RPGLIFE</t>
+          <t>NOCIL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3075,13 +3075,13 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SURYODAY</t>
+          <t>OMAXAUTO</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3095,13 +3095,13 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3115,18 +3115,18 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>PINELABS</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STEAMHOUSE</t>
+          <t>PRAJIND</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3155,13 +3155,13 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>RAMRAT</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3175,13 +3175,13 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>TIPSFILMS</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3195,13 +3195,13 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>WHEELS</t>
+          <t>RPGLIFE</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3215,13 +3215,13 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MILKYMIST</t>
+          <t>SHADOWFAX</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3235,18 +3235,18 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SANOFI</t>
+          <t>MILKYMIST</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3255,13 +3255,13 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>LINCOLN</t>
+          <t>SHYAMTEL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3275,18 +3275,18 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BOROLTD</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3295,13 +3295,13 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3315,18 +3315,18 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>STEAMHOUSE</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3335,13 +3335,13 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>SURYODAY</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3355,18 +3355,18 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BLISSGVS</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3375,18 +3375,18 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>TIPSFILMS</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3395,18 +3395,18 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>TITAGARH</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3415,18 +3415,18 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CARERATING</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3435,13 +3435,13 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>DWARKESH</t>
+          <t>WHEELS</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3455,18 +3455,18 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>EMMBI</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3475,13 +3475,13 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CAPITALSFB</t>
+          <t>LINCOLN</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3495,13 +3495,13 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>FSL</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3515,18 +3515,18 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>GREENPLY</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3535,18 +3535,18 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>3IINFOLTD</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3555,13 +3555,13 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>ARCIL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3575,18 +3575,18 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>INDGN</t>
+          <t>ASMS</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3595,13 +3595,13 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>INDSWFTLAB</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3615,13 +3615,13 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>KREBSBIO</t>
+          <t>BLISSGVS</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3635,18 +3635,18 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>FINOPB</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3655,13 +3655,13 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>GLOBALE</t>
+          <t>CAPITALSFB</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -3671,57 +3671,57 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>CAPITALSFB</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>LCCPROJECT</t>
+          <t>CARERATING</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>KAMOPAINTS</t>
+          <t>DWARKESH</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3731,17 +3731,17 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>BOROLTD</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3751,17 +3751,17 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>GMDCLTD</t>
+          <t>EPACK</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3771,17 +3771,17 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>FINOPB</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -3791,17 +3791,17 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>FSL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -3811,17 +3811,17 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>GREENPLY</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -3831,17 +3831,17 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>BHARATGEAR</t>
+          <t>ICRA</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3851,17 +3851,17 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>BESTAGRO</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3871,37 +3871,37 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ANDHRAPAP</t>
+          <t>INDGN</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>INDSWFTLAB</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -3911,17 +3911,17 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>KALPATARU</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -3931,37 +3931,37 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>KREBSBIO</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>IITL</t>
+          <t>EMMBI</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -3971,17 +3971,17 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR</t>
+          <t>GOCOLORS</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -3991,17 +3991,17 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>NITINSPIN</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4011,17 +4011,17 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>MHLXMIRU</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4031,17 +4031,17 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>MERCURYEV</t>
+          <t>KAMOPAINTS</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4051,17 +4051,17 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>LCCPROJECT</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4071,37 +4071,37 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>DLINKINDIA</t>
+          <t>WELSPUNLIV</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>RESPONIND</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4111,37 +4111,37 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ATULAUTO</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>LATENTVIEW</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4151,17 +4151,17 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SHK</t>
+          <t>GMDCLTD</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4171,37 +4171,37 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>GLOBALE</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ZUARI</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4231,37 +4231,37 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>NELCAST</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>TVTODAY</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4291,37 +4291,37 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>BHARATGEAR</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>IDEAFORGE</t>
+          <t>BESTAGRO</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4331,17 +4331,17 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>HECPROJECT</t>
+          <t>ANDHRAPAP</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4351,37 +4351,37 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>DIGITIDE</t>
+          <t>ALMONDZ</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>BCLIND</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4391,77 +4391,77 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>AFIL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SUBEXLTD</t>
+          <t>UTTAMSUGAR</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4471,17 +4471,17 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR</t>
+          <t>SURAJEST</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4491,17 +4491,17 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>RML</t>
+          <t>NITINSPIN</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4511,37 +4511,37 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>RBZJEWEL</t>
+          <t>MHLXMIRU</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>NEULANDLAB</t>
+          <t>MERCURYEV</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4551,17 +4551,17 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4571,17 +4571,17 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>GSPLTRANS</t>
+          <t>IITL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4591,57 +4591,57 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>DLINKINDIA</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>ATULAUTO</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -4651,17 +4651,17 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>NEPHROPLUS</t>
+          <t>LATENTVIEW</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -4671,17 +4671,17 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>SHK</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -4691,17 +4691,17 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>UNICHEMLAB</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -4711,17 +4711,17 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>STOVEKRAFT</t>
+          <t>PNC</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -4731,17 +4731,17 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>TVTODAY</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -4751,37 +4751,37 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>WALCHANNAG</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>ZUARI</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>PANAMAPET</t>
+          <t>NELCAST</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -4811,17 +4811,17 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>NAVKARURB</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -4831,57 +4831,57 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>MINDTECK</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>MITTAL</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>IDEAFORGE</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -4891,37 +4891,37 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>LCL</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>JASH</t>
+          <t>BCLIND</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -4931,17 +4931,17 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>EXCELINDUS</t>
+          <t>DIGITIDE</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -4951,97 +4951,97 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>ARE&amp;M</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>HAPPSTMNDS</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>HECPROJECT</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>CERA</t>
+          <t>HLEGLAS</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>ZYDUSWELL</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5071,37 +5071,37 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>UGROCAP</t>
+          <t>NEULANDLAB</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>TEAMLEASE</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5111,17 +5111,17 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>PRAXIS</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5131,37 +5131,37 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ORIENTPPR</t>
+          <t>SUBEXLTD</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>SHUKRAPHAR</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5171,17 +5171,17 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>MFML</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5191,17 +5191,17 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>GHCLTEXTIL</t>
+          <t>RML</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5211,17 +5211,17 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>EXCELSOFT</t>
+          <t>NEPHROPLUS</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5231,37 +5231,37 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>BIRLACABLE</t>
+          <t>RBZJEWEL</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>AMAGI</t>
+          <t>LUXIND</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5271,17 +5271,17 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>GOACARBON</t>
+          <t>KOTHARIPET</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5291,17 +5291,17 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>TTKPRESTIG</t>
+          <t>IPL</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5311,17 +5311,17 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>GSPLTRANS</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -5331,37 +5331,37 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>KAKATCEM</t>
+          <t>EMCURE</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>HONASA</t>
+          <t>DALMIASUG</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5371,37 +5371,37 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>CORDSCABLE</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>COFFEEDAY</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5411,17 +5411,17 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>FOSECOIND</t>
+          <t>MASTERTR</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5431,57 +5431,57 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>GOLDIAM</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>MINDTECK</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>RANEHOLDIN</t>
+          <t>MITTAL</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5491,51 +5491,1031 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>JAICORPLTD</t>
+          <t>NAVKARURB</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
+          <t>PANAMAPET</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>STOVEKRAFT</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>RITES</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>SAREGAMA</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>SHUKRAPHAR</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>UNICHEMLAB</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>WEBELSOLAR</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>PRICOLLTD</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>LENSKART</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>JKLAKSHMI</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>JASH</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>CERA</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>ELLEN</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>EMUDHRA</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>CAPACITE</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>EXCELINDUS</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>GKSL</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>GMMPFAUDLR</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>GRSE</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>ENTERO</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>LCL</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>LXCHEM</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>UGROCAP</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D279" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>TEAMLEASE</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>PRAXIS</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>ORIENTPPR</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D282" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>MUTHOOTMF</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>MFML</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D284" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>IRIS</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D285" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>GHCLTEXTIL</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D286" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>EXCELSOFT</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D287" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>BIRLACABLE</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D288" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>AMAGI</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D289" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>AGARWALEYE</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D290" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>GOACARBON</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D291" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>TTKPRESTIG</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D292" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>RAIN</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D293" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>KAKATCEM</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D294" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>FOSECOIND</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D295" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>CORDSCABLE</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D296" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>COFFEEDAY</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D297" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>HONASA</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D298" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>GOLDIAM</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+      <c r="D299" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="D300" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>RANEHOLDIN</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D301" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
           <t>MTNL</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="D256" t="n">
-        <v>22</v>
+      <c r="D302" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>VENKEYS</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D303" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>JAICORPLTD</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D304" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>SANDHAR</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="D305" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/data/upcoming_events.xlsx
+++ b/data/upcoming_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D305"/>
+  <dimension ref="A1:D294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>BHARATCOAL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,77 +451,77 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>RAILTEL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BHARATCOAL</t>
+          <t>VINEETLAB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CHEMCON</t>
+          <t>VIDHIING</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GERMAN</t>
+          <t>UGARSUGAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -531,77 +531,77 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MODIS</t>
+          <t>SRIT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>SHANTIGEAR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RAJOOENG</t>
+          <t>RIR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -611,17 +611,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SESHAPAPER</t>
+          <t>PNGSREVA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -631,57 +631,57 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TIJARIA</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RAILTEL</t>
+          <t>NDTV</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BHARATCOAL</t>
+          <t>NDTV</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -691,11 +691,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -721,12 +721,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VINEETLAB</t>
+          <t>LEAPIND</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -741,7 +741,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>VIDHIING</t>
+          <t>SMCGLOBAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -761,7 +761,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UGARSUGAR</t>
+          <t>JBMA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -781,12 +781,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SRIT</t>
+          <t>AAVAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -821,7 +821,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SMCGLOBAL</t>
+          <t>ACEVECTOR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -841,7 +841,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SHANTIGEAR</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -861,7 +861,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RIR</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -881,7 +881,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PNGSREVA</t>
+          <t>CYBERMEDIA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>ASTEC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -921,12 +921,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>DEEPA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -941,7 +941,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LEAPIND</t>
+          <t>DHANBANK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -961,12 +961,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>GENUSPOWER</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Buyback</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -981,7 +981,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>JBMA</t>
+          <t>ISHANCH</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1001,7 +1001,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>ITCHOTELS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1021,12 +1021,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AAVAS</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1041,47 +1041,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ACEVECTOR</t>
+          <t>OMAXE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>ONESOURCE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1091,37 +1091,37 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CYBERMEDIA</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ASTEC</t>
+          <t>QUICKHEAL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1131,17 +1131,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DEEPA</t>
+          <t>RAYMOND</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DHANBANK</t>
+          <t>RAYMONDREL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1171,37 +1171,37 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GENUSPOWER</t>
+          <t>SHAHINVEST</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Buyback</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ISHANCH</t>
+          <t>TBZ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1211,62 +1211,62 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ITCHOTELS</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>STARHEALTH</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>RAYMONDREL</t>
+          <t>STERTOOLS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1281,12 +1281,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ODIGMA</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1301,12 +1301,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>OMAXE</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1321,7 +1321,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ONESOURCE</t>
+          <t>VISL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1341,12 +1341,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>WAAREEENER</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1361,12 +1361,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>QUICKHEAL</t>
+          <t>ODIGMA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1381,12 +1381,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RAYMOND</t>
+          <t>SIYSIL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1401,12 +1401,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>NIITLTD</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TBZ</t>
+          <t>LTFOODS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SIYSIL</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>MOREPENLAB</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1481,12 +1481,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STARHEALTH</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1501,12 +1501,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STERTOOLS</t>
+          <t>BHARATSE</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1521,7 +1521,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>CENTENKA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1541,7 +1541,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>VISL</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1561,7 +1561,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>WAAREEENER</t>
+          <t>DYCL</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1581,7 +1581,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NIITLTD</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1601,7 +1601,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SHAHINVEST</t>
+          <t>GULFPETRO</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1621,12 +1621,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MOREPENLAB</t>
+          <t>HOMEFIRST</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1641,12 +1641,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>CONCORDBIO</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1661,12 +1661,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>INDOCO</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1681,12 +1681,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>INFOMEDIA</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1701,12 +1701,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BHARATSE</t>
+          <t>IRISDOREME</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1721,7 +1721,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CENTENKA</t>
+          <t>JSWCEMENT</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1741,12 +1741,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>KHANDSE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1761,12 +1761,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CONCORDBIO</t>
+          <t>KNACK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1781,7 +1781,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DYCL</t>
+          <t>HUHTAMAKI</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1801,12 +1801,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GANDHAR</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1821,47 +1821,47 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GULFPETRO</t>
+          <t>SATIN</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>SASKEN</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>HUHTAMAKI</t>
+          <t>SADHNANIQ</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1871,17 +1871,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>INDOCO</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>INFOMEDIA</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>IRISDOREME</t>
+          <t>PRUDENT</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>JSWCEMENT</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1951,37 +1951,37 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>KHANDSE</t>
+          <t>ORBTEXP</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>KNACK</t>
+          <t>SEITINVIT</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>LTFOODS</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2011,42 +2011,42 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HOMEFIRST</t>
+          <t>SHALPAINTS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SASKEN</t>
+          <t>WELINV</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2061,7 +2061,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SADHNANIQ</t>
+          <t>STYLAMIND</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2081,7 +2081,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>REFEX</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2101,12 +2101,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2121,12 +2121,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ORBTEXP</t>
+          <t>SUNDRMFAST</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2141,12 +2141,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>TCIFINANCE</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SATIN</t>
+          <t>VSTIND</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PRUDENT</t>
+          <t>ZENSARTECH</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2221,7 +2221,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SEITINVIT</t>
+          <t>ZOTA</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2241,12 +2241,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>VSTIND</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2281,7 +2281,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STYLAMIND</t>
+          <t>NKIND</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2301,7 +2301,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2321,12 +2321,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>MEESHO</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2341,12 +2341,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SUNDRMFAST</t>
+          <t>NITYAS</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2361,7 +2361,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>TCIFINANCE</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2381,12 +2381,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>ADROITIND</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2401,7 +2401,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>NKIND</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2421,12 +2421,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>WELINV</t>
+          <t>AGI</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2441,7 +2441,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ZENSARTECH</t>
+          <t>ANANTRAJ</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2461,12 +2461,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ZOTA</t>
+          <t>ATLASCYCLE</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2481,7 +2481,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SHALPAINTS</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2501,7 +2501,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>NITYAS</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2521,12 +2521,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>CARTRADE</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2541,12 +2541,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>CONTROLPR</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2561,12 +2561,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MEESHO</t>
+          <t>20MICRONS</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2581,12 +2581,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>20MICRONS</t>
+          <t>FABTECH</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2601,12 +2601,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2621,7 +2621,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2641,12 +2641,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ADROITIND</t>
+          <t>KAMDHENU</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2661,7 +2661,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>JETFREIGHT</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2681,12 +2681,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2701,7 +2701,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ATLASCYCLE</t>
+          <t>INFOBEAN</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2721,12 +2721,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>GOODLUCK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2741,12 +2741,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>GOKULAGRO</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2761,7 +2761,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CARTRADE</t>
+          <t>GATEWAY</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2781,12 +2781,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>AGI</t>
+          <t>JAGSNPHARM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -2801,47 +2801,47 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>NILKAMAL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CONTROLPR</t>
+          <t>SANOFI</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>KAMDHENU</t>
+          <t>NOCIL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2851,57 +2851,57 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>JETFREIGHT</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>JAGSNPHARM</t>
+          <t>PINELABS</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>INFOBEAN</t>
+          <t>PRAJIND</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2911,17 +2911,17 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>RAMRAT</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2931,37 +2931,37 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GOKULAGRO</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>GATEWAY</t>
+          <t>RPGLIFE</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FABTECH</t>
+          <t>SHADOWFAX</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2991,42 +2991,42 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>GOODLUCK</t>
+          <t>SURYODAY</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SANOFI</t>
+          <t>SHYAMTEL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>NILKAMAL</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3061,7 +3061,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>NOCIL</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3081,7 +3081,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>OMAXAUTO</t>
+          <t>STEAMHOUSE</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3101,12 +3101,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3121,12 +3121,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>PINELABS</t>
+          <t>TIPSFILMS</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3141,7 +3141,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>PRAJIND</t>
+          <t>TITAGARH</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3161,7 +3161,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>RAMRAT</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3181,7 +3181,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>WHEELS</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3201,7 +3201,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>RPGLIFE</t>
+          <t>MILKYMIST</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3221,12 +3221,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SHADOWFAX</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3241,7 +3241,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MILKYMIST</t>
+          <t>LINCOLN</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3261,7 +3261,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SHYAMTEL</t>
+          <t>OMAXAUTO</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3281,12 +3281,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3301,12 +3301,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>3IINFOLTD</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3321,7 +3321,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STEAMHOUSE</t>
+          <t>ARCIL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3341,12 +3341,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SURYODAY</t>
+          <t>ASMS</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3361,7 +3361,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3381,12 +3381,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>TIPSFILMS</t>
+          <t>BLISSGVS</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3401,7 +3401,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>TITAGARH</t>
+          <t>BOROLTD</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3421,7 +3421,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>WELCORP</t>
+          <t>CAPITALSFB</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3441,12 +3441,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>WHEELS</t>
+          <t>CAPITALSFB</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3461,12 +3461,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>CARERATING</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3481,7 +3481,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>LINCOLN</t>
+          <t>DWARKESH</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3501,7 +3501,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>EMMBI</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3521,7 +3521,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3541,12 +3541,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>FINOPB</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3561,7 +3561,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ARCIL</t>
+          <t>FSL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3581,12 +3581,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ASMS</t>
+          <t>GREENPLY</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3601,7 +3601,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>ICRA</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3621,12 +3621,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BLISSGVS</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3641,12 +3641,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>INDGN</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3661,12 +3661,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CAPITALSFB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3681,12 +3681,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>CAPITALSFB</t>
+          <t>INDSWFTLAB</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3701,12 +3701,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>CARERATING</t>
+          <t>KALPATARU</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3721,12 +3721,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>DWARKESH</t>
+          <t>KREBSBIO</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3741,7 +3741,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>BOROLTD</t>
+          <t>EPACK</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3761,7 +3761,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>EPACK</t>
+          <t>GOCOLORS</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3771,17 +3771,17 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>FINOPB</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -3791,17 +3791,17 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>FSL</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -3811,17 +3811,17 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>GREENPLY</t>
+          <t>KAMOPAINTS</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -3831,17 +3831,17 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>LCCPROJECT</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3851,17 +3851,17 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>WELSPUNLIV</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3871,57 +3871,57 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>INDGN</t>
+          <t>RESPONIND</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>INDSWFTLAB</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>KALPATARU</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -3931,57 +3931,57 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>KREBSBIO</t>
+          <t>GMDCLTD</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>EMMBI</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>GOCOLORS</t>
+          <t>GLOBALE</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4001,7 +4001,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4021,7 +4021,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4041,7 +4041,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>KAMOPAINTS</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4061,7 +4061,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>LCCPROJECT</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4081,7 +4081,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>WELSPUNLIV</t>
+          <t>BHARATGEAR</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4101,7 +4101,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>RESPONIND</t>
+          <t>BESTAGRO</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4121,12 +4121,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>ANDHRAPAP</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4141,12 +4141,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>ALMONDZ</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4161,7 +4161,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>GMDCLTD</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4181,12 +4181,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>AFIL</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4201,7 +4201,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>GLOBALE</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4241,7 +4241,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>UTTAMSUGAR</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4251,17 +4251,17 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>SURAJEST</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>NITINSPIN</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>BHARATGEAR</t>
+          <t>MHLXMIRU</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4311,17 +4311,17 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>BESTAGRO</t>
+          <t>MERCURYEV</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4331,17 +4331,17 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ANDHRAPAP</t>
+          <t>IITL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ALMONDZ</t>
+          <t>DLINKINDIA</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4371,17 +4371,17 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4391,17 +4391,17 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>AFIL</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4411,17 +4411,17 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>ATULAUTO</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4431,37 +4431,37 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>LATENTVIEW</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR</t>
+          <t>NELCAST</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4471,37 +4471,37 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SURAJEST</t>
+          <t>WALCHANNAG</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>NITINSPIN</t>
+          <t>ZUARI</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4511,37 +4511,37 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>MHLXMIRU</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>MERCURYEV</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4551,17 +4551,17 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>SHK</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4571,17 +4571,17 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>IITL</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4591,57 +4591,57 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>DLINKINDIA</t>
+          <t>PNC</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ATULAUTO</t>
+          <t>TVTODAY</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -4651,17 +4651,17 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>LATENTVIEW</t>
+          <t>IDEAFORGE</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -4671,22 +4671,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>SHK</t>
+          <t>ARE&amp;M</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4701,7 +4701,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>BCLIND</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -4721,7 +4721,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>PNC</t>
+          <t>DIGITIDE</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -4741,12 +4741,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>TVTODAY</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -4761,12 +4761,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>WALCHANNAG</t>
+          <t>HAPPSTMNDS</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -4781,7 +4781,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ZUARI</t>
+          <t>HECPROJECT</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -4801,7 +4801,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>NELCAST</t>
+          <t>HLEGLAS</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -4821,7 +4821,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -4841,47 +4841,47 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ZYDUSWELL</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>IDEAFORGE</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -4891,37 +4891,37 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>SUBEXLTD</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>BCLIND</t>
+          <t>SHUKRAPHAR</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -4931,17 +4931,17 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>DIGITIDE</t>
+          <t>RML</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -4951,57 +4951,57 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>NEULANDLAB</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>HAPPSTMNDS</t>
+          <t>NEPHROPLUS</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>HECPROJECT</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5011,17 +5011,17 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>HLEGLAS</t>
+          <t>LUXIND</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5031,17 +5031,17 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>MASTERTR</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5081,12 +5081,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>NEULANDLAB</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5101,7 +5101,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>VMART</t>
+          <t>DALMIASUG</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5121,12 +5121,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>SUBROS</t>
+          <t>RBZJEWEL</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5141,7 +5141,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>SUBEXLTD</t>
+          <t>GSPLTRANS</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5161,7 +5161,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR</t>
+          <t>IPL</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5181,7 +5181,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>KOTHARIPET</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5201,7 +5201,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>RML</t>
+          <t>EMCURE</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5221,7 +5221,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>NEPHROPLUS</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>RBZJEWEL</t>
+          <t>MINDTECK</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5251,17 +5251,17 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>MITTAL</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5271,17 +5271,17 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>KOTHARIPET</t>
+          <t>NAVKARURB</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5291,17 +5291,17 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>IPL</t>
+          <t>PANAMAPET</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5311,37 +5311,37 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>GSPLTRANS</t>
+          <t>RITES</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -5351,17 +5351,17 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>DALMIASUG</t>
+          <t>SHUKRAPHAR</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5371,37 +5371,37 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>UNICHEMLAB</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5411,17 +5411,17 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>MASTERTR</t>
+          <t>LENSKART</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5431,17 +5431,17 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5461,12 +5461,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>MINDTECK</t>
+          <t>STOVEKRAFT</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -5481,7 +5481,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>MITTAL</t>
+          <t>LCL</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5501,7 +5501,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>NAVKARURB</t>
+          <t>JASH</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -5521,7 +5521,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>PANAMAPET</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -5541,7 +5541,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>STOVEKRAFT</t>
+          <t>CAPACITE</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -5561,12 +5561,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -5581,7 +5581,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>EMUDHRA</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -5601,12 +5601,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR</t>
+          <t>CERA</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -5621,7 +5621,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>UNICHEMLAB</t>
+          <t>EXCELINDUS</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -5641,7 +5641,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>GKSL</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -5661,7 +5661,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -5681,7 +5681,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>GRSE</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -5701,12 +5701,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>JKLAKSHMI</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -5721,7 +5721,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>JASH</t>
+          <t>JKLAKSHMI</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -5741,7 +5741,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>MFML</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -5751,17 +5751,17 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>CERA</t>
+          <t>UGROCAP</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -5771,37 +5771,37 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>TEAMLEASE</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>PRAXIS</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -5811,57 +5811,57 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>CAPACITE</t>
+          <t>ORIENTPPR</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>EXCELINDUS</t>
+          <t>MUTHOOTMF</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>GKSL</t>
+          <t>LXCHEM</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -5871,17 +5871,17 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>GOACARBON</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -5891,17 +5891,17 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>GRSE</t>
+          <t>GHCLTEXTIL</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -5911,37 +5911,37 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>EXCELSOFT</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>LCL</t>
+          <t>BIRLACABLE</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -5951,17 +5951,17 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>AMAGI</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -5981,12 +5981,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>UGROCAP</t>
+          <t>AGARWALEYE</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -6001,7 +6001,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>TEAMLEASE</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -6021,7 +6021,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>PRAXIS</t>
+          <t>TTKPRESTIG</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -6031,37 +6031,37 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>ORIENTPPR</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>MUTHOOTMF</t>
+          <t>KAKATCEM</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -6071,17 +6071,17 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>MFML</t>
+          <t>HONASA</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -6091,17 +6091,17 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>CORDSCABLE</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -6111,17 +6111,17 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>GHCLTEXTIL</t>
+          <t>COFFEEDAY</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -6131,17 +6131,17 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>EXCELSOFT</t>
+          <t>FOSECOIND</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -6151,37 +6151,37 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>BIRLACABLE</t>
+          <t>GOLDIAM</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>AMAGI</t>
+          <t>KALYANKJIL</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -6191,17 +6191,17 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>AGARWALEYE</t>
+          <t>RANEHOLDIN</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -6211,17 +6211,17 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>GOACARBON</t>
+          <t>VENKEYS</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -6231,37 +6231,37 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>TTKPRESTIG</t>
+          <t>JAICORPLTD</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>MTNL</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -6271,250 +6271,30 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>KAKATCEM</t>
+          <t>SANDHAR</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>FOSECOIND</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="D295" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>CORDSCABLE</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="D296" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>COFFEEDAY</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="D297" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>HONASA</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="D298" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>GOLDIAM</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>Financial Results/Dividend</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>2026-11-07</t>
-        </is>
-      </c>
-      <c r="D299" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>KALYANKJIL</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="D300" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>RANEHOLDIN</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="D301" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>MTNL</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="D302" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>VENKEYS</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="D303" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>JAICORPLTD</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>Financial Results/Other business matters</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="D304" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>SANDHAR</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="D305" t="n">
         <v>24</v>
       </c>
     </row>

--- a/data/upcoming_events.xlsx
+++ b/data/upcoming_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D294"/>
+  <dimension ref="A1:D336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,17 +441,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BHARATCOAL</t>
+          <t>20MICRONS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -461,17 +461,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RAILTEL</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -481,27 +481,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VINEETLAB</t>
+          <t>ORBTEXP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VIDHIING</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -511,77 +511,77 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UGARSUGAR</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>PRUDENT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SRIT</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SHANTIGEAR</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -591,17 +591,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RIR</t>
+          <t>SADHNANIQ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -611,37 +611,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PNGSREVA</t>
+          <t>SASKEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>SATIN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -651,37 +651,37 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>SEITINVIT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>NKIND</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -691,17 +691,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>SMARTLINK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LEAPIND</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -731,97 +731,97 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SMCGLOBAL</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JBMA</t>
+          <t>SUNDRMFAST</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>SUNDRMFAST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AAVAS</t>
+          <t>TCIFINANCE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ACEVECTOR</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -831,17 +831,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>VNL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -851,17 +851,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>VSTIND</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -871,17 +871,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CYBERMEDIA</t>
+          <t>WELINV</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -891,17 +891,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ASTEC</t>
+          <t>ZENSARTECH</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -911,37 +911,37 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DEEPA</t>
+          <t>ZOTA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DHANBANK</t>
+          <t>STYLAMIND</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -951,37 +951,37 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GENUSPOWER</t>
+          <t>NITYAS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Buyback</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ISHANCH</t>
+          <t>SHALPAINTS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -991,157 +991,157 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ITCHOTELS</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>MEESHO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>OMAXE</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ONESOURCE</t>
+          <t>ADROITIND</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>QUICKHEAL</t>
+          <t>AGI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RAYMOND</t>
+          <t>ANANTRAJ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RAYMONDREL</t>
+          <t>ATLASCYCLE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1171,37 +1171,37 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SHAHINVEST</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TBZ</t>
+          <t>CARTRADE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1211,37 +1211,37 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>CNL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STARHEALTH</t>
+          <t>CONTROLPR</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STERTOOLS</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>FABTECH</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>VISL</t>
+          <t>KOTYARK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>WAAREEENER</t>
+          <t>KISSHT</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1351,77 +1351,77 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ODIGMA</t>
+          <t>KAMDHENU</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SIYSIL</t>
+          <t>JETFREIGHT</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NIITLTD</t>
+          <t>JAGSNPHARM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LTFOODS</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1431,77 +1431,77 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>GOODLUCK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MOREPENLAB</t>
+          <t>GOKULAGRO</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BHARATSE</t>
+          <t>GATEWAY</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1511,17 +1511,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CENTENKA</t>
+          <t>INFOBEAN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1531,17 +1531,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>SAMBHV</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1551,17 +1551,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DYCL</t>
+          <t>RPGLIFE</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1571,77 +1571,77 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GANDHAR</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GULFPETRO</t>
+          <t>RAMRAT</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>HOMEFIRST</t>
+          <t>PRAJIND</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CONCORDBIO</t>
+          <t>PARADEEP</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1651,17 +1651,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>INDOCO</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1671,57 +1671,57 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>INFOMEDIA</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>IRISDOREME</t>
+          <t>OMAXAUTO</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>JSWCEMENT</t>
+          <t>NOCIL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1731,37 +1731,37 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>KHANDSE</t>
+          <t>SANOFI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>KNACK</t>
+          <t>PINELABS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1771,17 +1771,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HUHTAMAKI</t>
+          <t>SHADOWFAX</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1791,37 +1791,37 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>WHEELS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SATIN</t>
+          <t>SHYAMTEL</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1831,37 +1831,37 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SASKEN</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SADHNANIQ</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1871,17 +1871,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>REFEX</t>
+          <t>STEAMHOUSE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1891,37 +1891,37 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>STLNETWORK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PRUDENT</t>
+          <t>SURYODAY</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1931,37 +1931,37 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>SUVIDHAA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ORBTEXP</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SEITINVIT</t>
+          <t>TIPSFILMS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>TITAGARH</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Board meeting Rescheduled</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SHALPAINTS</t>
+          <t>TITAGARH</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2031,17 +2031,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>WELINV</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2051,17 +2051,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STYLAMIND</t>
+          <t>NILKAMAL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2071,77 +2071,77 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SUNDRMFAST</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TCIFINANCE</t>
+          <t>LINCOLN</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2151,17 +2151,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>MILKYMIST</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2171,117 +2171,117 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>VSTIND</t>
+          <t>3IINFOLTD</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ZENSARTECH</t>
+          <t>AHCL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ZOTA</t>
+          <t>ARCIL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>ASMS</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SMARTLINK</t>
+          <t>BLISSGVS</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>NKIND</t>
+          <t>BOROLTD</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2291,57 +2291,57 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MEESHO</t>
+          <t>CAPITALSFB</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>NITYAS</t>
+          <t>CAPITALSFB</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2351,57 +2351,57 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>CARERATING</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ADROITIND</t>
+          <t>DWARKESH</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>EMMBI</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2411,37 +2411,37 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AGI</t>
+          <t>EPACK</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2451,17 +2451,17 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ATLASCYCLE</t>
+          <t>FSL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2471,17 +2471,17 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>FINOPB</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2491,37 +2491,37 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>KRISHNADEF</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CARTRADE</t>
+          <t>KALPATARU</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2531,97 +2531,97 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CONTROLPR</t>
+          <t>IRBINVIT</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>20MICRONS</t>
+          <t>INDSWFTLAB</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FABTECH</t>
+          <t>KREBSBIO</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>ICRA</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2631,17 +2631,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>KAMDHENU</t>
+          <t>HUBTOWN</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2651,17 +2651,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>JETFREIGHT</t>
+          <t>GREENPLY</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2671,97 +2671,97 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>INDGN</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>INFOBEAN</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>GOODLUCK</t>
+          <t>IRMENERGY</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>GOKULAGRO</t>
+          <t>RESPONIND</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>GATEWAY</t>
+          <t>KAMOPAINTS</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2771,17 +2771,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>JAGSNPHARM</t>
+          <t>LCCPROJECT</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2791,17 +2791,17 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>NILKAMAL</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2811,37 +2811,37 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SANOFI</t>
+          <t>NGIL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>NOCIL</t>
+          <t>PRANAV</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2851,37 +2851,37 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PINELABS</t>
+          <t>TEMPSENS</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2891,37 +2891,37 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>PRAJIND</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RAMRAT</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2931,17 +2931,17 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>RPGLIFE</t>
+          <t>SPANDANA</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SHADOWFAX</t>
+          <t>UDS</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2991,37 +2991,37 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SURYODAY</t>
+          <t>VADILALIND</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SHYAMTEL</t>
+          <t>VIMTALABS</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3031,37 +3031,37 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>WELSPUNLIV</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3071,37 +3071,37 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STEAMHOUSE</t>
+          <t>SHAHALLOYS</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>INDOUS</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3111,17 +3111,17 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>TIPSFILMS</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3131,17 +3131,17 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>TITAGARH</t>
+          <t>GOCOLORS</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3151,17 +3151,17 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>WELCORP</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3171,17 +3171,17 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>WHEELS</t>
+          <t>AFIL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3191,17 +3191,17 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>MILKYMIST</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3211,17 +3211,17 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>ALMONDZ</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3231,17 +3231,17 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>LINCOLN</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3251,37 +3251,37 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>OMAXAUTO</t>
+          <t>ARIHANTCAP</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>ASIANENE</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3291,37 +3291,37 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>BESTAGRO</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ARCIL</t>
+          <t>ANDHRAPAP</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3331,97 +3331,97 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ASMS</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>DIAMONDYD</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BLISSGVS</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BOROLTD</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CAPITALSFB</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3431,57 +3431,57 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CAPITALSFB</t>
+          <t>FINPIPE</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CARERATING</t>
+          <t>GLOBALE</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>DWARKESH</t>
+          <t>GMDCLTD</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3491,17 +3491,17 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>EMMBI</t>
+          <t>BHARATGEAR</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3511,37 +3511,37 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>NILAINFRA</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>FINOPB</t>
+          <t>PACEDIGITK</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -3551,17 +3551,17 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>FSL</t>
+          <t>RAMBHAJO</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3571,17 +3571,17 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>GREENPLY</t>
+          <t>MHLXMIRU</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -3591,17 +3591,17 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>SUMEETINDS</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>SURAJEST</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3631,57 +3631,57 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>INDGN</t>
+          <t>UTTAMSUGAR</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>STUDDS</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>INDSWFTLAB</t>
+          <t>MERCURYEV</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -3691,17 +3691,17 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>KALPATARU</t>
+          <t>NITINSPIN</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -3711,37 +3711,37 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>KREBSBIO</t>
+          <t>LATENTVIEW</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>EPACK</t>
+          <t>ATULAUTO</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3751,17 +3751,17 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>GOCOLORS</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3771,37 +3771,37 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>DLINKINDIA</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>DOLPHIN</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -3811,17 +3811,17 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>KAMOPAINTS</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -3831,17 +3831,17 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>LCCPROJECT</t>
+          <t>MEIL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3851,17 +3851,17 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>WELSPUNLIV</t>
+          <t>GANECOS</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3871,17 +3871,17 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>RESPONIND</t>
+          <t>IITL</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -3891,47 +3891,47 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>EXXARO</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>RSL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -3941,17 +3941,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>GMDCLTD</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -3961,17 +3961,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>PCBL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -3981,7 +3981,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>GLOBALE</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -4001,7 +4001,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>PNC</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -4021,7 +4021,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -4041,7 +4041,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>PURVA</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -4061,7 +4061,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>RUPA</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -4081,7 +4081,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>BHARATGEAR</t>
+          <t>TVTODAY</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -4101,7 +4101,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>BESTAGRO</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -4121,17 +4121,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ANDHRAPAP</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -4141,17 +4141,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ALMONDZ</t>
+          <t>TRIDENT</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -4161,7 +4161,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>NARMADA</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -4181,7 +4181,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>AFIL</t>
+          <t>UFBL</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -4201,17 +4201,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>WALCHANNAG</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -4221,17 +4221,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>XTRANET</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -4241,7 +4241,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR</t>
+          <t>ZUARI</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4251,17 +4251,17 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SURAJEST</t>
+          <t>SHK</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4271,37 +4271,37 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>NITINSPIN</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>MHLXMIRU</t>
+          <t>NELCAST</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4311,17 +4311,17 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>MERCURYEV</t>
+          <t>KRYSTAL</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4331,57 +4331,57 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>IITL</t>
+          <t>AAKASH</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>DLINKINDIA</t>
+          <t>MOBIKWIK</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4391,17 +4391,17 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>BCLIND</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4411,17 +4411,17 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ATULAUTO</t>
+          <t>CAPILLARY</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4431,17 +4431,17 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>LATENTVIEW</t>
+          <t>CSLFINANCE</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4451,22 +4451,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>NELCAST</t>
+          <t>DEVYANI</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4475,18 +4475,18 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>WALCHANNAG</t>
+          <t>DIGITIDE</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4495,13 +4495,13 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ZUARI</t>
+          <t>DOMS</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4515,18 +4515,18 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>ARE&amp;M</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4535,18 +4535,18 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>GANESHCP</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4555,13 +4555,13 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SHK</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4575,18 +4575,18 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>HAPPSTMNDS</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>PNC</t>
+          <t>HECPROJECT</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -4615,18 +4615,18 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>HLEGLAS</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4635,13 +4635,13 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>TVTODAY</t>
+          <t>IDEAFORGE</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -4655,13 +4655,13 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>IDEAFORGE</t>
+          <t>JHS</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -4675,18 +4675,18 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>KANOHAR</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4695,13 +4695,13 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>BCLIND</t>
+          <t>EPACKPEB</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -4715,13 +4715,13 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>DIGITIDE</t>
+          <t>NEPHROPLUS</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -4731,57 +4731,57 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>NEULANDLAB</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>HAPPSTMNDS</t>
+          <t>RBZJEWEL</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>HECPROJECT</t>
+          <t>RML</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>HLEGLAS</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -4811,17 +4811,17 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>SHUKRAPHAR</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -4831,17 +4831,17 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>SUBEXLTD</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -4855,13 +4855,13 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>VMART</t>
+          <t>WEWIN</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -4875,13 +4875,13 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>SUBROS</t>
+          <t>SUMEETINDS</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -4895,13 +4895,13 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>SUBEXLTD</t>
+          <t>TFCILTD</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -4915,13 +4915,13 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -4935,13 +4935,13 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>RML</t>
+          <t>XPROINDIA</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -4955,13 +4955,13 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>NEULANDLAB</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -4975,13 +4975,13 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>NEPHROPLUS</t>
+          <t>ZYDUSWELL</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -4995,13 +4995,13 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>MASTERTR</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5015,13 +5015,13 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5035,13 +5035,13 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>MASTERTR</t>
+          <t>MANGLMCEM</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="233">
@@ -5075,18 +5075,18 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>KSB</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5095,13 +5095,13 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>DALMIASUG</t>
+          <t>LUXIND</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5115,18 +5115,18 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>RBZJEWEL</t>
+          <t>AARNAV</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>GSPLTRANS</t>
+          <t>AMANTA</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5155,13 +5155,13 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>IPL</t>
+          <t>ASIANTILES</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5175,18 +5175,18 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>KOTHARIPET</t>
+          <t>BODALCHEM</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5195,13 +5195,13 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>DALMIASUG</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>DAMCAPITAL</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>MINDTECK</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5251,17 +5251,17 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>MITTAL</t>
+          <t>EMCURE</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5271,17 +5271,17 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>NAVKARURB</t>
+          <t>GSPLTRANS</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5291,17 +5291,17 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>PANAMAPET</t>
+          <t>HIKAL</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5311,37 +5311,37 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>HMAAGRO</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>IPL</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -5351,17 +5351,17 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR</t>
+          <t>KOPRAN</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5371,17 +5371,17 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>UNICHEMLAB</t>
+          <t>KOTHARIPET</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5391,42 +5391,42 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>DHOOTTRANS</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>RITES</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -5435,18 +5435,18 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>MINDTECK</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -5455,13 +5455,13 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>STOVEKRAFT</t>
+          <t>MITTAL</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5475,13 +5475,13 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>LCL</t>
+          <t>NAVKARURB</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>JASH</t>
+          <t>PANAMAPET</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -5515,13 +5515,13 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -5535,13 +5535,13 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>CAPACITE</t>
+          <t>RAMCOIND</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -5555,18 +5555,18 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>SAKSOFT</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -5575,13 +5575,13 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -5595,18 +5595,18 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>CERA</t>
+          <t>SHUKRAPHAR</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -5615,13 +5615,13 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>EXCELINDUS</t>
+          <t>SKFINDUS</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -5635,13 +5635,13 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>GKSL</t>
+          <t>STOVEKRAFT</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -5655,13 +5655,13 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>UNICHEMLAB</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -5675,18 +5675,18 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>GRSE</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -5695,18 +5695,18 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>VINCOFE</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -5715,13 +5715,13 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>JKLAKSHMI</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -5735,13 +5735,13 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>MFML</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -5751,37 +5751,37 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>UGROCAP</t>
+          <t>MARINE</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>TEAMLEASE</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -5791,17 +5791,17 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>PRAXIS</t>
+          <t>LENSKART</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -5811,17 +5811,17 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ORIENTPPR</t>
+          <t>MANUGRAPH</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -5831,37 +5831,37 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>MUTHOOTMF</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>CAPACITE</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -5871,17 +5871,17 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>GOACARBON</t>
+          <t>ELECTHERM</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -5891,37 +5891,37 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>GHCLTEXTIL</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>EXCELSOFT</t>
+          <t>EMUDHRA</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -5931,37 +5931,37 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>BIRLACABLE</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>AMAGI</t>
+          <t>EXCELINDUS</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -5971,37 +5971,37 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>AGARWALEYE</t>
+          <t>CERA</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -6011,17 +6011,17 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>TTKPRESTIG</t>
+          <t>GODAVARIB</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -6031,17 +6031,17 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>GRSE</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -6051,37 +6051,37 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>KAKATCEM</t>
+          <t>JASH</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>HONASA</t>
+          <t>LCL</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -6091,17 +6091,17 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>CORDSCABLE</t>
+          <t>JKLAKSHMI</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -6111,17 +6111,17 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>COFFEEDAY</t>
+          <t>KRISHIVAL</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -6131,17 +6131,17 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>FOSECOIND</t>
+          <t>GKSL</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -6151,37 +6151,37 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>GOLDIAM</t>
+          <t>MUTHOOTMF</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>NBIFIN</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -6191,17 +6191,17 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>RANEHOLDIN</t>
+          <t>NIMBSPROJ</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -6211,57 +6211,57 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>VENKEYS</t>
+          <t>ORIENTPPR</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>JAICORPLTD</t>
+          <t>TCIEXP</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>MTNL</t>
+          <t>SAMPANN</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -6271,31 +6271,871 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D294" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>TEAMLEASE</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D295" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>UGROCAP</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D296" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>LXCHEM</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D297" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>PRAXIS</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D298" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>IRIS</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D299" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>MFML</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D300" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>GUJALKALI</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D301" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>AGARWALEYE</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D302" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>AMAGI</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D303" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>AWHCL</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D304" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>BIRLACABLE</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D305" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>DHRUV</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D306" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>BGLOBAL</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D307" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>EMIL</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D308" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>EXCELSOFT</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D309" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>GHCLTEXTIL</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D310" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>GOACARBON</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D311" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>ELIN</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>HAPPYFORGE</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D313" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D314" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>TTKPRESTIG</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D315" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>RAIN</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Dividend</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D316" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>RAIN</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D317" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>KAKATCEM</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D318" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>HONASA</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D319" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>CORDSCABLE</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D320" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>COHANCE</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D321" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>COFFEEDAY</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D322" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>FOSECOIND</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D323" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>GOLDIAM</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+      <c r="D324" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>ROSSELLIND</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="D326" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>AVANTIFEED</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="D327" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>DREDGECORP</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="D328" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>IFCI</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D329" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>RANEHOLDIN</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D330" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>VISAKAIND</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D331" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>JAICORPLTD</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D332" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>MTNL</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D333" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>VENKEYS</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D334" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>HISARMETAL</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>2026-11-14</t>
+        </is>
+      </c>
+      <c r="D335" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
           <t>SANDHAR</t>
         </is>
       </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
         <is>
           <t>2026-11-16</t>
         </is>
       </c>
-      <c r="D294" t="n">
-        <v>24</v>
+      <c r="D336" t="n">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/data/upcoming_events.xlsx
+++ b/data/upcoming_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D336"/>
+  <dimension ref="A1:D350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20MICRONS</t>
+          <t>3IINFOLTD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -461,17 +461,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>NOCIL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -481,7 +481,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORBTEXP</t>
+          <t>OMAXAUTO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -491,7 +491,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -501,17 +501,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -521,17 +521,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>PARADEEP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -541,7 +541,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PRUDENT</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -561,17 +561,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>PINELABS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -581,7 +581,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>REFEX</t>
+          <t>PRAJIND</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -601,7 +601,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SADHNANIQ</t>
+          <t>RAMRAT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -621,17 +621,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SASKEN</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -641,7 +641,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SATIN</t>
+          <t>SAMBHV</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -661,17 +661,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEITINVIT</t>
+          <t>SANOFI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -681,7 +681,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NKIND</t>
+          <t>SHADOWFAX</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -701,7 +701,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SMARTLINK</t>
+          <t>NILKAMAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -721,17 +721,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -741,17 +741,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -761,17 +761,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SUNDRMFAST</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -781,17 +781,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SUNDRMFAST</t>
+          <t>STEAMHOUSE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -801,7 +801,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TCIFINANCE</t>
+          <t>STLNETWORK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -821,7 +821,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>SURYODAY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -841,17 +841,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>VNL</t>
+          <t>SUVIDHAA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -861,7 +861,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>VSTIND</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -881,7 +881,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>WELINV</t>
+          <t>TIPSFILMS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -901,7 +901,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ZENSARTECH</t>
+          <t>TITAGARH</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -921,17 +921,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ZOTA</t>
+          <t>TITAGARH</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Board meeting Rescheduled</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -941,7 +941,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STYLAMIND</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -961,7 +961,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NITYAS</t>
+          <t>WHEELS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -981,7 +981,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SHALPAINTS</t>
+          <t>SHYAMTEL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1001,17 +1001,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1021,7 +1021,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MEESHO</t>
+          <t>RPGLIFE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1041,7 +1041,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>LINCOLN</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1061,17 +1061,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>AHCL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1081,17 +1081,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ADROITIND</t>
+          <t>ARCIL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1101,7 +1101,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>MILKYMIST</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1121,17 +1121,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AGI</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1141,17 +1141,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>BLISSGVS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1161,7 +1161,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ATLASCYCLE</t>
+          <t>BOROLTD</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1181,17 +1181,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1201,17 +1201,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CARTRADE</t>
+          <t>CAPITALSFB</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1221,7 +1221,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CNL</t>
+          <t>CAPITALSFB</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1241,17 +1241,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CONTROLPR</t>
+          <t>CARERATING</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1261,17 +1261,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>DWARKESH</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1281,7 +1281,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>EMMBI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1301,7 +1301,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FABTECH</t>
+          <t>EPACK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1321,17 +1321,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>KOTYARK</t>
+          <t>FINOPB</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -1341,17 +1341,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>KISSHT</t>
+          <t>ASMS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -1361,7 +1361,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>KAMDHENU</t>
+          <t>GREENPLY</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1381,7 +1381,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>JETFREIGHT</t>
+          <t>FSL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1401,17 +1401,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>JAGSNPHARM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -1421,17 +1421,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>KRISHNADEF</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -1441,7 +1441,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GOODLUCK</t>
+          <t>KREBSBIO</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -1461,17 +1461,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GOKULAGRO</t>
+          <t>KALPATARU</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -1481,17 +1481,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>IRBINVIT</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1501,7 +1501,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GATEWAY</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -1521,17 +1521,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>INFOBEAN</t>
+          <t>INDGN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -1541,7 +1541,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SAMBHV</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1555,13 +1555,13 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>RPGLIFE</t>
+          <t>ICRA</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>HUBTOWN</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1595,13 +1595,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>RAMRAT</t>
+          <t>INDSWFTLAB</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1615,23 +1615,23 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PRAJIND</t>
+          <t>RKFORGE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -1641,7 +1641,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PARADEEP</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -1661,7 +1661,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>MEDIASSIST</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -1681,17 +1681,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>MEDIASSIST</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Buyback</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -1701,7 +1701,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>OMAXAUTO</t>
+          <t>NGIL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -1721,17 +1721,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>NOCIL</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -1741,17 +1741,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SANOFI</t>
+          <t>PRANAV</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -1761,17 +1761,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PINELABS</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -1781,7 +1781,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SHADOWFAX</t>
+          <t>RATNAVEER</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -1801,7 +1801,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>WHEELS</t>
+          <t>RESPONIND</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -1821,17 +1821,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SHYAMTEL</t>
+          <t>SHAHALLOYS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -1841,17 +1841,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>TEMPSENS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -1861,17 +1861,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -1881,7 +1881,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STEAMHOUSE</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -1901,7 +1901,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STLNETWORK</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -1921,7 +1921,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SURYODAY</t>
+          <t>SPANDANA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -1941,17 +1941,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SUVIDHAA</t>
+          <t>SRTL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -1961,7 +1961,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>UDS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -1981,17 +1981,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TIPSFILMS</t>
+          <t>VADILALIND</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -2001,17 +2001,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TITAGARH</t>
+          <t>VIMTALABS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Board meeting Rescheduled</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -2021,7 +2021,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TITAGARH</t>
+          <t>WELSPUNLIV</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -2041,7 +2041,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>WELCORP</t>
+          <t>ZEEL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -2061,7 +2061,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>NILKAMAL</t>
+          <t>LCCPROJECT</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -2081,17 +2081,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -2101,7 +2101,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>KAMOPAINTS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -2121,7 +2121,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>GMDCLTD</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -2141,7 +2141,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>LINCOLN</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -2161,7 +2161,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MILKYMIST</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -2181,17 +2181,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>AERONEU</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -2201,17 +2201,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AHCL</t>
+          <t>AFIL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -2221,7 +2221,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ARCIL</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -2241,17 +2241,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ASMS</t>
+          <t>ALMONDZ</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -2261,17 +2261,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BLISSGVS</t>
+          <t>ANDHRAPAP</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -2281,17 +2281,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BOROLTD</t>
+          <t>ARIHANTCAP</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -2301,17 +2301,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>ASIANENE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -2321,17 +2321,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CAPITALSFB</t>
+          <t>BALKRISHNA</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -2341,7 +2341,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CAPITALSFB</t>
+          <t>BESTAGRO</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -2361,17 +2361,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CARERATING</t>
+          <t>BHARATGEAR</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -2381,7 +2381,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DWARKESH</t>
+          <t>ARTEMISMED</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -2401,7 +2401,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EMMBI</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -2421,7 +2421,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>EPACK</t>
+          <t>INDOUS</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -2441,7 +2441,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -2461,7 +2461,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>FSL</t>
+          <t>GOCOLORS</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -2481,7 +2481,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FINOPB</t>
+          <t>GLOBALE</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -2501,17 +2501,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>KRISHNADEF</t>
+          <t>FINPIPE</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -2521,7 +2521,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>KALPATARU</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -2541,17 +2541,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>IRBINVIT</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -2561,7 +2561,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>INDSWFTLAB</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -2581,7 +2581,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>KREBSBIO</t>
+          <t>DIAMONDYD</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -2601,7 +2601,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -2621,7 +2621,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>IRMENERGY</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -2641,7 +2641,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>HUBTOWN</t>
+          <t>MHLXMIRU</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2651,17 +2651,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>GREENPLY</t>
+          <t>UTTAMSUGAR</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2671,57 +2671,57 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>INDGN</t>
+          <t>SURAJEST</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>SUMEETINDS</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>IRMENERGY</t>
+          <t>STUDDS</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -2741,7 +2741,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>RESPONIND</t>
+          <t>RAMBHAJO</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -2761,7 +2761,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>KAMOPAINTS</t>
+          <t>PACEDIGITK</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -2781,7 +2781,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>LCCPROJECT</t>
+          <t>NITINSPIN</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -2801,7 +2801,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>NILAINFRA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -2821,7 +2821,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>NGIL</t>
+          <t>NEUEON</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -2841,7 +2841,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PRANAV</t>
+          <t>MERCURYEV</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -2861,17 +2861,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>LATENTVIEW</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -2881,17 +2881,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>TEMPSENS</t>
+          <t>IITL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -2901,17 +2901,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>GEMAROMA</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -2921,7 +2921,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>GANECOS</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -2941,7 +2941,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SKIPPER</t>
+          <t>EXXARO</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -2961,7 +2961,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SPANDANA</t>
+          <t>DOLPHIN</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -2981,17 +2981,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>UDS</t>
+          <t>DLINKINDIA</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -3001,17 +3001,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>VADILALIND</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -3021,7 +3021,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>VIMTALABS</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -3041,7 +3041,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>WELSPUNLIV</t>
+          <t>ATULAUTO</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -3061,7 +3061,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>MEIL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -3081,47 +3081,47 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SHAHALLOYS</t>
+          <t>SAIPARENT</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>INDOUS</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>NARMADA</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3131,37 +3131,37 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>GOCOLORS</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>NELCAST</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3171,37 +3171,37 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>AFIL</t>
+          <t>ORIENTTECH</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>PCBL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3211,37 +3211,37 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ALMONDZ</t>
+          <t>MOBIKWIK</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3251,37 +3251,37 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ARIHANTCAP</t>
+          <t>PNC</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ASIANENE</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3291,17 +3291,17 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BESTAGRO</t>
+          <t>PURVA</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3311,37 +3311,37 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ANDHRAPAP</t>
+          <t>RSL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>TRIDENT</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3351,37 +3351,37 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>DIAMONDYD</t>
+          <t>SHREEPUSHK</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3391,37 +3391,37 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>TNPETRO</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3431,17 +3431,17 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>FINPIPE</t>
+          <t>TVTODAY</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3451,17 +3451,17 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>GLOBALE</t>
+          <t>UFBL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3471,37 +3471,37 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>GMDCLTD</t>
+          <t>WALCHANNAG</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BHARATGEAR</t>
+          <t>WOCKPHARMA</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3511,17 +3511,17 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>NILAINFRA</t>
+          <t>XTRANET</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3531,17 +3531,17 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>PACEDIGITK</t>
+          <t>ZUARI</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -3551,17 +3551,17 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>RAMBHAJO</t>
+          <t>MEGASTAR</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3571,17 +3571,17 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>MHLXMIRU</t>
+          <t>SHK</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -3591,17 +3591,17 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SUMEETINDS</t>
+          <t>KRYSTAL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SURAJEST</t>
+          <t>RUPA</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3631,77 +3631,77 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR</t>
+          <t>KANOHAR</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>STUDDS</t>
+          <t>AAKASH</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>MERCURYEV</t>
+          <t>ARE&amp;M</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>NITINSPIN</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -3711,17 +3711,17 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>LATENTVIEW</t>
+          <t>BCLIND</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3731,17 +3731,17 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ATULAUTO</t>
+          <t>BHARATWIRE</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3751,17 +3751,17 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>BLSE</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3771,17 +3771,17 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>DLINKINDIA</t>
+          <t>BORANA</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -3791,17 +3791,17 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>DOLPHIN</t>
+          <t>CAPILLARY</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -3811,17 +3811,17 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>CROWN</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -3831,17 +3831,17 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>MEIL</t>
+          <t>CSLFINANCE</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3851,17 +3851,17 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>GANECOS</t>
+          <t>DCMFINSERV</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3871,17 +3871,17 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>IITL</t>
+          <t>KITEX</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -3891,17 +3891,17 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>EXXARO</t>
+          <t>AEROPLANE</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -3911,22 +3911,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>RSL</t>
+          <t>DIGITIDE</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3935,18 +3935,18 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>JHS</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3955,13 +3955,13 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>PCBL</t>
+          <t>JAYBARMARU</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -3975,13 +3975,13 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>IDEAFORGE</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -3995,18 +3995,18 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PNC</t>
+          <t>DEVYANI</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4015,13 +4015,13 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>HECPROJECT</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4035,13 +4035,13 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PURVA</t>
+          <t>HLEGLAS</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4055,13 +4055,13 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>RUPA</t>
+          <t>GSLSU</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4075,13 +4075,13 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>TVTODAY</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4095,18 +4095,18 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>GANESHCP</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4115,18 +4115,18 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>EPACKPEB</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4135,13 +4135,13 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>TRIDENT</t>
+          <t>DOMS</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4155,18 +4155,18 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>NARMADA</t>
+          <t>HAPPSTMNDS</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4175,13 +4175,13 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>UFBL</t>
+          <t>RML</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -4201,7 +4201,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>WALCHANNAG</t>
+          <t>RBZJEWEL</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -4221,17 +4221,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>XTRANET</t>
+          <t>ORISSAMINE</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -4241,17 +4241,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ZUARI</t>
+          <t>ONEPOINT</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -4261,7 +4261,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SHK</t>
+          <t>MANGLMCEM</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -4281,17 +4281,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>NEULANDLAB</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -4301,7 +4301,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>NELCAST</t>
+          <t>NEPHROPLUS</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -4321,7 +4321,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>KRYSTAL</t>
+          <t>MASTERTR</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -4341,17 +4341,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>AAKASH</t>
+          <t>RPPL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -4361,7 +4361,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>MOBIKWIK</t>
+          <t>NORTHARC</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -4381,7 +4381,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -4401,7 +4401,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>BCLIND</t>
+          <t>TRANSRAILL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -4421,7 +4421,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>CAPILLARY</t>
+          <t>SKFINDIA</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -4441,7 +4441,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>CSLFINANCE</t>
+          <t>SUBEXLTD</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -4461,17 +4461,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>DEVYANI</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -4481,7 +4481,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>DIGITIDE</t>
+          <t>SUMEETINDS</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -4501,7 +4501,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>DOMS</t>
+          <t>TFCILTD</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -4521,17 +4521,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -4541,17 +4541,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>WEWIN</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -4561,7 +4561,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>XPROINDIA</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -4581,17 +4581,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>HAPPSTMNDS</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -4601,7 +4601,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>HECPROJECT</t>
+          <t>ZYDUSWELL</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -4621,7 +4621,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>HLEGLAS</t>
+          <t>MANCREDIT</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -4641,7 +4641,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>IDEAFORGE</t>
+          <t>SHUKRAPHAR</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -4661,7 +4661,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>JHS</t>
+          <t>LUXIND</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -4681,17 +4681,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>KANOHAR</t>
+          <t>KOTHARIPET</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -4701,7 +4701,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>EPACKPEB</t>
+          <t>AARNAV</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -4721,7 +4721,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>NEPHROPLUS</t>
+          <t>KSB</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -4735,13 +4735,13 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>NEULANDLAB</t>
+          <t>ABINFRA</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -4755,18 +4755,18 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>RBZJEWEL</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -4775,13 +4775,13 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>RML</t>
+          <t>AMANTA</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -4795,18 +4795,18 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>AMRUTANJAN</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -4815,18 +4815,18 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR</t>
+          <t>ARIHANTSUP</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -4835,13 +4835,13 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>SUBEXLTD</t>
+          <t>ASIANTILES</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -4855,18 +4855,18 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>WEWIN</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -4875,18 +4875,18 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>SUMEETINDS</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -4895,18 +4895,18 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>TFCILTD</t>
+          <t>BODALCHEM</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -4915,13 +4915,13 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>VMART</t>
+          <t>CEWATER</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -4935,13 +4935,13 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>XPROINDIA</t>
+          <t>ASHOKAMET</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -4955,13 +4955,13 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>DAMCAPITAL</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -4975,13 +4975,13 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>DALMIASUG</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -4995,13 +4995,13 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>MASTERTR</t>
+          <t>IPL</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5015,13 +5015,13 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>SUBROS</t>
+          <t>HMAAGRO</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5035,13 +5035,13 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>MANGLMCEM</t>
+          <t>HIKAL</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>GSPLTRANS</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5075,13 +5075,13 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>KSB</t>
+          <t>KOPRAN</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5095,13 +5095,13 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>EMCURE</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5115,18 +5115,18 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>AARNAV</t>
+          <t>DHOOTTRANS</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>AMANTA</t>
+          <t>DEEPINDS</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5155,13 +5155,13 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>ASIANTILES</t>
+          <t>GRAPHITE</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5175,23 +5175,23 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>BODALCHEM</t>
+          <t>ROLEXRINGS</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -5201,7 +5201,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>DALMIASUG</t>
+          <t>MITTAL</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -5221,7 +5221,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>DAMCAPITAL</t>
+          <t>NAVKARURB</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -5241,17 +5241,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>OMNI</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D242" t="n">
@@ -5261,7 +5261,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>PANAMAPET</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D243" t="n">
@@ -5281,7 +5281,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>GSPLTRANS</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D244" t="n">
@@ -5301,17 +5301,17 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>HIKAL</t>
+          <t>PREMIERENE</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -5321,7 +5321,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>HMAAGRO</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D246" t="n">
@@ -5341,7 +5341,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>IPL</t>
+          <t>RAMCOIND</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D247" t="n">
@@ -5361,17 +5361,17 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>KOPRAN</t>
+          <t>RITES</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -5381,17 +5381,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>KOTHARIPET</t>
+          <t>SAKSOFT</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D249" t="n">
@@ -5401,7 +5401,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>DHOOTTRANS</t>
+          <t>MINDTECK</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -5421,12 +5421,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>SHANKARA</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -5435,18 +5435,18 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>MINDTECK</t>
+          <t>SHRINGARMS</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -5455,13 +5455,13 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>MITTAL</t>
+          <t>SHUKRAPHAR</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5475,13 +5475,13 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>NAVKARURB</t>
+          <t>SKFINDUS</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>PANAMAPET</t>
+          <t>STOVEKRAFT</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -5515,13 +5515,13 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>SWANCORP</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -5535,13 +5535,13 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>RAMCOIND</t>
+          <t>TIJARIA</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -5555,18 +5555,18 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>SAKSOFT</t>
+          <t>UNICHEMLAB</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -5575,18 +5575,18 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -5595,13 +5595,13 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR</t>
+          <t>VINCOFE</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -5615,13 +5615,13 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>SKFINDUS</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -5635,13 +5635,13 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>STOVEKRAFT</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -5655,13 +5655,13 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>UNICHEMLAB</t>
+          <t>JASH</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -5675,13 +5675,13 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>MANUGRAPH</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -5695,13 +5695,13 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>VINCOFE</t>
+          <t>MARINE</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -5715,13 +5715,13 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -5735,13 +5735,13 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -5755,18 +5755,18 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>MARINE</t>
+          <t>CERA</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -5775,13 +5775,13 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>ELECTHERM</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -5795,18 +5795,18 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -5815,18 +5815,18 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>MANUGRAPH</t>
+          <t>EMUDHRA</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -5835,18 +5835,18 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -5855,13 +5855,13 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>CAPACITE</t>
+          <t>EXCELINDUS</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -5875,13 +5875,13 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ELECTHERM</t>
+          <t>GAYAPROJ</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -5895,18 +5895,18 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>GKSL</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -5915,13 +5915,13 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>CAPACITE</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -5935,18 +5935,18 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>GODAVARIB</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -5955,13 +5955,13 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>EXCELINDUS</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -5975,18 +5975,18 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>CERA</t>
+          <t>LCL</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -5995,13 +5995,13 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>LENSKART</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -6015,13 +6015,13 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>GODAVARIB</t>
+          <t>KRISHIVAL</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -6035,13 +6035,13 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>GRSE</t>
+          <t>KSHITIJPOL</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -6055,13 +6055,13 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>JASH</t>
+          <t>IVP</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -6075,13 +6075,13 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>LCL</t>
+          <t>HARIOMPIPE</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -6095,13 +6095,13 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>JKLAKSHMI</t>
+          <t>GUJTHEM</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -6115,13 +6115,13 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>KRISHIVAL</t>
+          <t>GRSE</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -6135,13 +6135,13 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>GKSL</t>
+          <t>JKLAKSHMI</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -6155,13 +6155,13 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>MUTHOOTMF</t>
+          <t>ORIENTPPR</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -6175,13 +6175,13 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>NBIFIN</t>
+          <t>LXCHEM</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -6195,13 +6195,13 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>NIMBSPROJ</t>
+          <t>MFML</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ORIENTPPR</t>
+          <t>MUTHOOTMF</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -6235,13 +6235,13 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>TCIEXP</t>
+          <t>NBIFIN</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -6255,13 +6255,13 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>SAMPANN</t>
+          <t>NIMBSPROJ</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -6275,13 +6275,13 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>PRAXIS</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -6295,13 +6295,13 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>TEAMLEASE</t>
+          <t>TCIEXP</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -6315,18 +6315,18 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>UGROCAP</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -6335,13 +6335,13 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>SAMPANN</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -6355,13 +6355,13 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>PRAXIS</t>
+          <t>SMT</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -6375,13 +6375,13 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>TEAMLEASE</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -6395,18 +6395,18 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>MFML</t>
+          <t>UGROCAP</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -6415,18 +6415,18 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>GUJALKALI</t>
+          <t>VEEGALAND</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -6435,13 +6435,13 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>AGARWALEYE</t>
+          <t>INDIANHUME</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -6455,13 +6455,13 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>AMAGI</t>
+          <t>PROTEAN</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -6475,13 +6475,13 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>AWHCL</t>
+          <t>IGARASHI</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -6495,13 +6495,13 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>BIRLACABLE</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -6515,13 +6515,13 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>DHRUV</t>
+          <t>GUJALKALI</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -6535,13 +6535,13 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>BGLOBAL</t>
+          <t>AGARWALEYE</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -6555,13 +6555,13 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>AMAGI</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -6575,13 +6575,13 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>EXCELSOFT</t>
+          <t>ASHOKA</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -6595,13 +6595,13 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>GHCLTEXTIL</t>
+          <t>AWHCL</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -6615,13 +6615,13 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>GOACARBON</t>
+          <t>BGLOBAL</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -6635,13 +6635,13 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>ELIN</t>
+          <t>CEMPRO</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -6655,18 +6655,18 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>HAPPYFORGE</t>
+          <t>DHRUV</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -6675,13 +6675,13 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>BIRLACABLE</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -6691,17 +6691,17 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>TTKPRESTIG</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -6711,37 +6711,37 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>EUROPRATIK</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>EXCELSOFT</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -6751,37 +6751,37 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>KAKATCEM</t>
+          <t>GHCLTEXTIL</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>HONASA</t>
+          <t>GOACARBON</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -6791,37 +6791,37 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>CORDSCABLE</t>
+          <t>GPTHEALTH</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>COHANCE</t>
+          <t>ELIN</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -6831,17 +6831,17 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>COFFEEDAY</t>
+          <t>HAPPYFORGE</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -6851,22 +6851,22 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>FOSECOIND</t>
+          <t>KAKATCEM</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -6875,33 +6875,33 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>GOLDIAM</t>
+          <t>TTKPRESTIG</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -6911,57 +6911,57 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>ROSSELLIND</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>AVANTIFEED</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>DREDGECORP</t>
+          <t>FOSECOIND</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -6971,17 +6971,17 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>IFCI</t>
+          <t>CORDSCABLE</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -6991,17 +6991,17 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>RANEHOLDIN</t>
+          <t>COHANCE</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -7011,17 +7011,17 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>VISAKAIND</t>
+          <t>COFFEEDAY</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -7031,111 +7031,391 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>JAICORPLTD</t>
+          <t>HONASA</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>MTNL</t>
+          <t>GOLDIAM</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>VENKEYS</t>
+          <t>AVANTIFEED</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>HISARMETAL</t>
+          <t>DREDGECORP</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="D336" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>ROSSELLIND</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="D337" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>VISAKAIND</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D338" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>RANEHOLDIN</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D339" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>BALAXI</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D340" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>ALICON</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D341" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>IFCI</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D342" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>JAICORPLTD</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D343" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>MTNL</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D344" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>PRECOT</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D345" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>VENKEYS</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D346" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>HISARMETAL</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>2026-11-14</t>
+        </is>
+      </c>
+      <c r="D347" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>TVSELECT</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>2026-11-14</t>
+        </is>
+      </c>
+      <c r="D348" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
           <t>SANDHAR</t>
         </is>
       </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
         <is>
           <t>2026-11-16</t>
         </is>
       </c>
-      <c r="D336" t="n">
-        <v>21</v>
+      <c r="D349" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>RNBDENIMS</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>2026-12-05</t>
+        </is>
+      </c>
+      <c r="D350" t="n">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/data/upcoming_events.xlsx
+++ b/data/upcoming_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D350"/>
+  <dimension ref="A1:D379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,17 +441,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -461,7 +461,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NOCIL</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -471,7 +471,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -481,7 +481,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OMAXAUTO</t>
+          <t>MEDIASSIST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -491,7 +491,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -501,17 +501,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>MEDIASSIST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Buyback</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -521,17 +521,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PARADEEP</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -541,7 +541,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>PRANAV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -561,17 +561,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PINELABS</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -581,7 +581,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PRAJIND</t>
+          <t>RATNAVEER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -601,7 +601,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RAMRAT</t>
+          <t>RESPONIND</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -621,17 +621,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>RKFORGE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -641,17 +641,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SAMBHV</t>
+          <t>SHAHALLOYS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -661,17 +661,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SANOFI</t>
+          <t>LCCPROJECT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -681,17 +681,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SHADOWFAX</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -701,7 +701,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NILKAMAL</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -721,17 +721,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -741,17 +741,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>SPANDANA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -761,17 +761,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>SRTL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -781,17 +781,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STEAMHOUSE</t>
+          <t>TEMPSENS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -801,7 +801,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STLNETWORK</t>
+          <t>UDS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -821,17 +821,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SURYODAY</t>
+          <t>VADILALIND</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -841,17 +841,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SUVIDHAA</t>
+          <t>VIMTALABS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -861,7 +861,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>WELSPUNLIV</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -881,7 +881,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TIPSFILMS</t>
+          <t>ZEEL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -901,17 +901,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TITAGARH</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -921,17 +921,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TITAGARH</t>
+          <t>KAMOPAINTS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Board meeting Rescheduled</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -941,7 +941,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WELCORP</t>
+          <t>NGIL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -961,7 +961,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>WHEELS</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -981,7 +981,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SHYAMTEL</t>
+          <t>AERONEU</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1001,7 +1001,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>AFIL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1021,7 +1021,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RPGLIFE</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1041,17 +1041,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LINCOLN</t>
+          <t>ALMONDZ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1061,17 +1061,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AHCL</t>
+          <t>ANDHRAPAP</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1081,17 +1081,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ARCIL</t>
+          <t>ARIHANTCAP</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1101,7 +1101,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MILKYMIST</t>
+          <t>IRMENERGY</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1121,7 +1121,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>ASIANENE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1141,17 +1141,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BLISSGVS</t>
+          <t>BALKRISHNA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1161,7 +1161,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BOROLTD</t>
+          <t>BESTAGRO</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1181,17 +1181,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>BHARATGEAR</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1201,17 +1201,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CAPITALSFB</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1221,7 +1221,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CAPITALSFB</t>
+          <t>ARTEMISMED</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1241,17 +1241,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CARERATING</t>
+          <t>DIAMONDYD</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1261,7 +1261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DWARKESH</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1281,7 +1281,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EMMBI</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1301,17 +1301,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EPACK</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1321,7 +1321,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FINOPB</t>
+          <t>FINPIPE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -1341,17 +1341,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ASMS</t>
+          <t>GLOBALE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -1361,7 +1361,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GREENPLY</t>
+          <t>GMDCLTD</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1381,7 +1381,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FSL</t>
+          <t>GOCOLORS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1401,17 +1401,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -1421,17 +1421,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KRISHNADEF</t>
+          <t>INDOUS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -1441,17 +1441,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>KREBSBIO</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -1461,7 +1461,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>KALPATARU</t>
+          <t>NILAINFRA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1471,37 +1471,37 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>IRBINVIT</t>
+          <t>NITINSPIN</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>PACEDIGITK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1511,37 +1511,37 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>INDGN</t>
+          <t>PRIORITY</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>RAMBHAJO</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1551,17 +1551,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>UTTAMSUGAR</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>HUBTOWN</t>
+          <t>STUDDS</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1591,17 +1591,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>INDSWFTLAB</t>
+          <t>SUMEETINDS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1611,27 +1611,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>RKFORGE</t>
+          <t>SURAJEST</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -1641,7 +1641,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>NEUEON</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -1661,7 +1661,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MEDIASSIST</t>
+          <t>SIGACHI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -1681,17 +1681,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MEDIASSIST</t>
+          <t>MHLXMIRU</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Buyback</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -1701,17 +1701,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NGIL</t>
+          <t>DLINKINDIA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -1721,17 +1721,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>MEIL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -1741,7 +1741,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PRANAV</t>
+          <t>MERCURYEV</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -1761,17 +1761,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>ATULAUTO</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -1781,7 +1781,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>RATNAVEER</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -1801,7 +1801,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>RESPONIND</t>
+          <t>DOLPHIN</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -1821,7 +1821,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SHAHALLOYS</t>
+          <t>ESSENTIA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -1841,17 +1841,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TEMPSENS</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -1861,17 +1861,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>GANECOS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -1881,7 +1881,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>GEMAROMA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -1901,7 +1901,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SKIPPER</t>
+          <t>IITL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -1921,7 +1921,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SPANDANA</t>
+          <t>LATENTVIEW</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -1941,17 +1941,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SRTL</t>
+          <t>EXXARO</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -1961,7 +1961,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>UDS</t>
+          <t>SAIPARENT</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>VADILALIND</t>
+          <t>PNC</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>VIMTALABS</t>
+          <t>ORIENTTECH</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>WELSPUNLIV</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2031,17 +2031,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ZEEL</t>
+          <t>PCBL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2051,57 +2051,57 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>LCCPROJECT</t>
+          <t>PATINTLOG</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>NELCAST</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>KAMOPAINTS</t>
+          <t>MOBIKWIK</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2111,37 +2111,37 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GMDCLTD</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>NARMADA</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2151,37 +2151,37 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AERONEU</t>
+          <t>MOHITIND</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2191,17 +2191,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AFIL</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2211,17 +2211,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>MEGASTAR</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2231,37 +2231,37 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ALMONDZ</t>
+          <t>NDLVENTURE</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ANDHRAPAP</t>
+          <t>PURVA</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ARIHANTCAP</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ASIANENE</t>
+          <t>RUPA</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2311,37 +2311,37 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BALKRISHNA</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BESTAGRO</t>
+          <t>ZUARI</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BHARATGEAR</t>
+          <t>XTRANET</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2371,17 +2371,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ARTEMISMED</t>
+          <t>WOCKPHARMA</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2391,37 +2391,37 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>WALCHANNAG</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>INDOUS</t>
+          <t>UFBL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2431,37 +2431,37 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>RSL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>GOCOLORS</t>
+          <t>TVTODAY</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2471,37 +2471,37 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>GLOBALE</t>
+          <t>TPHQ</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>FINPIPE</t>
+          <t>TNPETRO</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2511,17 +2511,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2531,77 +2531,77 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>SIGNPOST</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>SHREEPUSHK</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DIAMONDYD</t>
+          <t>SHK</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>TRIDENT</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2611,17 +2611,17 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>IRMENERGY</t>
+          <t>KRYSTAL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2631,17 +2631,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MHLXMIRU</t>
+          <t>DANGEE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2651,37 +2651,37 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR</t>
+          <t>KANOHAR</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SURAJEST</t>
+          <t>KITEX</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2691,37 +2691,37 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SUMEETINDS</t>
+          <t>AAKASH</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STUDDS</t>
+          <t>AEROPLANE</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2731,37 +2731,37 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>RAMBHAJO</t>
+          <t>ARE&amp;M</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>PACEDIGITK</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2771,17 +2771,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>NITINSPIN</t>
+          <t>BCLIND</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2791,17 +2791,17 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>NILAINFRA</t>
+          <t>BHARATWIRE</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2811,17 +2811,17 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>NEUEON</t>
+          <t>BLSE</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2831,37 +2831,37 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MERCURYEV</t>
+          <t>BORANA</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>LATENTVIEW</t>
+          <t>CROWN</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2871,17 +2871,17 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>IITL</t>
+          <t>CSLFINANCE</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GEMAROMA</t>
+          <t>DCMFINSERV</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2911,37 +2911,37 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GANECOS</t>
+          <t>DEVYANI</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>EXXARO</t>
+          <t>DIGITIDE</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2951,57 +2951,57 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>DOLPHIN</t>
+          <t>DIVGIITTS</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>DLINKINDIA</t>
+          <t>CAPILLARY</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>EFCIL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3011,37 +3011,37 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>JTLIND</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ATULAUTO</t>
+          <t>DOMS</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3051,17 +3051,17 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MEIL</t>
+          <t>JAYBARMARU</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SAIPARENT</t>
+          <t>IGCL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -3101,12 +3101,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>IDEAFORGE</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3115,13 +3115,13 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>NARMADA</t>
+          <t>HLEGLAS</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3135,18 +3135,18 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>HECPROJECT</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3155,18 +3155,18 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>NELCAST</t>
+          <t>HAPPSTMNDS</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3175,18 +3175,18 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ORIENTTECH</t>
+          <t>JHS</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3195,13 +3195,13 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PCBL</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3215,13 +3215,13 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MOBIKWIK</t>
+          <t>GOYALALUM</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3235,18 +3235,18 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>GANESHCP</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3255,13 +3255,13 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>PNC</t>
+          <t>ESDS</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>EPACKPEB</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3295,13 +3295,13 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>PURVA</t>
+          <t>GSLSU</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3315,23 +3315,23 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>RSL</t>
+          <t>RML</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -3341,7 +3341,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>TRIDENT</t>
+          <t>RHETAN</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -3361,17 +3361,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SHREEPUSHK</t>
+          <t>RBZJEWEL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising/Other business matters</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -3381,7 +3381,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>PARAGMILK</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -3401,17 +3401,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>ORISSAMINE</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -3421,7 +3421,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>TNPETRO</t>
+          <t>ONIDA</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -3441,17 +3441,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>TVTODAY</t>
+          <t>ONEPOINT</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -3461,7 +3461,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>UFBL</t>
+          <t>MASTERTR</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -3481,17 +3481,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>WALCHANNAG</t>
+          <t>NEPHROPLUS</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -3501,17 +3501,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>WOCKPHARMA</t>
+          <t>METROPOLIS</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -3521,7 +3521,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>XTRANET</t>
+          <t>MANGLMCEM</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -3541,7 +3541,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ZUARI</t>
+          <t>MANCREDIT</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -3561,7 +3561,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>MEGASTAR</t>
+          <t>LUXIND</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -3581,7 +3581,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SHK</t>
+          <t>LAXMIDENTL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -3601,7 +3601,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>KRYSTAL</t>
+          <t>NEULANDLAB</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -3621,7 +3621,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>RUPA</t>
+          <t>RPPL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -3641,17 +3641,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>KANOHAR</t>
+          <t>ZYDUSWELL</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -3661,17 +3661,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>AAKASH</t>
+          <t>SEDEMAC</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -3681,17 +3681,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>KSB</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -3701,7 +3701,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -3721,7 +3721,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>BCLIND</t>
+          <t>XPROINDIA</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -3741,7 +3741,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>BHARATWIRE</t>
+          <t>WEWIN</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -3761,7 +3761,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>BLSE</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -3781,17 +3781,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>BORANA</t>
+          <t>TRANSRAILL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -3801,17 +3801,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CAPILLARY</t>
+          <t>RSYSTEMS</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -3821,7 +3821,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CROWN</t>
+          <t>TFCILTD</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -3841,7 +3841,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>CSLFINANCE</t>
+          <t>SUMEETINDS</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -3861,7 +3861,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>DCMFINSERV</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -3881,7 +3881,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>KITEX</t>
+          <t>SUBEXLTD</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -3901,7 +3901,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>AEROPLANE</t>
+          <t>SKFINDIA</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -3921,7 +3921,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>DIGITIDE</t>
+          <t>SHUKRAPHAR</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -3941,7 +3941,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>JHS</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -3961,7 +3961,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>JAYBARMARU</t>
+          <t>SUYOG</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -3981,7 +3981,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>IDEAFORGE</t>
+          <t>KOTHARIPET</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -4001,17 +4001,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>DEVYANI</t>
+          <t>NORTHARC</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -4021,7 +4021,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>HECPROJECT</t>
+          <t>JGCHEM</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -4041,7 +4041,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>HLEGLAS</t>
+          <t>AWFIS</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -4061,17 +4061,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>GSLSU</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -4081,7 +4081,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>ASIANTILES</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -4101,17 +4101,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>ASHOKAMET</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -4121,7 +4121,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>EPACKPEB</t>
+          <t>ARIS</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -4141,7 +4141,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>DOMS</t>
+          <t>ARFIN</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -4161,17 +4161,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>HAPPSTMNDS</t>
+          <t>BLS</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -4181,7 +4181,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>RML</t>
+          <t>ANTHEM</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4195,18 +4195,18 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>RBZJEWEL</t>
+          <t>AMANTA</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4215,18 +4215,18 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ORISSAMINE</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4235,18 +4235,18 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ONEPOINT</t>
+          <t>ABINFRA</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4255,13 +4255,13 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>MANGLMCEM</t>
+          <t>AARTIDRUGS</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4275,13 +4275,13 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>NEULANDLAB</t>
+          <t>AARNAV</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4295,13 +4295,13 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>NEPHROPLUS</t>
+          <t>KOPRAN</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4315,18 +4315,18 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>MASTERTR</t>
+          <t>AMRUTANJAN</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4335,18 +4335,18 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>RPPL</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4355,18 +4355,18 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>NORTHARC</t>
+          <t>ARIHANTSUP</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4375,13 +4375,13 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>CEWATER</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4395,13 +4395,13 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>TRANSRAILL</t>
+          <t>IPL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4415,18 +4415,18 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SKFINDIA</t>
+          <t>BODALCHEM</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4435,13 +4435,13 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SUBEXLTD</t>
+          <t>HMAAGRO</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4455,13 +4455,13 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SUBROS</t>
+          <t>HIKAL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4475,13 +4475,13 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SUMEETINDS</t>
+          <t>HGINFRA</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4495,13 +4495,13 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>TFCILTD</t>
+          <t>GSPLTRANS</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4515,13 +4515,13 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>VMART</t>
+          <t>GLASSWALL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -4535,13 +4535,13 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>WEWIN</t>
+          <t>EMCURE</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4555,13 +4555,13 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>XPROINDIA</t>
+          <t>GRAPHITE</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4575,13 +4575,13 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4595,18 +4595,18 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>DHOOTTRANS</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -4615,13 +4615,13 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>MANCREDIT</t>
+          <t>DEEPINDS</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -4635,18 +4635,18 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR</t>
+          <t>DATAMATICS</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4655,13 +4655,13 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>DAMCAPITAL</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -4675,13 +4675,13 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>KOTHARIPET</t>
+          <t>DALMIASUG</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -4695,13 +4695,13 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>AARNAV</t>
+          <t>ROLEXRINGS</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -4721,17 +4721,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>KSB</t>
+          <t>PREMIERENE</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -4741,17 +4741,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ABINFRA</t>
+          <t>REPL</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -4761,7 +4761,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>RAMCOIND</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -4781,7 +4781,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>AMANTA</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -4801,7 +4801,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>AMRUTANJAN</t>
+          <t>RITES</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -4821,17 +4821,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ARIHANTSUP</t>
+          <t>PLATIND</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -4841,17 +4841,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ASIANTILES</t>
+          <t>MAYURUNIQ</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -4861,17 +4861,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>ORICONENT</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -4881,17 +4881,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>OMNI</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -4901,17 +4901,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>BODALCHEM</t>
+          <t>NAVKARURB</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -4921,7 +4921,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>CEWATER</t>
+          <t>MOL</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -4941,7 +4941,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ASHOKAMET</t>
+          <t>MITTAL</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -4961,17 +4961,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>DAMCAPITAL</t>
+          <t>MINDTECK</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -4981,7 +4981,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>DALMIASUG</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -5001,17 +5001,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>IPL</t>
+          <t>SAKSOFT</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -5021,7 +5021,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>HMAAGRO</t>
+          <t>PANAMAPET</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -5041,7 +5041,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>HIKAL</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -5061,7 +5061,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>GSPLTRANS</t>
+          <t>VINCOFE</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -5081,17 +5081,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>KOPRAN</t>
+          <t>SCI</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -5101,7 +5101,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -5121,17 +5121,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>DHOOTTRANS</t>
+          <t>WANBURY</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -5141,7 +5141,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>DEEPINDS</t>
+          <t>MARINE</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -5161,17 +5161,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>GRAPHITE</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D238" t="n">
@@ -5181,7 +5181,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ROLEXRINGS</t>
+          <t>UNICHEMLAB</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5195,18 +5195,18 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>MITTAL</t>
+          <t>TVSINVIT</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>NAVKARURB</t>
+          <t>TOKYOPLAST</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5235,13 +5235,13 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>OMNI</t>
+          <t>SBCL</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5255,13 +5255,13 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>PANAMAPET</t>
+          <t>TIJARIA</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5275,13 +5275,13 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>STOVEKRAFT</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5295,18 +5295,18 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>PREMIERENE</t>
+          <t>SOFTTECH</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -5315,13 +5315,13 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>SMSPHARMA</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -5335,13 +5335,13 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>RAMCOIND</t>
+          <t>SJS</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -5355,18 +5355,18 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>SHUKRAPHAR</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5375,18 +5375,18 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>SAKSOFT</t>
+          <t>SHRINGARMS</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -5395,18 +5395,18 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>MINDTECK</t>
+          <t>SHANKARA</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -5415,13 +5415,13 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>SHANKARA</t>
+          <t>SWANCORP</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5435,18 +5435,18 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>SHRINGARMS</t>
+          <t>MAPMYINDIA</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -5455,13 +5455,13 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR</t>
+          <t>SKFINDUS</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5475,18 +5475,18 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>SKFINDUS</t>
+          <t>MANIKA</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>STOVEKRAFT</t>
+          <t>ELECTHERM</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -5515,13 +5515,13 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>SWANCORP</t>
+          <t>DELTAMAGNT</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -5535,13 +5535,13 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>TIJARIA</t>
+          <t>CPCAP</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -5555,13 +5555,13 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>UNICHEMLAB</t>
+          <t>CORALFINAC</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -5575,18 +5575,18 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>CHEMPLASTS</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -5595,18 +5595,18 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>VINCOFE</t>
+          <t>CERA</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -5615,13 +5615,13 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>CENTUM</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -5635,18 +5635,18 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -5655,13 +5655,13 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>JASH</t>
+          <t>CAPACITE</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="264">
@@ -5695,13 +5695,13 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>MARINE</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -5715,18 +5715,18 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>BALRAMCHIN</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -5735,13 +5735,13 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>BAJEL</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -5755,18 +5755,18 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>CERA</t>
+          <t>AUSOMENT</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -5775,18 +5775,18 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ELECTHERM</t>
+          <t>APOLLOTYRE</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -5795,18 +5795,18 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>63MOONS</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -5835,18 +5835,18 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>EMUDHRA</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -5855,13 +5855,13 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>EXCELINDUS</t>
+          <t>BLBLIMITED</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -5875,13 +5875,13 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>GAYAPROJ</t>
+          <t>EPL</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -5895,18 +5895,18 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>GKSL</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -5915,13 +5915,13 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>CAPACITE</t>
+          <t>LENSKART</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -5935,13 +5935,13 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>GODAVARIB</t>
+          <t>LCL</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -5955,13 +5955,13 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>KSHITIJPOL</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -5975,13 +5975,13 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>LCL</t>
+          <t>JKLAKSHMI</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -5995,13 +5995,13 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>JISLJALEQS</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -6015,13 +6015,13 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>KRISHIVAL</t>
+          <t>JISLDVREQS</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -6035,13 +6035,13 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>KSHITIJPOL</t>
+          <t>JASH</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -6055,13 +6055,13 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>IVP</t>
+          <t>KRISHIVAL</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="284">
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="285">
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="286">
@@ -6135,13 +6135,13 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>JKLAKSHMI</t>
+          <t>GODAVARIB</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -6155,33 +6155,33 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>ORIENTPPR</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>GKSL</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -6191,17 +6191,17 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>MFML</t>
+          <t>GAYAPROJ</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -6211,37 +6211,37 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>MUTHOOTMF</t>
+          <t>IVP</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>NBIFIN</t>
+          <t>EXCELINDUS</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -6251,22 +6251,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>NIMBSPROJ</t>
+          <t>ORIENTPPR</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -6275,13 +6275,13 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>PRAXIS</t>
+          <t>NIMBSPROJ</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -6295,13 +6295,13 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>TCIEXP</t>
+          <t>NBIFIN</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -6315,18 +6315,18 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>MUTHOOTMF</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -6335,13 +6335,13 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>SAMPANN</t>
+          <t>LXCHEM</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -6355,13 +6355,13 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>MANYAVAR</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -6375,13 +6375,13 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>TEAMLEASE</t>
+          <t>MAITHANALL</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -6395,18 +6395,18 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>UGROCAP</t>
+          <t>KARAMTARA</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -6415,13 +6415,13 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>VEEGALAND</t>
+          <t>PRAXIS</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -6435,13 +6435,13 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>INDIANHUME</t>
+          <t>MFML</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="303">
@@ -6475,13 +6475,13 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>IGARASHI</t>
+          <t>TEAMLEASE</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -6495,13 +6495,13 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -6515,18 +6515,18 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>GUJALKALI</t>
+          <t>RUDRA</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -6535,13 +6535,13 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>AGARWALEYE</t>
+          <t>SAMPANN</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -6555,13 +6555,13 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>AMAGI</t>
+          <t>SETL</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -6575,13 +6575,13 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>ASHOKA</t>
+          <t>SHAH</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -6595,13 +6595,13 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>AWHCL</t>
+          <t>SMT</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -6615,13 +6615,13 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>BGLOBAL</t>
+          <t>SYMBIOTEC</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -6635,13 +6635,13 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>CEMPRO</t>
+          <t>TCIEXP</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -6655,13 +6655,13 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>DHRUV</t>
+          <t>UGROCAP</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -6675,13 +6675,13 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>BIRLACABLE</t>
+          <t>VEEGALAND</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -6695,13 +6695,13 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -6715,13 +6715,13 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>EUROPRATIK</t>
+          <t>RNBDENIMS</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -6735,13 +6735,13 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>EXCELSOFT</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -6755,18 +6755,18 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>GHCLTEXTIL</t>
+          <t>HITECH</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -6775,13 +6775,13 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>GOACARBON</t>
+          <t>IGARASHI</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -6795,18 +6795,18 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>GPTHEALTH</t>
+          <t>AGARWALEYE</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -6815,13 +6815,13 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>ELIN</t>
+          <t>AMAGI</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -6835,13 +6835,13 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>HAPPYFORGE</t>
+          <t>ARVSMART</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -6855,33 +6855,33 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>KAKATCEM</t>
+          <t>ASHOKA</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>TTKPRESTIG</t>
+          <t>AWHCL</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -6891,17 +6891,17 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>BGLOBAL</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -6911,37 +6911,37 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>BIRLACABLE</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>BUILDPRO</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -6951,17 +6951,17 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>FOSECOIND</t>
+          <t>INDIANHUME</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -6971,17 +6971,17 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>CORDSCABLE</t>
+          <t>CREST</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -6991,37 +6991,37 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>COHANCE</t>
+          <t>DHRUV</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>COFFEEDAY</t>
+          <t>CEMPRO</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -7031,17 +7031,17 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>HONASA</t>
+          <t>DUCON</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -7051,37 +7051,37 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>GOLDIAM</t>
+          <t>HAPPYFORGE</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>AVANTIFEED</t>
+          <t>DPWIRES</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -7091,37 +7091,37 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>DREDGECORP</t>
+          <t>GPTHEALTH</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>GOACARBON</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -7131,17 +7131,17 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>ROSSELLIND</t>
+          <t>GHCLTEXTIL</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -7151,37 +7151,37 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>VISAKAIND</t>
+          <t>GUJALKALI</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>RANEHOLDIN</t>
+          <t>EXCELSOFT</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -7191,37 +7191,37 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>BALAXI</t>
+          <t>EUROPRATIK</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>ALICON</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -7231,17 +7231,17 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>IFCI</t>
+          <t>ELIN</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -7251,37 +7251,37 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>JAICORPLTD</t>
+          <t>GCSL</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>MTNL</t>
+          <t>TTKPRESTIG</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -7291,37 +7291,37 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>PRECOT</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>VENKEYS</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -7331,57 +7331,57 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>HISARMETAL</t>
+          <t>NITYAS</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>TVSELECT</t>
+          <t>KAKATCEM</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>SANDHAR</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -7391,31 +7391,611 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
+          <t>HONASA</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D350" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>CORDSCABLE</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D351" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>COHANCE</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D352" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>COFFEEDAY</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D353" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>BLUSPRING</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D354" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>ASTERDM</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D355" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>ALEMBICLTD</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D356" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>FOSECOIND</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D357" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>GOLDIAM</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+      <c r="D358" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>TATACHEM</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+      <c r="D359" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>AVANTIFEED</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="D360" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>DREDGECORP</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="D361" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="D362" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>ROSSELLIND</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="D363" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>VISAKAIND</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D364" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>RANEHOLDIN</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D365" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>MANAKALUCO</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D366" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>BALAXI</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D367" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>ALICON</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D368" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>IFCI</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D369" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>JAICORPLTD</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D370" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>MOTOGENFIN</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D371" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>MTNL</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D372" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>PRECOT</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D373" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>RHIM</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D374" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>VENKEYS</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D375" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>HISARMETAL</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>2026-11-14</t>
+        </is>
+      </c>
+      <c r="D376" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>TVSELECT</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>2026-11-14</t>
+        </is>
+      </c>
+      <c r="D377" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>SANDHAR</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="D378" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
           <t>RNBDENIMS</t>
         </is>
       </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
         <is>
           <t>2026-12-05</t>
         </is>
       </c>
-      <c r="D350" t="n">
-        <v>39</v>
+      <c r="D379" t="n">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/data/upcoming_events.xlsx
+++ b/data/upcoming_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D379"/>
+  <dimension ref="A1:D388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>ATULAUTO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -461,7 +461,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>UTTAMSUGAR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -471,7 +471,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -481,7 +481,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MEDIASSIST</t>
+          <t>SURAJEST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -491,7 +491,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -501,17 +501,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MEDIASSIST</t>
+          <t>SUMEETINDS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Buyback</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -521,17 +521,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>STUDDS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -541,7 +541,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PRANAV</t>
+          <t>RAMBHAJO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -561,17 +561,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>PRIORITY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -581,7 +581,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RATNAVEER</t>
+          <t>PACEDIGITK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -601,7 +601,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RESPONIND</t>
+          <t>NITINSPIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -621,17 +621,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RKFORGE</t>
+          <t>NILAINFRA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -641,17 +641,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SHAHALLOYS</t>
+          <t>NEUEON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -661,7 +661,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LCCPROJECT</t>
+          <t>MHLXMIRU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -681,17 +681,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>SIGACHI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -701,7 +701,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>MEIL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -721,7 +721,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SKIPPER</t>
+          <t>MERCURYEV</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -741,7 +741,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SPANDANA</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -761,17 +761,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SRTL</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -781,17 +781,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TEMPSENS</t>
+          <t>DOLPHIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -801,17 +801,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UDS</t>
+          <t>ESSENTIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -821,7 +821,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VADILALIND</t>
+          <t>DLINKINDIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -841,7 +841,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>VIMTALABS</t>
+          <t>GANECOS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -861,7 +861,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WELSPUNLIV</t>
+          <t>GEMAROMA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -881,7 +881,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ZEEL</t>
+          <t>IITL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -901,17 +901,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>LATENTVIEW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -921,7 +921,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>KAMOPAINTS</t>
+          <t>EXXARO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -941,7 +941,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NGIL</t>
+          <t>SAIPARENT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>PNC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -971,37 +971,37 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AERONEU</t>
+          <t>ORIENTTECH</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AFIL</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>PCBL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ALMONDZ</t>
+          <t>PATINTLOG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ANDHRAPAP</t>
+          <t>NELCAST</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1071,17 +1071,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ARIHANTCAP</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IRMENERGY</t>
+          <t>NARMADA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1111,37 +1111,37 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ASIANENE</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BALKRISHNA</t>
+          <t>MOHITIND</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BESTAGRO</t>
+          <t>MOBIKWIK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1171,17 +1171,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BHARATGEAR</t>
+          <t>MEGASTAR</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1191,17 +1191,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1211,17 +1211,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ARTEMISMED</t>
+          <t>NDLVENTURE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1231,57 +1231,57 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DIAMONDYD</t>
+          <t>PURVA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>WALCHANNAG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>RUPA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1291,37 +1291,37 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>ZUARI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FINPIPE</t>
+          <t>XTRANET</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GLOBALE</t>
+          <t>WOCKPHARMA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1351,17 +1351,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GMDCLTD</t>
+          <t>KRYSTAL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1371,17 +1371,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GOCOLORS</t>
+          <t>UFBL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>TVTODAY</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1411,37 +1411,37 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>INDOUS</t>
+          <t>RSL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>TRIDENT</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NILAINFRA</t>
+          <t>TNPETRO</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1471,37 +1471,37 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NITINSPIN</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PACEDIGITK</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1511,17 +1511,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PRIORITY</t>
+          <t>SIGNPOST</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1531,37 +1531,37 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>RAMBHAJO</t>
+          <t>SHREEPUSHK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR</t>
+          <t>SHK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1571,37 +1571,37 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STUDDS</t>
+          <t>TPHQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SUMEETINDS</t>
+          <t>KITEX</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1611,77 +1611,77 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SURAJEST</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>NEUEON</t>
+          <t>JTLIND</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SIGACHI</t>
+          <t>DEVYANI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MHLXMIRU</t>
+          <t>DCMFINSERV</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1691,37 +1691,37 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DLINKINDIA</t>
+          <t>DANGEE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MEIL</t>
+          <t>CSLFINANCE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1731,17 +1731,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MERCURYEV</t>
+          <t>CROWN</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1751,17 +1751,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ATULAUTO</t>
+          <t>CAPILLARY</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1771,17 +1771,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>DIGITIDE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1791,57 +1791,57 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DOLPHIN</t>
+          <t>BORANA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ESSENTIA</t>
+          <t>BCLIND</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1851,37 +1851,37 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GANECOS</t>
+          <t>ARE&amp;M</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GEMAROMA</t>
+          <t>AEROPLANE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>IITL</t>
+          <t>AAKASH</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>LATENTVIEW</t>
+          <t>KANOHAR</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EXXARO</t>
+          <t>BHARATWIRE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1951,27 +1951,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SAIPARENT</t>
+          <t>DIVGIITTS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -1981,7 +1981,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PNC</t>
+          <t>BLSE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1995,18 +1995,18 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ORIENTTECH</t>
+          <t>EFCIL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2015,13 +2015,13 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>JHS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2035,13 +2035,13 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PCBL</t>
+          <t>DOMS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2055,18 +2055,18 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PATINTLOG</t>
+          <t>JAYBARMARU</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2075,13 +2075,13 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>NELCAST</t>
+          <t>IGCL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MOBIKWIK</t>
+          <t>IDEAFORGE</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2115,18 +2115,18 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>HECPROJECT</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>NARMADA</t>
+          <t>HLEGLAS</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2155,18 +2155,18 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>GSLSU</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2175,13 +2175,13 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MOHITIND</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2195,13 +2195,13 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>GOYALALUM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2215,18 +2215,18 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MEGASTAR</t>
+          <t>GANESHCP</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2235,13 +2235,13 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>NDLVENTURE</t>
+          <t>ESDS</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2255,13 +2255,13 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PURVA</t>
+          <t>EPACKPEB</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2275,18 +2275,18 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>HAPPSTMNDS</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2295,13 +2295,13 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>RUPA</t>
+          <t>RHETAN</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -2321,7 +2321,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>RBZJEWEL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -2341,17 +2341,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ZUARI</t>
+          <t>ONEPOINT</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -2361,7 +2361,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>XTRANET</t>
+          <t>RADHIKAJWE</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -2381,7 +2381,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>WOCKPHARMA</t>
+          <t>POKARNA</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -2401,17 +2401,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>WALCHANNAG</t>
+          <t>PARAGMILK</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -2421,17 +2421,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>UFBL</t>
+          <t>ORISSAMINE</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -2441,17 +2441,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>RSL</t>
+          <t>ONIDA</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -2461,7 +2461,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>TVTODAY</t>
+          <t>NORTHARC</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -2481,17 +2481,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>TPHQ</t>
+          <t>MANGLMCEM</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -2501,7 +2501,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>TNPETRO</t>
+          <t>NEPHROPLUS</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -2521,17 +2521,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>NDRINVIT</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -2541,17 +2541,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SIGNPOST</t>
+          <t>METROPOLIS</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -2561,17 +2561,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SHREEPUSHK</t>
+          <t>MASTERTR</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -2581,7 +2581,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SHK</t>
+          <t>MANCREDIT</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -2601,7 +2601,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>TRIDENT</t>
+          <t>LUXIND</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -2621,7 +2621,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>KRYSTAL</t>
+          <t>LAXMIDENTL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -2641,7 +2641,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DANGEE</t>
+          <t>RML</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -2661,17 +2661,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>KANOHAR</t>
+          <t>NEULANDLAB</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -2681,7 +2681,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>KITEX</t>
+          <t>RPPL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -2701,17 +2701,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AAKASH</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -2721,7 +2721,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AEROPLANE</t>
+          <t>SEAMECLTD</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -2741,17 +2741,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>KSB</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -2761,7 +2761,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>ZYDUSWELL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -2781,7 +2781,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BCLIND</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -2801,7 +2801,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BHARATWIRE</t>
+          <t>XPROINDIA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -2821,7 +2821,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BLSE</t>
+          <t>WEWIN</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -2841,17 +2841,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BORANA</t>
+          <t>VASCONEQ</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -2861,7 +2861,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CROWN</t>
+          <t>TRANSRAILL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -2881,7 +2881,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CSLFINANCE</t>
+          <t>TFCILTD</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -2901,17 +2901,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>DCMFINSERV</t>
+          <t>RSYSTEMS</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -2921,17 +2921,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>DEVYANI</t>
+          <t>SUYOG</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -2941,7 +2941,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>DIGITIDE</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -2961,17 +2961,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>DIVGIITTS</t>
+          <t>SUBEXLTD</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -2981,7 +2981,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CAPILLARY</t>
+          <t>SOTL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -3001,7 +3001,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>EFCIL</t>
+          <t>SKFINDIA</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -3021,17 +3021,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>JTLIND</t>
+          <t>SHUKRAPHAR</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -3041,7 +3041,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>DOMS</t>
+          <t>SHANTIGOLD</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -3061,7 +3061,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>JAYBARMARU</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -3081,7 +3081,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>IGCL</t>
+          <t>SEDEMAC</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -3101,7 +3101,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>IDEAFORGE</t>
+          <t>SUMEETINDS</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -3121,7 +3121,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>HLEGLAS</t>
+          <t>KOTHARIPET</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -3141,7 +3141,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>HECPROJECT</t>
+          <t>BLS</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -3161,17 +3161,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>HAPPSTMNDS</t>
+          <t>JGCHEM</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -3181,17 +3181,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>JHS</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -3201,7 +3201,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>BELDING</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -3221,7 +3221,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>GOYALALUM</t>
+          <t>AWFIS</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -3241,17 +3241,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -3261,7 +3261,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ESDS</t>
+          <t>ASIANTILES</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -3281,7 +3281,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>EPACKPEB</t>
+          <t>ASHOKAMET</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -3301,17 +3301,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>GSLSU</t>
+          <t>ARIHANTSUP</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -3321,7 +3321,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>RML</t>
+          <t>ARFIN</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3335,18 +3335,18 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>RHETAN</t>
+          <t>BODALCHEM</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3355,18 +3355,18 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>RBZJEWEL</t>
+          <t>ANTHEM</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>PARAGMILK</t>
+          <t>AMANTA</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3395,18 +3395,18 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ORISSAMINE</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3415,13 +3415,13 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ONIDA</t>
+          <t>ADVENTHTL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3435,18 +3435,18 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ONEPOINT</t>
+          <t>ADSL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3455,13 +3455,13 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MASTERTR</t>
+          <t>ABINFRA</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3475,13 +3475,13 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>NEPHROPLUS</t>
+          <t>AARTIDRUGS</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3495,18 +3495,18 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>METROPOLIS</t>
+          <t>AARNAV</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MANGLMCEM</t>
+          <t>KOPRAN</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3535,18 +3535,18 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>MANCREDIT</t>
+          <t>AMRUTANJAN</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3555,13 +3555,13 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>CAMLINFINE</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3575,13 +3575,13 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>LAXMIDENTL</t>
+          <t>ARIS</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -3595,13 +3595,13 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>NEULANDLAB</t>
+          <t>CEWATER</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3615,13 +3615,13 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>RPPL</t>
+          <t>IPL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3635,18 +3635,18 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>CAMLINFINE</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3655,13 +3655,13 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SEDEMAC</t>
+          <t>HMAAGRO</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -3675,13 +3675,13 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>KSB</t>
+          <t>HIKAL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -3695,13 +3695,13 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>HGINFRA</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -3715,13 +3715,13 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>XPROINDIA</t>
+          <t>GSPLTRANS</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3735,13 +3735,13 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>WEWIN</t>
+          <t>GRAPHITE</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3755,13 +3755,13 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>VMART</t>
+          <t>GLASSWALL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3775,18 +3775,18 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>TRANSRAILL</t>
+          <t>FAZE3Q</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3795,18 +3795,18 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>RSYSTEMS</t>
+          <t>EMCURE</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3815,13 +3815,13 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>TFCILTD</t>
+          <t>INVENTURE</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -3835,13 +3835,13 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SUMEETINDS</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3855,18 +3855,18 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>SUBROS</t>
+          <t>EBGNG</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3875,13 +3875,13 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SUBEXLTD</t>
+          <t>DALMIASUG</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SKFINDIA</t>
+          <t>DAMCAPITAL</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -3915,18 +3915,18 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR</t>
+          <t>CLEANMAX</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3935,13 +3935,13 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>DEEPINDS</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -3955,18 +3955,18 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SUYOG</t>
+          <t>DHOOTTRANS</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3975,18 +3975,18 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>KOTHARIPET</t>
+          <t>DATAMATICS</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -3995,23 +3995,23 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>NORTHARC</t>
+          <t>SAKSOFT</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -4021,17 +4021,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>JGCHEM</t>
+          <t>PREMIERENE</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -4041,7 +4041,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>AWFIS</t>
+          <t>ROLEXRINGS</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -4061,17 +4061,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>RITES</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -4081,17 +4081,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ASIANTILES</t>
+          <t>REPL</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -4101,7 +4101,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ASHOKAMET</t>
+          <t>RAMCOIND</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -4121,7 +4121,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ARIS</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -4141,7 +4141,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ARFIN</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -4161,7 +4161,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>BLS</t>
+          <t>PLATIND</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -4181,7 +4181,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ANTHEM</t>
+          <t>OMNI</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -4201,7 +4201,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>AMANTA</t>
+          <t>ORIENTCER</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -4221,7 +4221,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>ORICONENT</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -4241,17 +4241,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ABINFRA</t>
+          <t>NRBBEARING</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -4261,7 +4261,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>AARTIDRUGS</t>
+          <t>NAVKARURB</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -4281,7 +4281,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>AARNAV</t>
+          <t>MOL</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -4301,7 +4301,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>KOPRAN</t>
+          <t>MITTAL</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -4321,17 +4321,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>AMRUTANJAN</t>
+          <t>MINDTECK</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -4341,17 +4341,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>SBCL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -4361,17 +4361,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ARIHANTSUP</t>
+          <t>PANAMAPET</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -4381,17 +4381,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>CEWATER</t>
+          <t>SCI</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -4401,7 +4401,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>IPL</t>
+          <t>ZENITHSTL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -4421,17 +4421,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>BODALCHEM</t>
+          <t>SHRINGARMS</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -4441,7 +4441,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>HMAAGRO</t>
+          <t>MAZDA</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -4461,7 +4461,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>HIKAL</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -4481,7 +4481,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>HGINFRA</t>
+          <t>WANBURY</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -4501,7 +4501,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>GSPLTRANS</t>
+          <t>VINCOFE</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -4521,17 +4521,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>GLASSWALL</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -4541,7 +4541,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>UNICHEMLAB</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -4561,17 +4561,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>GRAPHITE</t>
+          <t>TVSINVIT</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -4581,7 +4581,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>TOKYOPLAST</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -4601,17 +4601,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>DHOOTTRANS</t>
+          <t>TIJARIA</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -4621,7 +4621,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>DEEPINDS</t>
+          <t>TENNIND</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -4641,17 +4641,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>DATAMATICS</t>
+          <t>TCC</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -4661,7 +4661,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>DAMCAPITAL</t>
+          <t>SWANCORP</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -4681,7 +4681,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>DALMIASUG</t>
+          <t>SUNCLAY</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -4701,7 +4701,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ROLEXRINGS</t>
+          <t>STOVEKRAFT</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -4715,18 +4715,18 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>PREMIERENE</t>
+          <t>SOFTTECH</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4735,18 +4735,18 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>REPL</t>
+          <t>SMSPHARMA</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -4755,13 +4755,13 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>RAMCOIND</t>
+          <t>SKFINDUS</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -4775,13 +4775,13 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>SJS</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -4795,18 +4795,18 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>SHUKRAPHAR</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -4815,13 +4815,13 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>PLATIND</t>
+          <t>SHANKARA</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -4835,7 +4835,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="222">
@@ -4855,13 +4855,13 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ORICONENT</t>
+          <t>CPCAP</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -4875,13 +4875,13 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>OMNI</t>
+          <t>MARINE</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -4895,18 +4895,18 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>NAVKARURB</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -4915,13 +4915,13 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>MOL</t>
+          <t>ELECTHERM</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -4935,13 +4935,13 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>MITTAL</t>
+          <t>DELTAMAGNT</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -4955,18 +4955,18 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>MINDTECK</t>
+          <t>CORALFINAC</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -4975,13 +4975,13 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>CHEMPLASTS</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -4995,18 +4995,18 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>SAKSOFT</t>
+          <t>CERA</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5015,13 +5015,13 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>PANAMAPET</t>
+          <t>CENTUM</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5035,13 +5035,13 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>CAPACITE</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>VINCOFE</t>
+          <t>EMUDHRA</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5075,18 +5075,18 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>SCI</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5095,13 +5095,13 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5115,18 +5115,18 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>WANBURY</t>
+          <t>BALRAMCHIN</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>MARINE</t>
+          <t>BAJEL</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5155,18 +5155,18 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>AUSOMENT</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5175,13 +5175,13 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>UNICHEMLAB</t>
+          <t>APTECHT</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5195,18 +5195,18 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>TVSINVIT</t>
+          <t>APOLLOTYRE</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Fund Raising</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>TOKYOPLAST</t>
+          <t>63MOONS</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5235,13 +5235,13 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>SBCL</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5255,13 +5255,13 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>TIJARIA</t>
+          <t>BLBLIMITED</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5275,18 +5275,18 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>STOVEKRAFT</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -5295,13 +5295,13 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>SOFTTECH</t>
+          <t>AUGMONT</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5315,13 +5315,13 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>SMSPHARMA</t>
+          <t>EXCELINDUS</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -5335,13 +5335,13 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>SJS</t>
+          <t>EPL</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -5355,18 +5355,18 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR</t>
+          <t>MANUGRAPH</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5375,18 +5375,18 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>SHRINGARMS</t>
+          <t>MANIKA</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -5395,13 +5395,13 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>SHANKARA</t>
+          <t>LCL</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5415,13 +5415,13 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>SWANCORP</t>
+          <t>KSHITIJPOL</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5435,18 +5435,18 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>MAPMYINDIA</t>
+          <t>KRISHIVAL</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -5455,13 +5455,13 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>SKFINDUS</t>
+          <t>JKLAKSHMI</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5475,18 +5475,18 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>MANIKA</t>
+          <t>JISLJALEQS</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ELECTHERM</t>
+          <t>JISLDVREQS</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -5515,13 +5515,13 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>DELTAMAGNT</t>
+          <t>LENSKART</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -5535,13 +5535,13 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>CPCAP</t>
+          <t>IVP</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -5555,13 +5555,13 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>CORALFINAC</t>
+          <t>HARIOMPIPE</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -5575,13 +5575,13 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>CHEMPLASTS</t>
+          <t>GUJTHEM</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -5595,18 +5595,18 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>CERA</t>
+          <t>GRSE</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -5615,18 +5615,18 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>CENTUM</t>
+          <t>MAPMYINDIA</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -5635,18 +5635,18 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>GODAVARIB</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -5655,13 +5655,13 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>CAPACITE</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -5675,18 +5675,18 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>MANUGRAPH</t>
+          <t>GKSL</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -5695,13 +5695,13 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>JASH</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -5715,18 +5715,18 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>BALRAMCHIN</t>
+          <t>GAYAPROJ</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -5735,13 +5735,13 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>BAJEL</t>
+          <t>PRAXIS</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D267" t="n">
@@ -5761,17 +5761,17 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>AUSOMENT</t>
+          <t>POLYMED</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D268" t="n">
@@ -5781,17 +5781,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>APOLLOTYRE</t>
+          <t>PATELENG</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D269" t="n">
@@ -5801,17 +5801,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>63MOONS</t>
+          <t>ORIENTPPR</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D270" t="n">
@@ -5821,7 +5821,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>ORIENTLTD</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -5841,17 +5841,17 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D272" t="n">
@@ -5861,7 +5861,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>BLBLIMITED</t>
+          <t>MFML</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D273" t="n">
@@ -5881,7 +5881,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>EPL</t>
+          <t>NBIFIN</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D274" t="n">
@@ -5901,7 +5901,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>MUTHOOTMF</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D275" t="n">
@@ -5921,7 +5921,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>MONEYVIEW</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D276" t="n">
@@ -5941,7 +5941,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>LCL</t>
+          <t>MANYAVAR</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D277" t="n">
@@ -5961,17 +5961,17 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>KSHITIJPOL</t>
+          <t>MANGALAM</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D278" t="n">
@@ -5981,7 +5981,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>JKLAKSHMI</t>
+          <t>PROTEAN</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D279" t="n">
@@ -6001,7 +6001,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>JISLJALEQS</t>
+          <t>MAITHANALL</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D280" t="n">
@@ -6021,7 +6021,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>JISLDVREQS</t>
+          <t>NIMBSPROJ</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D281" t="n">
@@ -6041,7 +6041,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>JASH</t>
+          <t>RATEGAIN</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D282" t="n">
@@ -6061,7 +6061,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>KRISHIVAL</t>
+          <t>SHIPROCKET</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -6071,7 +6071,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D283" t="n">
@@ -6081,7 +6081,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>HARIOMPIPE</t>
+          <t>RNBDENIMS</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D284" t="n">
@@ -6101,7 +6101,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>GUJTHEM</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D285" t="n">
@@ -6121,7 +6121,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>GRSE</t>
+          <t>LEMONTREE</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D286" t="n">
@@ -6141,7 +6141,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>GODAVARIB</t>
+          <t>VEEGALAND</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D287" t="n">
@@ -6161,17 +6161,17 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>UGROCAP</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D288" t="n">
@@ -6181,17 +6181,17 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>GKSL</t>
+          <t>TEXRAIL</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D289" t="n">
@@ -6201,7 +6201,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>GAYAPROJ</t>
+          <t>TEAMLEASE</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D290" t="n">
@@ -6221,7 +6221,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>IVP</t>
+          <t>TCIEXP</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D291" t="n">
@@ -6241,17 +6241,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>EXCELINDUS</t>
+          <t>REPCOHOME</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D292" t="n">
@@ -6261,12 +6261,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ORIENTPPR</t>
+          <t>SYMBIOTEC</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -6275,13 +6275,13 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>NIMBSPROJ</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -6295,13 +6295,13 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>NBIFIN</t>
+          <t>SHAH</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -6315,18 +6315,18 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>MUTHOOTMF</t>
+          <t>SETL</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -6335,13 +6335,13 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>SAMPANN</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -6355,13 +6355,13 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>MANYAVAR</t>
+          <t>RUDRA</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -6375,13 +6375,13 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>MAITHANALL</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -6395,13 +6395,13 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>KARAMTARA</t>
+          <t>RPSGVENT</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -6415,13 +6415,13 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>PRAXIS</t>
+          <t>SMT</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -6435,18 +6435,18 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>MFML</t>
+          <t>KIRIINDUS</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -6455,13 +6455,13 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>PROTEAN</t>
+          <t>LXCHEM</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -6475,13 +6475,13 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>TEAMLEASE</t>
+          <t>JINDWORLD</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -6495,18 +6495,18 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>DHRUV</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -6515,13 +6515,13 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>RUDRA</t>
+          <t>CREST</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -6535,13 +6535,13 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>SAMPANN</t>
+          <t>CEMPRO</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -6555,13 +6555,13 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>SETL</t>
+          <t>BUILDPRO</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -6575,13 +6575,13 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>SHAH</t>
+          <t>BIRLACABLE</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -6595,13 +6595,13 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>BGLOBAL</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -6615,13 +6615,13 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>SYMBIOTEC</t>
+          <t>AWHCL</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -6635,18 +6635,18 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>TCIEXP</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -6655,18 +6655,18 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>UGROCAP</t>
+          <t>ASHOKA</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -6675,18 +6675,18 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>VEEGALAND</t>
+          <t>ASHAPURMIN</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -6695,13 +6695,13 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>ARVSMART</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -6715,13 +6715,13 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>RNBDENIMS</t>
+          <t>APOLLOPIPE</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -6735,13 +6735,13 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>AMAGI</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -6755,18 +6755,18 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>HITECH</t>
+          <t>AGARWALEYE</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -6775,13 +6775,13 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>IGARASHI</t>
+          <t>KARAMTARA</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -6795,18 +6795,18 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>AGARWALEYE</t>
+          <t>DPWIRES</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -6815,13 +6815,13 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>AMAGI</t>
+          <t>DUCON</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -6835,13 +6835,13 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>ARVSMART</t>
+          <t>CAMPUS</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -6855,13 +6855,13 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>ASHOKA</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -6875,13 +6875,13 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>AWHCL</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -6895,18 +6895,18 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>BGLOBAL</t>
+          <t>INDOWIND</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -6915,13 +6915,13 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>BIRLACABLE</t>
+          <t>INDIANHUME</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -6935,13 +6935,13 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>BUILDPRO</t>
+          <t>ELIN</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -6955,13 +6955,13 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>INDIANHUME</t>
+          <t>IGARASHI</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -6975,18 +6975,18 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>CREST</t>
+          <t>HITECH</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -6995,18 +6995,18 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>DHRUV</t>
+          <t>HAPPYFORGE</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -7015,18 +7015,18 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>CEMPRO</t>
+          <t>GUJALKALI</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>DUCON</t>
+          <t>IKIO</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -7055,18 +7055,18 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>HAPPYFORGE</t>
+          <t>GPTHEALTH</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -7075,18 +7075,18 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>DPWIRES</t>
+          <t>GOACARBON</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -7095,18 +7095,18 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>GPTHEALTH</t>
+          <t>GHCLTEXTIL</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -7115,13 +7115,13 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>GOACARBON</t>
+          <t>GCSL</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -7135,13 +7135,13 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>GHCLTEXTIL</t>
+          <t>FERMENTA</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -7155,18 +7155,18 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>GUJALKALI</t>
+          <t>EXCELSOFT</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>EXCELSOFT</t>
+          <t>GTL</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="340">
@@ -7215,13 +7215,13 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>LAMBODHARA</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D341" t="n">
@@ -7241,7 +7241,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>ELIN</t>
+          <t>NITYAS</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D342" t="n">
@@ -7261,17 +7261,17 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>GCSL</t>
+          <t>OCCLLTD</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D343" t="n">
@@ -7281,12 +7281,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>TTKPRESTIG</t>
+          <t>PRECWIRE</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -7295,18 +7295,18 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>RICOAUTO</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="346">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -7335,13 +7335,13 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>NITYAS</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -7355,18 +7355,18 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>KAKATCEM</t>
+          <t>SILGO</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -7375,13 +7375,13 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>TTKPRESTIG</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -7395,18 +7395,18 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>HONASA</t>
+          <t>KAKATCEM</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -7415,13 +7415,13 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>CORDSCABLE</t>
+          <t>PRSMJOHNSN</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -7435,13 +7435,13 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>COHANCE</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -7455,18 +7455,18 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>COFFEEDAY</t>
+          <t>CCAVENUE</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -7475,13 +7475,13 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>BLUSPRING</t>
+          <t>FOSECOIND</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -7495,13 +7495,13 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>ASTERDM</t>
+          <t>DENTA</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -7515,18 +7515,18 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>ALEMBICLTD</t>
+          <t>CORDSCABLE</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -7535,13 +7535,13 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>FOSECOIND</t>
+          <t>COHANCE</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -7555,33 +7555,33 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>GOLDIAM</t>
+          <t>COFFEEDAY</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>TATACHEM</t>
+          <t>BLUSPRING</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -7591,37 +7591,37 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>AVANTIFEED</t>
+          <t>BAJEL</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>DREDGECORP</t>
+          <t>ASTERDM</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -7631,37 +7631,37 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>ALEMBICLTD</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>ROSSELLIND</t>
+          <t>AGIIL</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -7671,17 +7671,17 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>VISAKAIND</t>
+          <t>HONASA</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -7691,17 +7691,17 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>RANEHOLDIN</t>
+          <t>ANDHRSUGAR</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -7711,57 +7711,57 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>MANAKALUCO</t>
+          <t>GOLDIAM</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>BALAXI</t>
+          <t>MAWANASUG</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>ALICON</t>
+          <t>TATACHEM</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -7771,17 +7771,17 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>IFCI</t>
+          <t>ROSSELLIND</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -7791,37 +7791,37 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>JAICORPLTD</t>
+          <t>KALYANKJIL</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>MOTOGENFIN</t>
+          <t>AVANTIFEED</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -7831,17 +7831,17 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>MTNL</t>
+          <t>DREDGECORP</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -7851,17 +7851,17 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>PRECOT</t>
+          <t>ALICON</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -7871,37 +7871,37 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>RHIM</t>
+          <t>BALAXI</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>VENKEYS</t>
+          <t>IFCI</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -7911,37 +7911,37 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>HISARMETAL</t>
+          <t>MANAKALUCO</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>TVSELECT</t>
+          <t>RANEHOLDIN</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -7951,17 +7951,17 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>SANDHAR</t>
+          <t>VISAKAIND</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -7971,31 +7971,211 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
+          <t>VENKEYS</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D379" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>RHIM</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D380" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>PRECOT</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D381" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>JAICORPLTD</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D382" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>MOTOGENFIN</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D383" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>MTNL</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D384" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>HISARMETAL</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>2026-11-14</t>
+        </is>
+      </c>
+      <c r="D385" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>TVSELECT</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>2026-11-14</t>
+        </is>
+      </c>
+      <c r="D386" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>SANDHAR</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="D387" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
           <t>RNBDENIMS</t>
         </is>
       </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C379" t="inlineStr">
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
         <is>
           <t>2026-12-05</t>
         </is>
       </c>
-      <c r="D379" t="n">
-        <v>38</v>
+      <c r="D388" t="n">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/data/upcoming_events.xlsx
+++ b/data/upcoming_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D388"/>
+  <dimension ref="A1:D430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ATULAUTO</t>
+          <t>SAIPARENT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -461,27 +461,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SURAJEST</t>
+          <t>MEGASTAR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -491,17 +491,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SUMEETINDS</t>
+          <t>MOBIKWIK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -511,17 +511,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STUDDS</t>
+          <t>MOHITIND</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -531,37 +531,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RAMBHAJO</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PRIORITY</t>
+          <t>NARMADA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -571,37 +571,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PACEDIGITK</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NITINSPIN</t>
+          <t>NDLVENTURE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -611,17 +611,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NILAINFRA</t>
+          <t>NELCAST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -631,57 +631,57 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NEUEON</t>
+          <t>ORIENTTECH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MHLXMIRU</t>
+          <t>PATINTLOG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SIGACHI</t>
+          <t>PCBL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -691,17 +691,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MEIL</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MERCURYEV</t>
+          <t>PNC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,17 +751,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>PURVA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -771,77 +771,77 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DOLPHIN</t>
+          <t>RSL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ESSENTIA</t>
+          <t>ZUARI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DLINKINDIA</t>
+          <t>XTRANET</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GANECOS</t>
+          <t>WOCKPHARMA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -851,37 +851,37 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GEMAROMA</t>
+          <t>WALCHANNAG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IITL</t>
+          <t>UFBL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -891,17 +891,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LATENTVIEW</t>
+          <t>TVTODAY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EXXARO</t>
+          <t>KRYSTAL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -931,17 +931,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SAIPARENT</t>
+          <t>TRIDENT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -961,7 +961,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PNC</t>
+          <t>TNPETRO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -975,18 +975,18 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ORIENTTECH</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -995,13 +995,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PCBL</t>
+          <t>SIGNPOST</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1035,18 +1035,18 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PATINTLOG</t>
+          <t>SHK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1055,13 +1055,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NELCAST</t>
+          <t>RUPA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1075,13 +1075,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>TPHQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NARMADA</t>
+          <t>KITEX</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1115,18 +1115,18 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>SHREEPUSHK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1135,18 +1135,18 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MOHITIND</t>
+          <t>JTLIND</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1155,18 +1155,18 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MOBIKWIK</t>
+          <t>KANOHAR</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1175,18 +1175,18 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MEGASTAR</t>
+          <t>AAKASH</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>AEROPLANE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1215,18 +1215,18 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NDLVENTURE</t>
+          <t>ARE&amp;M</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1235,13 +1235,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PURVA</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1255,18 +1255,18 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>WALCHANNAG</t>
+          <t>BCLIND</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>RUPA</t>
+          <t>BHARATWIRE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1295,18 +1295,18 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ZUARI</t>
+          <t>BORANA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1315,13 +1315,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>XTRANET</t>
+          <t>CAPILLARY</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>WOCKPHARMA</t>
+          <t>CROWN</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1355,13 +1355,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>KRYSTAL</t>
+          <t>CSLFINANCE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>UFBL</t>
+          <t>DANGEE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TVTODAY</t>
+          <t>DCMFINSERV</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1415,13 +1415,13 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>RSL</t>
+          <t>DEVYANI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1435,13 +1435,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TRIDENT</t>
+          <t>DIGITIDE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1455,13 +1455,13 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TNPETRO</t>
+          <t>BLSE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1475,18 +1475,18 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>DOMS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1495,13 +1495,13 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>JHS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1515,18 +1515,18 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SIGNPOST</t>
+          <t>DIVGIITTS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1535,18 +1535,18 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SHREEPUSHK</t>
+          <t>JAYBARMARU</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1555,13 +1555,13 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SHK</t>
+          <t>IGCL</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1575,18 +1575,18 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TPHQ</t>
+          <t>IDEAFORGE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1595,13 +1595,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>KITEX</t>
+          <t>HECPROJECT</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>HAPPSTMNDS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1635,18 +1635,18 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>JTLIND</t>
+          <t>HLEGLAS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1655,18 +1655,18 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DEVYANI</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1675,13 +1675,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DCMFINSERV</t>
+          <t>GOYALALUM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1695,18 +1695,18 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DANGEE</t>
+          <t>GANESHCP</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CSLFINANCE</t>
+          <t>ESDS</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CROWN</t>
+          <t>EPACKPEB</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1755,13 +1755,13 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CAPILLARY</t>
+          <t>EFCIL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1775,13 +1775,13 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DIGITIDE</t>
+          <t>GSLSU</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1795,13 +1795,13 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BORANA</t>
+          <t>RBZJEWEL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -1821,17 +1821,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BCLIND</t>
+          <t>ONEPOINT</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -1841,7 +1841,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>RHETAN</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -1861,17 +1861,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>RADHIKAJWE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -1881,7 +1881,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AEROPLANE</t>
+          <t>POKARNA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -1901,17 +1901,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AAKASH</t>
+          <t>PARAGMILK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -1921,17 +1921,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>KANOHAR</t>
+          <t>ORISSAMINE</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -1941,7 +1941,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BHARATWIRE</t>
+          <t>ONIDA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -1961,17 +1961,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DIVGIITTS</t>
+          <t>NORTHARC</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -1981,7 +1981,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BLSE</t>
+          <t>MANCREDIT</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -2001,7 +2001,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EFCIL</t>
+          <t>NEPHROPLUS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -2021,17 +2021,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>JHS</t>
+          <t>NDRINVIT</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -2041,17 +2041,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DOMS</t>
+          <t>METROPOLIS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -2061,7 +2061,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>JAYBARMARU</t>
+          <t>MASTERTR</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -2081,7 +2081,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>IGCL</t>
+          <t>MANGLMCEM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -2101,7 +2101,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>IDEAFORGE</t>
+          <t>LUXIND</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -2121,7 +2121,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>HECPROJECT</t>
+          <t>RML</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -2141,7 +2141,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>HLEGLAS</t>
+          <t>LAXMIDENTL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -2161,7 +2161,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>GSLSU</t>
+          <t>NEULANDLAB</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -2181,7 +2181,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>RPPL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -2201,7 +2201,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>GOYALALUM</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -2221,17 +2221,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>SAGARDEEP</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -2241,7 +2241,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ESDS</t>
+          <t>KSB</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -2261,7 +2261,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EPACKPEB</t>
+          <t>ZYDUSWELL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -2281,17 +2281,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>HAPPSTMNDS</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -2301,7 +2301,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>RHETAN</t>
+          <t>XPROINDIA</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2315,18 +2315,18 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>RBZJEWEL</t>
+          <t>WEWIN</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2335,18 +2335,18 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ONEPOINT</t>
+          <t>VASCONEQ</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2355,13 +2355,13 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>RADHIKAJWE</t>
+          <t>TRANSRAILL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>POKARNA</t>
+          <t>TFCILTD</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2395,13 +2395,13 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PARAGMILK</t>
+          <t>SUYOG</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2415,18 +2415,18 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ORISSAMINE</t>
+          <t>SUMEETINDS</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2435,13 +2435,13 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ONIDA</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>NORTHARC</t>
+          <t>SUBEXLTD</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MANGLMCEM</t>
+          <t>SOTL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2495,13 +2495,13 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>NEPHROPLUS</t>
+          <t>SKFINDIA</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2515,18 +2515,18 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>NDRINVIT</t>
+          <t>SHUKRAPHAR</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2535,18 +2535,18 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>METROPOLIS</t>
+          <t>SHANTIGOLD</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2555,13 +2555,13 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MASTERTR</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2575,13 +2575,13 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MANCREDIT</t>
+          <t>SEDEMAC</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2595,13 +2595,13 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>SEAMECLTD</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2615,18 +2615,18 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>LAXMIDENTL</t>
+          <t>RSYSTEMS</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>RML</t>
+          <t>KOTHARIPET</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2655,13 +2655,13 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>NEULANDLAB</t>
+          <t>GRAPHITE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2675,13 +2675,13 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>RPPL</t>
+          <t>JGCHEM</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2695,18 +2695,18 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>VMART</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2715,13 +2715,13 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SEAMECLTD</t>
+          <t>BLS</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2735,13 +2735,13 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>KSB</t>
+          <t>BELDING</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2755,13 +2755,13 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>AWFIS</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2775,18 +2775,18 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -2795,13 +2795,13 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>XPROINDIA</t>
+          <t>ASIANTILES</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2815,13 +2815,13 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>WEWIN</t>
+          <t>ASHOKAMET</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2835,18 +2835,18 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>VASCONEQ</t>
+          <t>ARIS</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -2855,18 +2855,18 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>TRANSRAILL</t>
+          <t>ARIHANTSUP</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -2875,13 +2875,13 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>TFCILTD</t>
+          <t>ANTHEM</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2895,18 +2895,18 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>RSYSTEMS</t>
+          <t>AMRUTANJAN</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -2915,13 +2915,13 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SUYOG</t>
+          <t>AMANTA</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2935,13 +2935,13 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SUBROS</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2955,13 +2955,13 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SUBEXLTD</t>
+          <t>ADVENTHTL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2975,13 +2975,13 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SOTL</t>
+          <t>ADSL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2995,13 +2995,13 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SKFINDIA</t>
+          <t>ABINFRA</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3015,13 +3015,13 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR</t>
+          <t>AARTIDRUGS</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3035,13 +3035,13 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SHANTIGOLD</t>
+          <t>AARNAV</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3055,13 +3055,13 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>KOPRAN</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3075,18 +3075,18 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SEDEMAC</t>
+          <t>BODALCHEM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3095,18 +3095,18 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SUMEETINDS</t>
+          <t>CAMLINFINE</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3115,13 +3115,13 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>KOTHARIPET</t>
+          <t>ARFIN</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>BLS</t>
+          <t>CEWATER</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3155,13 +3155,13 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>JGCHEM</t>
+          <t>IPL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3175,18 +3175,18 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>CAMLINFINE</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3195,13 +3195,13 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BELDING</t>
+          <t>INVENTURE</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3215,13 +3215,13 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>AWFIS</t>
+          <t>HMAAGRO</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3235,18 +3235,18 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>HIKAL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3255,13 +3255,13 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ASIANTILES</t>
+          <t>HGINFRA</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ASHOKAMET</t>
+          <t>GLASSWALL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3295,18 +3295,18 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ARIHANTSUP</t>
+          <t>GENCON</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3315,18 +3315,18 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ARFIN</t>
+          <t>FAZE3Q</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3335,18 +3335,18 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BODALCHEM</t>
+          <t>GSPLTRANS</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3355,13 +3355,13 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ANTHEM</t>
+          <t>EMCURE</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3375,18 +3375,18 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>AMANTA</t>
+          <t>EBGNG</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3395,13 +3395,13 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3415,18 +3415,18 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ADVENTHTL</t>
+          <t>DHOOTTRANS</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3435,13 +3435,13 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ADSL</t>
+          <t>DEEPINDS</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3455,18 +3455,18 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ABINFRA</t>
+          <t>DATAMATICS</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3475,13 +3475,13 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>AARTIDRUGS</t>
+          <t>DAMCAPITAL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3495,13 +3495,13 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>AARNAV</t>
+          <t>DALMIASUG</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3515,18 +3515,18 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>KOPRAN</t>
+          <t>CLEANMAX</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3535,23 +3535,23 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>AMRUTANJAN</t>
+          <t>RAMCOIND</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -3561,7 +3561,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CAMLINFINE</t>
+          <t>REDINGTON</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -3581,7 +3581,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ARIS</t>
+          <t>RELTD</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -3601,17 +3601,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CEWATER</t>
+          <t>REPL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -3621,7 +3621,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>IPL</t>
+          <t>ROLEXRINGS</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -3641,17 +3641,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>CAMLINFINE</t>
+          <t>RITES</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -3661,7 +3661,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>HMAAGRO</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -3681,7 +3681,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>HIKAL</t>
+          <t>PWL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -3701,17 +3701,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>HGINFRA</t>
+          <t>SAKSOFT</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -3721,7 +3721,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>GSPLTRANS</t>
+          <t>RIIT</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -3741,7 +3741,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>GRAPHITE</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -3761,7 +3761,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>GLASSWALL</t>
+          <t>MOLDTECH</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -3781,17 +3781,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>FAZE3Q</t>
+          <t>PLATIND</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -3801,7 +3801,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>PATELRMART</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -3821,7 +3821,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>INVENTURE</t>
+          <t>PANAMAPET</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -3841,7 +3841,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>ORIENTCER</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -3861,17 +3861,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>EBGNG</t>
+          <t>ORICONENT</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -3881,7 +3881,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>DALMIASUG</t>
+          <t>OMNI</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -3901,17 +3901,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>DAMCAPITAL</t>
+          <t>NRBBEARING</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -3921,17 +3921,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>CLEANMAX</t>
+          <t>MOL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -3941,7 +3941,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>DEEPINDS</t>
+          <t>MITTAL</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -3961,7 +3961,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>DHOOTTRANS</t>
+          <t>MINDTECK</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -3981,17 +3981,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>DATAMATICS</t>
+          <t>SBCL</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Dividend/Bonus/Other business matters</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -4001,7 +4001,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SAKSOFT</t>
+          <t>PREMIERENE</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4015,18 +4015,18 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>PREMIERENE</t>
+          <t>SBCL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4035,18 +4035,18 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ROLEXRINGS</t>
+          <t>VINEETLAB</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4055,18 +4055,18 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>SHANKARA</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4075,18 +4075,18 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>REPL</t>
+          <t>MAZDA</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4095,13 +4095,13 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>RAMCOIND</t>
+          <t>ZENITHSTL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4115,13 +4115,13 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4135,13 +4135,13 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>WANBURY</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4155,13 +4155,13 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>PLATIND</t>
+          <t>VLEGOV</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4175,13 +4175,13 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>OMNI</t>
+          <t>VINCOFE</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4195,18 +4195,18 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ORIENTCER</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4215,13 +4215,13 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ORICONENT</t>
+          <t>UNICHEMLAB</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4235,18 +4235,18 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>NRBBEARING</t>
+          <t>TVSINVIT</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4255,13 +4255,13 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>NAVKARURB</t>
+          <t>TRACXN</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4275,13 +4275,13 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>MOL</t>
+          <t>TOKYOPLAST</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4295,13 +4295,13 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>MITTAL</t>
+          <t>TIJARIA</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4315,18 +4315,18 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>MINDTECK</t>
+          <t>TENNIND</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4335,13 +4335,13 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SBCL</t>
+          <t>TCC</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>PANAMAPET</t>
+          <t>SWANCORP</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4375,18 +4375,18 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SCI</t>
+          <t>SUNCLAY</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4395,13 +4395,13 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ZENITHSTL</t>
+          <t>STOVEKRAFT</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4415,13 +4415,13 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SHRINGARMS</t>
+          <t>SOFTTECH</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4435,13 +4435,13 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>MAZDA</t>
+          <t>SMSPHARMA</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4455,13 +4455,13 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>SKFINDUS</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4475,13 +4475,13 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>WANBURY</t>
+          <t>SJS</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4495,13 +4495,13 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>VINCOFE</t>
+          <t>SHUKRAPHAR</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4515,18 +4515,18 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>SHRINGARMS</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4535,18 +4535,18 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>UNICHEMLAB</t>
+          <t>SCI</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4555,13 +4555,13 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>TVSINVIT</t>
+          <t>MAYURUNIQ</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4575,13 +4575,13 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>TOKYOPLAST</t>
+          <t>NAVKARURB</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>TIJARIA</t>
+          <t>MARINE</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -4615,18 +4615,18 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>TENNIND</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4635,13 +4635,13 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>TCC</t>
+          <t>ELECTHERM</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -4655,13 +4655,13 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>SWANCORP</t>
+          <t>DOLLEX</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -4675,18 +4675,18 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>SUNCLAY</t>
+          <t>DIFFNKG</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4695,13 +4695,13 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>STOVEKRAFT</t>
+          <t>DELTAMAGNT</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -4715,13 +4715,13 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>SOFTTECH</t>
+          <t>CPCAP</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -4735,13 +4735,13 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>SMSPHARMA</t>
+          <t>CORALFINAC</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -4755,13 +4755,13 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>SKFINDUS</t>
+          <t>CHEMPLASTS</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -4775,18 +4775,18 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>SJS</t>
+          <t>CERA</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -4795,13 +4795,13 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR</t>
+          <t>CENTUM</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -4815,13 +4815,13 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>SHANKARA</t>
+          <t>CAPACITE</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -4835,18 +4835,18 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>MAYURUNIQ</t>
+          <t>EMUDHRA</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -4855,13 +4855,13 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>CPCAP</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -4875,13 +4875,13 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>MARINE</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -4895,18 +4895,18 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>BECTORFOOD</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -4915,18 +4915,18 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ELECTHERM</t>
+          <t>BALRAMCHIN</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -4935,18 +4935,18 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>DELTAMAGNT</t>
+          <t>BALKRISIND</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -4955,13 +4955,13 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>CORALFINAC</t>
+          <t>BAJEL</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -4975,13 +4975,13 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>CHEMPLASTS</t>
+          <t>AUSOMENT</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -4995,18 +4995,18 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>CERA</t>
+          <t>AUGMONT</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5015,13 +5015,13 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>CENTUM</t>
+          <t>APTECHT</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5035,18 +5035,18 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>CAPACITE</t>
+          <t>APOLLOTYRE</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>63MOONS</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5075,13 +5075,13 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5095,13 +5095,13 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>BLBLIMITED</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5115,18 +5115,18 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>BALRAMCHIN</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>BAJEL</t>
+          <t>AEROENTER</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5155,13 +5155,13 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>AUSOMENT</t>
+          <t>EXCELINDUS</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5175,13 +5175,13 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>APTECHT</t>
+          <t>EPL</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5195,18 +5195,18 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>APOLLOTYRE</t>
+          <t>MAPMYINDIA</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5215,18 +5215,18 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>63MOONS</t>
+          <t>MANIKA</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5235,13 +5235,13 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>LUMINO</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5255,13 +5255,13 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>BLBLIMITED</t>
+          <t>LENSKART</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5275,18 +5275,18 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>LCL</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -5295,13 +5295,13 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>AUGMONT</t>
+          <t>KSHITIJPOL</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5315,13 +5315,13 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>EXCELINDUS</t>
+          <t>KRISHIVAL</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -5335,13 +5335,13 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>EPL</t>
+          <t>JKLAKSHMI</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -5355,18 +5355,18 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>MANUGRAPH</t>
+          <t>JISLJALEQS</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5375,18 +5375,18 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>MANIKA</t>
+          <t>JISLDVREQS</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -5395,18 +5395,18 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>LCL</t>
+          <t>MANUGRAPH</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -5415,13 +5415,13 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>KSHITIJPOL</t>
+          <t>IVP</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5435,13 +5435,13 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>KRISHIVAL</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5455,13 +5455,13 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>JKLAKSHMI</t>
+          <t>HTEL</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5475,13 +5475,13 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>JISLJALEQS</t>
+          <t>HARIOMPIPE</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>JISLDVREQS</t>
+          <t>GUJTHEM</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -5515,13 +5515,13 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>GRSE</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -5535,13 +5535,13 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>IVP</t>
+          <t>GODAVARIB</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -5555,13 +5555,13 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>HARIOMPIPE</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -5575,13 +5575,13 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>GUJTHEM</t>
+          <t>GKSL</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -5595,13 +5595,13 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>GRSE</t>
+          <t>GAJA</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -5615,18 +5615,18 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>MAPMYINDIA</t>
+          <t>JASH</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -5635,13 +5635,13 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>GODAVARIB</t>
+          <t>GAYAPROJ</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -5655,13 +5655,13 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>ORIENTLTD</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -5681,17 +5681,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>GKSL</t>
+          <t>ORIENTPPR</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -5701,7 +5701,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>JASH</t>
+          <t>PATELENG</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D265" t="n">
@@ -5721,7 +5721,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>GAYAPROJ</t>
+          <t>RATEGAIN</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D266" t="n">
@@ -5755,18 +5755,18 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>POLYMED</t>
+          <t>PREMIER</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -5775,13 +5775,13 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>PATELENG</t>
+          <t>PROTEAN</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -5795,18 +5795,18 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>ORIENTPPR</t>
+          <t>REPCOHOME</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -5815,18 +5815,18 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ORIENTLTD</t>
+          <t>POLYMED</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="272">
@@ -5855,13 +5855,13 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>MFML</t>
+          <t>MMFL</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="274">
@@ -5895,7 +5895,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="275">
@@ -5915,13 +5915,13 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>MONEYVIEW</t>
+          <t>MUFIN</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -5935,13 +5935,13 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>MANYAVAR</t>
+          <t>MONEYVIEW</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -5955,18 +5955,18 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>MANGALAM</t>
+          <t>MFML</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -5975,13 +5975,13 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>PROTEAN</t>
+          <t>MBEL</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -5995,13 +5995,13 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>MAITHANALL</t>
+          <t>MANYAVAR</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -6015,18 +6015,18 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>NIMBSPROJ</t>
+          <t>MANGALAM</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -6035,13 +6035,13 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>RATEGAIN</t>
+          <t>RNBDENIMS</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -6055,13 +6055,13 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>SHIPROCKET</t>
+          <t>MAITHANALL</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -6075,13 +6075,13 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>RNBDENIMS</t>
+          <t>LXCHEM</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -6095,13 +6095,13 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>NIMBSPROJ</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -6115,13 +6115,13 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>LEMONTREE</t>
+          <t>RPSGVENT</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -6135,13 +6135,13 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>VEEGALAND</t>
+          <t>SYMBIOTEC</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -6155,18 +6155,18 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>UGROCAP</t>
+          <t>RUDRA</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -6175,18 +6175,18 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>TEXRAIL</t>
+          <t>WINDLAS</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -6195,13 +6195,13 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>TEAMLEASE</t>
+          <t>LEMONTREE</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>TCIEXP</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -6235,13 +6235,13 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>REPCOHOME</t>
+          <t>VENUSPIPES</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -6255,13 +6255,13 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>SYMBIOTEC</t>
+          <t>VEEGALAND</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -6275,13 +6275,13 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>URJA</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -6295,13 +6295,13 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>SHAH</t>
+          <t>UNIVASTU</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -6315,18 +6315,18 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>SETL</t>
+          <t>UGROCAP</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -6335,13 +6335,13 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>SAMPANN</t>
+          <t>TONBO</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -6355,18 +6355,18 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>RUDRA</t>
+          <t>TEXRAIL</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -6375,18 +6375,18 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>TEXINFRA</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -6395,13 +6395,13 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>RPSGVENT</t>
+          <t>TEAMLEASE</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -6415,13 +6415,13 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>TCIEXP</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -6435,13 +6435,13 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>KIRIINDUS</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -6455,18 +6455,18 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>SONATSOFTW</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -6475,13 +6475,13 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>JINDWORLD</t>
+          <t>SMT</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -6495,18 +6495,18 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>DHRUV</t>
+          <t>SHIPROCKET</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -6515,13 +6515,13 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>CREST</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -6535,13 +6535,13 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>CEMPRO</t>
+          <t>SHANKESH</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -6555,13 +6555,13 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>BUILDPRO</t>
+          <t>SHAH</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -6575,13 +6575,13 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>BIRLACABLE</t>
+          <t>SETL</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -6595,13 +6595,13 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>BGLOBAL</t>
+          <t>SAMPANN</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -6615,13 +6615,13 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>AWHCL</t>
+          <t>SABEVENTS</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -6635,18 +6635,18 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -6655,18 +6655,18 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>ASHOKA</t>
+          <t>LEMERITE</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -6675,18 +6675,18 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>ASHAPURMIN</t>
+          <t>MANYAVAR</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -6695,13 +6695,13 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>ARVSMART</t>
+          <t>KRONOX</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -6715,13 +6715,13 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>APOLLOPIPE</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -6735,13 +6735,13 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>AMAGI</t>
+          <t>DUCON</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -6755,18 +6755,18 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>AGARWALEYE</t>
+          <t>DPWIRES</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -6775,18 +6775,18 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>KARAMTARA</t>
+          <t>DHRUV</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -6795,13 +6795,13 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>DPWIRES</t>
+          <t>DEVIT</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -6815,13 +6815,13 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>DUCON</t>
+          <t>CEMPRO</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -6835,7 +6835,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="322">
@@ -6855,13 +6855,13 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>BUILDPRO</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -6875,13 +6875,13 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>BIRLACABLE</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -6895,18 +6895,18 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>INDOWIND</t>
+          <t>BGLOBAL</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -6915,13 +6915,13 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>INDIANHUME</t>
+          <t>ELIN</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -6935,13 +6935,13 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>ELIN</t>
+          <t>BCONCEPTS</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -6955,18 +6955,18 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>IGARASHI</t>
+          <t>AVADHSUGAR</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -6975,18 +6975,18 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>HITECH</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -6995,13 +6995,13 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>HAPPYFORGE</t>
+          <t>ASHOKA</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -7015,13 +7015,13 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>GUJALKALI</t>
+          <t>ASHAPURMIN</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>IKIO</t>
+          <t>ARVSMART</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -7055,18 +7055,18 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>GPTHEALTH</t>
+          <t>APOLLOPIPE</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -7075,13 +7075,13 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>GOACARBON</t>
+          <t>AMAGI</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -7095,13 +7095,13 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>GHCLTEXTIL</t>
+          <t>AGARWALEYE</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -7115,13 +7115,13 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>GCSL</t>
+          <t>ABFRL</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -7135,13 +7135,13 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>FERMENTA</t>
+          <t>KUSUMGAR</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>EXCELSOFT</t>
+          <t>AWHCL</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>GTL</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -7195,13 +7195,13 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>EUROPRATIK</t>
+          <t>CREST</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -7215,13 +7215,13 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>LAMBODHARA</t>
+          <t>EXCELSOFT</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -7231,17 +7231,17 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>NITYAS</t>
+          <t>KRITI</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -7251,57 +7251,57 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>OCCLLTD</t>
+          <t>KIRIINDUS</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>PRECWIRE</t>
+          <t>KHADIM</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>RICOAUTO</t>
+          <t>KARAMTARA</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -7311,37 +7311,37 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>EUROPRATIK</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -7351,37 +7351,37 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>SILGO</t>
+          <t>INDOWIND</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>TTKPRESTIG</t>
+          <t>INDIANHUME</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -7391,37 +7391,37 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>KAKATCEM</t>
+          <t>IKIO</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>PRSMJOHNSN</t>
+          <t>IGARASHI</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -7431,57 +7431,57 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>HITECH</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>CCAVENUE</t>
+          <t>HAPPYFORGE</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>FOSECOIND</t>
+          <t>JINDWORLD</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -7491,17 +7491,17 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>DENTA</t>
+          <t>GTL</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -7511,37 +7511,37 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>CORDSCABLE</t>
+          <t>GUJALKALI</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>COHANCE</t>
+          <t>GALAPREC</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>COFFEEDAY</t>
+          <t>GERMAN</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -7571,17 +7571,17 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>BLUSPRING</t>
+          <t>GHCLTEXTIL</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -7591,17 +7591,17 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>BAJEL</t>
+          <t>GCSL</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -7611,17 +7611,17 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>ASTERDM</t>
+          <t>GODIGIT</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -7631,57 +7631,57 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>ALEMBICLTD</t>
+          <t>GOKEX</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>AGIIL</t>
+          <t>GPTHEALTH</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>HONASA</t>
+          <t>GOACARBON</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -7691,17 +7691,17 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>ANDHRSUGAR</t>
+          <t>FERMENTA</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -7711,77 +7711,77 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>GOLDIAM</t>
+          <t>NITYAS</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>MAWANASUG</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>TATACHEM</t>
+          <t>OCCLLTD</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>ROSSELLIND</t>
+          <t>PIXTRANS</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -7791,57 +7791,57 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>PRECWIRE</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>AVANTIFEED</t>
+          <t>PRSMJOHNSN</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>DREDGECORP</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -7851,37 +7851,37 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>ALICON</t>
+          <t>SIRCA</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>BALAXI</t>
+          <t>SCODATUBES</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -7891,17 +7891,17 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>IFCI</t>
+          <t>SILGO</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -7911,17 +7911,17 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>MANAKALUCO</t>
+          <t>SOLEX</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -7931,17 +7931,17 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>RANEHOLDIN</t>
+          <t>TTKPRESTIG</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -7951,17 +7951,17 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>VISAKAIND</t>
+          <t>VTL</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -7971,17 +7971,17 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>VENKEYS</t>
+          <t>LAMBODHARA</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -7991,17 +7991,17 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>RHIM</t>
+          <t>RICOAUTO</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -8011,37 +8011,37 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>PRECOT</t>
+          <t>KAKATCEM</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>JAICORPLTD</t>
+          <t>CCAVENUE</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -8051,17 +8051,17 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>MOTOGENFIN</t>
+          <t>INDOBORAX</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -8071,17 +8071,17 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>MTNL</t>
+          <t>AGIIL</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -8091,17 +8091,17 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>HISARMETAL</t>
+          <t>ALEMBICLTD</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -8111,17 +8111,17 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>TVSELECT</t>
+          <t>ASTERDM</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -8131,17 +8131,17 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>SANDHAR</t>
+          <t>AUTOIND</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -8151,31 +8151,871 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
+          <t>BLUSPRING</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D388" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>CMRGREEN</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D389" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>BAJEL</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D390" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>COHANCE</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D391" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>CORDSCABLE</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D392" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>DENTA</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D393" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>FOSECOIND</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D394" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>GTLINFRA</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D395" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>HONASA</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D396" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>COFFEEDAY</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D397" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D398" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>TATACHEM</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+      <c r="D399" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>ANDHRSUGAR</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+      <c r="D400" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>GOLDIAM</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+      <c r="D401" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>MAWANASUG</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+      <c r="D402" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>PROSTARM</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+      <c r="D403" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>ROSSELLIND</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="D404" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="D405" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>AVANTIFEED</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="D406" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>DREDGECORP</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="D407" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>ALICON</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D408" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>AVALON</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D409" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>BALAXI</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D410" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>CROWN</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D411" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>IFCI</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D412" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>MANAKALUCO</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D413" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>PRIMESECU</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D414" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>RANEHOLDIN</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D415" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>VARDMNPOLY</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D416" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>VISAKAIND</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D417" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>VENKEYS</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D418" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>RHIM</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D419" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>PRECOT</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D420" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>MTNL</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D421" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>BFINVEST</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D422" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D423" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>JAICORPLTD</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D424" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>EIDPARRY</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D425" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>MOTOGENFIN</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D426" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>HISARMETAL</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>2026-11-14</t>
+        </is>
+      </c>
+      <c r="D427" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>TVSELECT</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>2026-11-14</t>
+        </is>
+      </c>
+      <c r="D428" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>SANDHAR</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="D429" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
           <t>RNBDENIMS</t>
         </is>
       </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C388" t="inlineStr">
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
         <is>
           <t>2026-12-05</t>
         </is>
       </c>
-      <c r="D388" t="n">
-        <v>37</v>
+      <c r="D430" t="n">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
